--- a/research/traditional_assets/database/data/norway/norway_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1321527059634609</v>
       </c>
       <c r="X2">
-        <v>0.08060662525856385</v>
+        <v>0.08058424769319814</v>
       </c>
       <c r="Y2">
-        <v>0.05154608070489702</v>
+        <v>0.05156845827026274</v>
       </c>
       <c r="Z2">
         <v>0.6018152713049925</v>
@@ -662,10 +662,10 @@
         <v>0.09507676882763957</v>
       </c>
       <c r="AB2">
-        <v>0.06582882870840294</v>
+        <v>0.06581527601468636</v>
       </c>
       <c r="AC2">
-        <v>0.02924794011923663</v>
+        <v>0.02926149281295322</v>
       </c>
       <c r="AD2">
         <v>9948.700000000001</v>
@@ -787,10 +787,10 @@
         <v>0.1321527059634609</v>
       </c>
       <c r="X3">
-        <v>0.08060662525856385</v>
+        <v>0.08058424769319814</v>
       </c>
       <c r="Y3">
-        <v>0.05154608070489702</v>
+        <v>0.05156845827026274</v>
       </c>
       <c r="Z3">
         <v>0.6018152713049925</v>
@@ -799,10 +799,10 @@
         <v>0.09507676882763957</v>
       </c>
       <c r="AB3">
-        <v>0.06582882870840294</v>
+        <v>0.06581527601468636</v>
       </c>
       <c r="AC3">
-        <v>0.02924794011923663</v>
+        <v>0.02926149281295322</v>
       </c>
       <c r="AD3">
         <v>9948.700000000001</v>
@@ -1139,49 +1139,49 @@
         <v>2.60239162929746</v>
       </c>
       <c r="F2">
-        <v>3.13664839580326</v>
+        <v>3.11991582298659</v>
       </c>
       <c r="G2">
         <v>4.03975311649815</v>
       </c>
       <c r="H2">
-        <v>1.94631380192472</v>
+        <v>2.04875137044707</v>
       </c>
       <c r="I2">
         <v>0.394362456545092</v>
       </c>
       <c r="J2">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>15278.6</v>
       </c>
       <c r="L2">
-        <v>19431.3155953215</v>
+        <v>19407.4299309962</v>
       </c>
       <c r="M2">
         <v>23644.4</v>
       </c>
       <c r="N2">
-        <v>22641.6025953215</v>
+        <v>22869.9899309962</v>
       </c>
       <c r="O2">
         <v>9948.700000000001</v>
       </c>
       <c r="P2">
-        <v>4793.187</v>
+        <v>5045.46</v>
       </c>
       <c r="Q2">
-        <v>0.0658288287084029</v>
+        <v>0.0658152760146864</v>
       </c>
       <c r="R2">
-        <v>0.0677967785082443</v>
+        <v>0.0673198289535071</v>
       </c>
       <c r="S2">
         <v>0.043134</v>
       </c>
       <c r="T2">
-        <v>0.045162</v>
+        <v>0.043134</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.08060662525856389</v>
+        <v>0.08058424769319809</v>
       </c>
       <c r="X2">
-        <v>0.0731061709978325</v>
+        <v>0.0733662861918839</v>
       </c>
       <c r="Y2">
         <v>0.803331355501112</v>
       </c>
       <c r="Z2">
-        <v>0.63022206830686</v>
+        <v>0.636634785031961</v>
       </c>
       <c r="AA2">
         <v>9948.700000000001</v>
@@ -1236,7 +1236,7 @@
         <v>15278.6</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="C2">
-        <v>23706.66544514484</v>
+        <v>23707.24722273858</v>
       </c>
       <c r="D2">
-        <v>22123.76544514484</v>
+        <v>22124.34722273858</v>
       </c>
       <c r="E2">
         <v>-9948.700000000001</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06877733984922371</v>
+        <v>0.06875161226967512</v>
       </c>
       <c r="C3">
-        <v>23503.66353598001</v>
+        <v>23509.34494810757</v>
       </c>
       <c r="D3">
-        <v>22173.03653598001</v>
+        <v>22178.71794810757</v>
       </c>
       <c r="E3">
         <v>-9696.427000000001</v>
@@ -1539,37 +1539,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M3">
-        <v>13.0425141</v>
+        <v>12.6893319</v>
       </c>
       <c r="N3">
-        <v>857.4574858999998</v>
+        <v>857.8106680999998</v>
       </c>
       <c r="O3">
-        <v>188.640646898</v>
+        <v>188.718346982</v>
       </c>
       <c r="P3">
-        <v>668.8168390019998</v>
+        <v>669.0923211179999</v>
       </c>
       <c r="Q3">
-        <v>2261.016839002</v>
+        <v>2261.292321118</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06906472712042799</v>
+        <v>0.0690497699693688</v>
       </c>
       <c r="T3">
         <v>0.5369461886690254</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.74326692888143</v>
+        <v>68.60093241000338</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06867181755250264</v>
+        <v>0.06863520262145574</v>
       </c>
       <c r="C4">
-        <v>23300.88157662269</v>
+        <v>23311.71056463428</v>
       </c>
       <c r="D4">
-        <v>22222.52757662269</v>
+        <v>22233.35656463428</v>
       </c>
       <c r="E4">
         <v>-9444.154</v>
@@ -1621,37 +1621,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M4">
-        <v>26.0850282</v>
+        <v>25.3786638</v>
       </c>
       <c r="N4">
-        <v>844.4149717999998</v>
+        <v>845.1213361999997</v>
       </c>
       <c r="O4">
-        <v>185.771293796</v>
+        <v>185.926693964</v>
       </c>
       <c r="P4">
-        <v>658.6436780039999</v>
+        <v>659.1946422359998</v>
       </c>
       <c r="Q4">
-        <v>2250.843678004</v>
+        <v>2251.394642236</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06925030362500269</v>
+        <v>0.06923522716475076</v>
       </c>
       <c r="T4">
         <v>0.5412292647748445</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.37163346444071</v>
+        <v>34.30046620500168</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06856629525578155</v>
+        <v>0.06851879297323638</v>
       </c>
       <c r="C5">
-        <v>23098.32104317602</v>
+        <v>23114.34605710666</v>
       </c>
       <c r="D5">
-        <v>22272.24004317601</v>
+        <v>22288.26505710666</v>
       </c>
       <c r="E5">
         <v>-9191.881000000001</v>
@@ -1703,37 +1703,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M5">
-        <v>39.12754230000001</v>
+        <v>38.0679957</v>
       </c>
       <c r="N5">
-        <v>831.3724576999998</v>
+        <v>832.4320042999998</v>
       </c>
       <c r="O5">
-        <v>182.901940694</v>
+        <v>183.1350409459999</v>
       </c>
       <c r="P5">
-        <v>648.4705170059999</v>
+        <v>649.2969633539999</v>
       </c>
       <c r="Q5">
-        <v>2240.670517006</v>
+        <v>2241.496963354</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06943970644925934</v>
+        <v>0.06942450821983132</v>
       </c>
       <c r="T5">
         <v>0.545600651728206</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.24775564296047</v>
+        <v>22.86697747000112</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06846077295906047</v>
+        <v>0.06840238332501701</v>
       </c>
       <c r="C6">
-        <v>22895.98342498105</v>
+        <v>22917.25342996812</v>
       </c>
       <c r="D6">
-        <v>22322.17542498105</v>
+        <v>22343.44542996812</v>
       </c>
       <c r="E6">
         <v>-8939.608</v>
@@ -1785,37 +1785,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M6">
-        <v>52.17005640000001</v>
+        <v>50.7573276</v>
       </c>
       <c r="N6">
-        <v>818.3299435999998</v>
+        <v>819.7426723999997</v>
       </c>
       <c r="O6">
-        <v>180.0325875919999</v>
+        <v>180.3433879279999</v>
       </c>
       <c r="P6">
-        <v>638.2973560079998</v>
+        <v>639.3992844719997</v>
       </c>
       <c r="Q6">
-        <v>2230.497356008</v>
+        <v>2231.599284472</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.069633055165688</v>
+        <v>0.06961773263022605</v>
       </c>
       <c r="T6">
         <v>0.550063109243096</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.68581673222035</v>
+        <v>17.15023310250084</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06835525066233941</v>
+        <v>0.06828597367679765</v>
       </c>
       <c r="C7">
-        <v>22693.87022476559</v>
+        <v>22720.43470756142</v>
       </c>
       <c r="D7">
-        <v>22372.33522476559</v>
+        <v>22398.89970756142</v>
       </c>
       <c r="E7">
         <v>-8687.335000000001</v>
@@ -1867,37 +1867,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M7">
-        <v>65.21257050000001</v>
+        <v>63.44665950000001</v>
       </c>
       <c r="N7">
-        <v>805.2874294999998</v>
+        <v>807.0533404999998</v>
       </c>
       <c r="O7">
-        <v>177.16323449</v>
+        <v>177.5517349099999</v>
       </c>
       <c r="P7">
-        <v>628.1241950099999</v>
+        <v>629.5016055899998</v>
       </c>
       <c r="Q7">
-        <v>2220.32419501</v>
+        <v>2221.70160559</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06983047438140991</v>
+        <v>0.06981502492294489</v>
       </c>
       <c r="T7">
         <v>0.5546195132319837</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.34865338577628</v>
+        <v>13.72018648200067</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06824972836561831</v>
+        <v>0.06816956402857828</v>
       </c>
       <c r="C8">
-        <v>22491.98295879487</v>
+        <v>22523.8919343762</v>
       </c>
       <c r="D8">
-        <v>22422.72095879487</v>
+        <v>22454.6299343762</v>
       </c>
       <c r="E8">
         <v>-8435.062</v>
@@ -1949,37 +1949,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M8">
-        <v>78.25508460000002</v>
+        <v>76.13599140000001</v>
       </c>
       <c r="N8">
-        <v>792.2449153999997</v>
+        <v>794.3640085999998</v>
       </c>
       <c r="O8">
-        <v>174.2938813879999</v>
+        <v>174.760081892</v>
       </c>
       <c r="P8">
-        <v>617.9510340119998</v>
+        <v>619.6039267079998</v>
       </c>
       <c r="Q8">
-        <v>2210.151034012</v>
+        <v>2211.803926708</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07003209400597693</v>
+        <v>0.07001651492401945</v>
       </c>
       <c r="T8">
         <v>0.5592728619865922</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.12387782148024</v>
+        <v>11.43348873500056</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06814420606889723</v>
+        <v>0.0680531543803589</v>
       </c>
       <c r="C9">
-        <v>22290.32315702432</v>
+        <v>22327.62717530026</v>
       </c>
       <c r="D9">
-        <v>22473.33415702432</v>
+        <v>22510.63817530026</v>
       </c>
       <c r="E9">
         <v>-8182.789000000001</v>
@@ -2031,37 +2031,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M9">
-        <v>91.29759870000002</v>
+        <v>88.82532330000001</v>
       </c>
       <c r="N9">
-        <v>779.2024012999998</v>
+        <v>781.6746766999997</v>
       </c>
       <c r="O9">
-        <v>171.424528286</v>
+        <v>171.968428874</v>
       </c>
       <c r="P9">
-        <v>607.7778730139999</v>
+        <v>609.7062478259998</v>
       </c>
       <c r="Q9">
-        <v>2199.977873014</v>
+        <v>2201.906247826</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07023804953644865</v>
+        <v>0.07022233804339667</v>
       </c>
       <c r="T9">
         <v>0.5640262827574291</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.534752418411632</v>
+        <v>9.800133201429054</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06810732377217617</v>
+        <v>0.06803034473213955</v>
       </c>
       <c r="C10">
-        <v>22055.79448156422</v>
+        <v>22086.36134739576</v>
       </c>
       <c r="D10">
-        <v>22491.07848156422</v>
+        <v>22521.64534739576</v>
       </c>
       <c r="E10">
         <v>-7930.516000000001</v>
@@ -2113,37 +2113,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M10">
-        <v>106.5601152</v>
+        <v>104.5419312</v>
       </c>
       <c r="N10">
-        <v>763.9398847999997</v>
+        <v>765.9580687999998</v>
       </c>
       <c r="O10">
-        <v>168.066774656</v>
+        <v>168.5107751359999</v>
       </c>
       <c r="P10">
-        <v>595.8731101439998</v>
+        <v>597.4472936639997</v>
       </c>
       <c r="Q10">
-        <v>2188.073110144</v>
+        <v>2189.647293664</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07044848236106105</v>
+        <v>0.07043263557841255</v>
       </c>
       <c r="T10">
         <v>0.5688830387624144</v>
       </c>
       <c r="U10">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.169097775149549</v>
+        <v>8.326802365403402</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06801038147545509</v>
+        <v>0.06792563508392019</v>
       </c>
       <c r="C11">
-        <v>21850.29497760852</v>
+        <v>21884.75615691423</v>
       </c>
       <c r="D11">
-        <v>22537.85197760851</v>
+        <v>22572.31315691422</v>
       </c>
       <c r="E11">
         <v>-7678.243</v>
@@ -2195,37 +2195,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M11">
-        <v>119.8801296</v>
+        <v>117.6096726</v>
       </c>
       <c r="N11">
-        <v>750.6198703999997</v>
+        <v>752.8903273999997</v>
       </c>
       <c r="O11">
-        <v>165.136371488</v>
+        <v>165.6358720279999</v>
       </c>
       <c r="P11">
-        <v>585.4834989119997</v>
+        <v>587.2544553719997</v>
       </c>
       <c r="Q11">
-        <v>2177.683498912</v>
+        <v>2179.454455372</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07066354008291768</v>
+        <v>0.07064755503727492</v>
       </c>
       <c r="T11">
         <v>0.5738465366576193</v>
       </c>
       <c r="U11">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.261420244577377</v>
+        <v>7.401602102580801</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06808503917873401</v>
+        <v>0.06795352543570081</v>
       </c>
       <c r="C12">
-        <v>21561.98333793735</v>
+        <v>21618.96507093231</v>
       </c>
       <c r="D12">
-        <v>22501.81333793735</v>
+        <v>22558.7950709323</v>
       </c>
       <c r="E12">
         <v>-7425.97</v>
@@ -2277,37 +2277,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M12">
-        <v>138.75015</v>
+        <v>134.966055</v>
       </c>
       <c r="N12">
-        <v>731.7498499999997</v>
+        <v>735.5339449999998</v>
       </c>
       <c r="O12">
-        <v>160.9849669999999</v>
+        <v>161.8174679</v>
       </c>
       <c r="P12">
-        <v>570.7648829999998</v>
+        <v>573.7164770999998</v>
       </c>
       <c r="Q12">
-        <v>2162.964883</v>
+        <v>2165.9164771</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07088337686526001</v>
+        <v>0.07086725048411201</v>
       </c>
       <c r="T12">
         <v>0.578920334506051</v>
       </c>
       <c r="U12">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.273867091314854</v>
+        <v>6.449769906959196</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06800525688201293</v>
+        <v>0.06786207578748145</v>
       </c>
       <c r="C13">
-        <v>21348.2269469677</v>
+        <v>21411.0771226935</v>
       </c>
       <c r="D13">
-        <v>22540.3299469677</v>
+        <v>22603.1801226935</v>
       </c>
       <c r="E13">
         <v>-7173.697</v>
@@ -2359,37 +2359,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M13">
-        <v>152.625165</v>
+        <v>148.4626605</v>
       </c>
       <c r="N13">
-        <v>717.8748349999997</v>
+        <v>722.0373394999998</v>
       </c>
       <c r="O13">
-        <v>157.9324636999999</v>
+        <v>158.84821469</v>
       </c>
       <c r="P13">
-        <v>559.9423712999998</v>
+        <v>563.1891248099998</v>
       </c>
       <c r="Q13">
-        <v>2152.1423713</v>
+        <v>2155.38912481</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07110815380001453</v>
+        <v>0.07109188290728252</v>
       </c>
       <c r="T13">
         <v>0.5841081502836609</v>
       </c>
       <c r="U13">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.703515537558959</v>
+        <v>5.863427188144724</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06806587458529184</v>
+        <v>0.06784550613926207</v>
       </c>
       <c r="C14">
-        <v>21066.67743793781</v>
+        <v>21166.86489172902</v>
       </c>
       <c r="D14">
-        <v>22511.05343793781</v>
+        <v>22611.24089172902</v>
       </c>
       <c r="E14">
         <v>-6921.424000000001</v>
@@ -2441,37 +2441,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M14">
-        <v>171.041094</v>
+        <v>164.3810868</v>
       </c>
       <c r="N14">
-        <v>699.4589059999997</v>
+        <v>706.1189131999997</v>
       </c>
       <c r="O14">
-        <v>153.8809593199999</v>
+        <v>155.3461609039999</v>
       </c>
       <c r="P14">
-        <v>545.5779466799997</v>
+        <v>550.7727522959998</v>
       </c>
       <c r="Q14">
-        <v>2137.77794668</v>
+        <v>2142.972752296</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07133803930146801</v>
+        <v>0.07132162061279781</v>
       </c>
       <c r="T14">
         <v>0.5894138709653074</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.089420206818835</v>
+        <v>5.295621393835435</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06799779228857078</v>
+        <v>0.0677602964910427</v>
       </c>
       <c r="C15">
-        <v>20847.29138569868</v>
+        <v>20956.13548032788</v>
       </c>
       <c r="D15">
-        <v>22543.94038569868</v>
+        <v>22652.78448032788</v>
       </c>
       <c r="E15">
         <v>-6669.151</v>
@@ -2523,37 +2523,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M15">
-        <v>185.2945185</v>
+        <v>178.0795107</v>
       </c>
       <c r="N15">
-        <v>685.2054814999997</v>
+        <v>692.4204892999998</v>
       </c>
       <c r="O15">
-        <v>150.7452059299999</v>
+        <v>152.332507646</v>
       </c>
       <c r="P15">
-        <v>534.4602755699998</v>
+        <v>540.0879816539998</v>
       </c>
       <c r="Q15">
-        <v>2126.66027557</v>
+        <v>2132.287981654</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07157320952709284</v>
+        <v>0.07155663964487667</v>
       </c>
       <c r="T15">
         <v>0.5948415622373364</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.697926344755846</v>
+        <v>4.88826590200194</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06792970999184969</v>
+        <v>0.06767508684282333</v>
       </c>
       <c r="C16">
-        <v>20628.00156473657</v>
+        <v>20745.55900582532</v>
       </c>
       <c r="D16">
-        <v>22576.92356473657</v>
+        <v>22694.48100582532</v>
       </c>
       <c r="E16">
         <v>-6416.878000000001</v>
@@ -2605,37 +2605,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M16">
-        <v>199.547943</v>
+        <v>191.7779346</v>
       </c>
       <c r="N16">
-        <v>670.9520569999997</v>
+        <v>678.7220653999998</v>
       </c>
       <c r="O16">
-        <v>147.6094525399999</v>
+        <v>149.3188543879999</v>
       </c>
       <c r="P16">
-        <v>523.3426044599998</v>
+        <v>529.4032110119998</v>
       </c>
       <c r="Q16">
-        <v>2115.54260446</v>
+        <v>2121.603211012</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0718138488277322</v>
+        <v>0.07179712423584109</v>
       </c>
       <c r="T16">
         <v>0.6003954788877849</v>
       </c>
       <c r="U16">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.362360177273287</v>
+        <v>4.539104051858944</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06802542769512862</v>
+        <v>0.06770687719460397</v>
       </c>
       <c r="C17">
-        <v>20329.38460690095</v>
+        <v>20477.71176265923</v>
       </c>
       <c r="D17">
-        <v>22530.57960690095</v>
+        <v>22678.90676265923</v>
       </c>
       <c r="E17">
         <v>-6164.605</v>
@@ -2687,37 +2687,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M17">
-        <v>219.0991005</v>
+        <v>209.2604535</v>
       </c>
       <c r="N17">
-        <v>651.4008994999997</v>
+        <v>661.2395464999997</v>
       </c>
       <c r="O17">
-        <v>143.3081978899999</v>
+        <v>145.4727002299999</v>
       </c>
       <c r="P17">
-        <v>508.0927016099997</v>
+        <v>515.7668462699999</v>
       </c>
       <c r="Q17">
-        <v>2100.29270161</v>
+        <v>2107.96684627</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07206015022956308</v>
+        <v>0.07204326728776937</v>
       </c>
       <c r="T17">
         <v>0.6060800759300086</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.973087968017466</v>
+        <v>4.159887763982121</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06796826539840754</v>
+        <v>0.06762946754638459</v>
       </c>
       <c r="C18">
-        <v>20104.76515359287</v>
+        <v>20263.39952288748</v>
       </c>
       <c r="D18">
-        <v>22558.23315359288</v>
+        <v>22716.86752288748</v>
       </c>
       <c r="E18">
         <v>-5912.332</v>
@@ -2769,37 +2769,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M18">
-        <v>233.7057072</v>
+        <v>223.2111504</v>
       </c>
       <c r="N18">
-        <v>636.7942927999998</v>
+        <v>647.2888495999997</v>
       </c>
       <c r="O18">
-        <v>140.0947444159999</v>
+        <v>142.4035469119999</v>
       </c>
       <c r="P18">
-        <v>496.6995483839999</v>
+        <v>504.8853026879998</v>
       </c>
       <c r="Q18">
-        <v>2088.899548384</v>
+        <v>2097.085302688</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07231231595048516</v>
+        <v>0.07229527088855309</v>
       </c>
       <c r="T18">
         <v>0.6119000205208567</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.724769970016375</v>
+        <v>3.899894778733239</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06791110310168647</v>
+        <v>0.06755205789816522</v>
       </c>
       <c r="C19">
-        <v>19880.21366643663</v>
+        <v>20049.21457632308</v>
       </c>
       <c r="D19">
-        <v>22585.95466643663</v>
+        <v>22754.95557632307</v>
       </c>
       <c r="E19">
         <v>-5660.059</v>
@@ -2851,37 +2851,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M19">
-        <v>248.3123139</v>
+        <v>237.1618473</v>
       </c>
       <c r="N19">
-        <v>622.1876860999997</v>
+        <v>633.3381526999997</v>
       </c>
       <c r="O19">
-        <v>136.8812909419999</v>
+        <v>139.3343935939999</v>
       </c>
       <c r="P19">
-        <v>485.3063951579998</v>
+        <v>494.0037591059997</v>
       </c>
       <c r="Q19">
-        <v>2077.506395158</v>
+        <v>2086.203759106</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07257055795383911</v>
+        <v>0.07255334686525931</v>
       </c>
       <c r="T19">
         <v>0.6178602047403999</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.505665854133059</v>
+        <v>3.670489203513636</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06785394080496537</v>
+        <v>0.06747464824994587</v>
       </c>
       <c r="C20">
-        <v>19655.73039630863</v>
+        <v>19835.15756431674</v>
       </c>
       <c r="D20">
-        <v>22613.74439630863</v>
+        <v>22793.17156431674</v>
       </c>
       <c r="E20">
         <v>-5407.786</v>
@@ -2933,37 +2933,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M20">
-        <v>262.9189206</v>
+        <v>251.1125442000001</v>
       </c>
       <c r="N20">
-        <v>607.5810793999997</v>
+        <v>619.3874557999998</v>
       </c>
       <c r="O20">
-        <v>133.6678374679999</v>
+        <v>136.265240276</v>
       </c>
       <c r="P20">
-        <v>473.9132419319998</v>
+        <v>483.1222155239998</v>
       </c>
       <c r="Q20">
-        <v>2066.113241932</v>
+        <v>2075.322215524</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0728350985426407</v>
+        <v>0.07281771737798276</v>
       </c>
       <c r="T20">
         <v>0.6239657593067611</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.310906640014555</v>
+        <v>3.466573136651768</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0677967785082443</v>
+        <v>0.0673972386017265</v>
       </c>
       <c r="C21">
-        <v>19431.31559532148</v>
+        <v>19621.22913253493</v>
       </c>
       <c r="D21">
-        <v>22641.60259532148</v>
+        <v>22831.51613253493</v>
       </c>
       <c r="E21">
         <v>-5155.513</v>
@@ -3015,37 +3015,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M21">
-        <v>277.5255273</v>
+        <v>265.0632411</v>
       </c>
       <c r="N21">
-        <v>592.9744726999998</v>
+        <v>605.4367588999997</v>
       </c>
       <c r="O21">
-        <v>130.454383994</v>
+        <v>133.1960869579999</v>
       </c>
       <c r="P21">
-        <v>462.5200887059998</v>
+        <v>472.2406719419998</v>
       </c>
       <c r="Q21">
-        <v>2054.720088706</v>
+        <v>2064.440671942</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07310617099783247</v>
+        <v>0.07308861555768703</v>
       </c>
       <c r="T21">
         <v>0.6302220683068598</v>
       </c>
       <c r="U21">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.136648395803263</v>
+        <v>3.284121918933254</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06814521621152322</v>
+        <v>0.06731982895350712</v>
       </c>
       <c r="C22">
-        <v>19010.28856442788</v>
+        <v>19407.42993099619</v>
       </c>
       <c r="D22">
-        <v>22472.84856442788</v>
+        <v>22869.98993099619</v>
       </c>
       <c r="E22">
         <v>-4903.24</v>
@@ -3097,45 +3097,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M22">
-        <v>305.2503300000001</v>
+        <v>279.0139380000001</v>
       </c>
       <c r="N22">
-        <v>565.2496699999997</v>
+        <v>591.4860619999997</v>
       </c>
       <c r="O22">
-        <v>124.3549273999999</v>
+        <v>130.1269336399999</v>
       </c>
       <c r="P22">
-        <v>440.8947425999997</v>
+        <v>461.3591283599998</v>
       </c>
       <c r="Q22">
-        <v>2033.0947426</v>
+        <v>2053.55912836</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07338402026440402</v>
+        <v>0.0733662861918839</v>
       </c>
       <c r="T22">
         <v>0.6366347850319609</v>
       </c>
       <c r="U22">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04719</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.851757768779478</v>
+        <v>3.119915822986591</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06810833391480214</v>
+        <v>0.06765191930528776</v>
       </c>
       <c r="C23">
-        <v>18775.75912185233</v>
+        <v>18991.01137284978</v>
       </c>
       <c r="D23">
-        <v>22490.59212185233</v>
+        <v>22705.84437284978</v>
       </c>
       <c r="E23">
         <v>-4650.967000000001</v>
@@ -3179,37 +3179,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M23">
-        <v>320.5128465</v>
+        <v>306.2089674</v>
       </c>
       <c r="N23">
-        <v>549.9871534999997</v>
+        <v>564.2910325999998</v>
       </c>
       <c r="O23">
-        <v>120.9971737699999</v>
+        <v>124.144027172</v>
       </c>
       <c r="P23">
-        <v>428.9899797299998</v>
+        <v>440.1470054279998</v>
       </c>
       <c r="Q23">
-        <v>2021.18997973</v>
+        <v>2032.347005428</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07366890368962296</v>
+        <v>0.07365098646238956</v>
       </c>
       <c r="T23">
         <v>0.6432098490159253</v>
       </c>
       <c r="U23">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.71595977978998</v>
+        <v>2.842829873309581</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06807145161808106</v>
+        <v>0.0675940096570684</v>
       </c>
       <c r="C24">
-        <v>18541.25772045761</v>
+        <v>18767.19211428922</v>
       </c>
       <c r="D24">
-        <v>22508.36372045761</v>
+        <v>22734.29811428922</v>
       </c>
       <c r="E24">
         <v>-4398.694</v>
@@ -3261,37 +3261,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M24">
-        <v>335.775363</v>
+        <v>320.7903468000001</v>
       </c>
       <c r="N24">
-        <v>534.7246369999998</v>
+        <v>549.7096531999997</v>
       </c>
       <c r="O24">
-        <v>117.63942014</v>
+        <v>120.9361237039999</v>
       </c>
       <c r="P24">
-        <v>417.0852168599998</v>
+        <v>428.7735294959998</v>
       </c>
       <c r="Q24">
-        <v>2009.28521686</v>
+        <v>2020.973529496</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07396109181805265</v>
+        <v>0.07394298673983127</v>
       </c>
       <c r="T24">
         <v>0.6499535043840939</v>
       </c>
       <c r="U24">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.592507062526799</v>
+        <v>2.713610333613691</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06851894932135999</v>
+        <v>0.06753610000884902</v>
       </c>
       <c r="C25">
-        <v>18075.23848003551</v>
+        <v>18543.44425859992</v>
       </c>
       <c r="D25">
-        <v>22294.61748003551</v>
+        <v>22762.82325859992</v>
       </c>
       <c r="E25">
         <v>-4146.420999999999</v>
@@ -3343,45 +3343,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M25">
-        <v>366.7040328000001</v>
+        <v>335.3717262000001</v>
       </c>
       <c r="N25">
-        <v>503.7959671999997</v>
+        <v>535.1282737999996</v>
       </c>
       <c r="O25">
-        <v>110.8351127839999</v>
+        <v>117.7282202359999</v>
       </c>
       <c r="P25">
-        <v>392.9608544159997</v>
+        <v>417.4000535639997</v>
       </c>
       <c r="Q25">
-        <v>1985.160854416</v>
+        <v>2009.600053564</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07426086924851946</v>
+        <v>0.07424257144006366</v>
       </c>
       <c r="T25">
         <v>0.6568723196319554</v>
       </c>
       <c r="U25">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04929600000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.373848995750667</v>
+        <v>2.595627275630487</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06850312702463891</v>
+        <v>0.06813339036062967</v>
       </c>
       <c r="C26">
-        <v>17830.45370950111</v>
+        <v>18000.35232198335</v>
       </c>
       <c r="D26">
-        <v>22302.10570950111</v>
+        <v>22472.00432198335</v>
       </c>
       <c r="E26">
         <v>-3894.148</v>
@@ -3425,37 +3425,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M26">
-        <v>382.6476864000001</v>
+        <v>371.1440376</v>
       </c>
       <c r="N26">
-        <v>487.8523135999997</v>
+        <v>499.3559623999997</v>
       </c>
       <c r="O26">
-        <v>107.3275089919999</v>
+        <v>109.8583117279999</v>
       </c>
       <c r="P26">
-        <v>380.5248046079998</v>
+        <v>389.4976506719998</v>
       </c>
       <c r="Q26">
-        <v>1972.724804608</v>
+        <v>1981.697650672</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07456853555873541</v>
+        <v>0.07455003994819692</v>
       </c>
       <c r="T26">
         <v>0.6639732089652868</v>
       </c>
       <c r="U26">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04929600000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.274938620927722</v>
+        <v>2.345450584708517</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06940380472791784</v>
+        <v>0.0681027807124103</v>
       </c>
       <c r="C27">
-        <v>17159.77296171874</v>
+        <v>17762.80229946779</v>
       </c>
       <c r="D27">
-        <v>21883.69796171874</v>
+        <v>22486.72729946779</v>
       </c>
       <c r="E27">
         <v>-3641.875</v>
@@ -3507,45 +3507,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M27">
-        <v>428.2334175000001</v>
+        <v>386.6083725</v>
       </c>
       <c r="N27">
-        <v>442.2665824999997</v>
+        <v>483.8916274999997</v>
       </c>
       <c r="O27">
-        <v>97.29864814999993</v>
+        <v>106.4561580499999</v>
       </c>
       <c r="P27">
-        <v>344.9679343499997</v>
+        <v>377.4354694499998</v>
       </c>
       <c r="Q27">
-        <v>1937.16793435</v>
+        <v>1969.63546945</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07488440630389044</v>
+        <v>0.07486570761654705</v>
       </c>
       <c r="T27">
         <v>0.671263455347507</v>
       </c>
       <c r="U27">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.052962</v>
+        <v>0.047814</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.032769897038686</v>
+        <v>2.251632561320176</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07226384243119675</v>
+        <v>0.06864001106419092</v>
       </c>
       <c r="C28">
-        <v>15677.1018796341</v>
+        <v>17254.89631998807</v>
       </c>
       <c r="D28">
-        <v>20653.2998796341</v>
+        <v>22231.09431998807</v>
       </c>
       <c r="E28">
         <v>-3389.602</v>
@@ -3589,45 +3589,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M28">
-        <v>537.1901262000001</v>
+        <v>420.4381818000001</v>
       </c>
       <c r="N28">
-        <v>333.3098737999997</v>
+        <v>450.0618181999997</v>
       </c>
       <c r="O28">
-        <v>73.32817223599993</v>
+        <v>99.01360000399993</v>
       </c>
       <c r="P28">
-        <v>259.9817015639997</v>
+        <v>351.0482181959998</v>
       </c>
       <c r="Q28">
-        <v>1852.181701564</v>
+        <v>1943.248218196</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07520881409621183</v>
+        <v>0.07518990684350124</v>
       </c>
       <c r="T28">
         <v>0.6787507354157332</v>
       </c>
       <c r="U28">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.06388200000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.620469099381595</v>
+        <v>2.070458958492241</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07239388013447567</v>
+        <v>0.07027392141597155</v>
       </c>
       <c r="C29">
-        <v>15372.16617995486</v>
+        <v>16259.67722690394</v>
       </c>
       <c r="D29">
-        <v>20600.63717995486</v>
+        <v>21488.14822690394</v>
       </c>
       <c r="E29">
         <v>-3137.329</v>
@@ -3671,45 +3671,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M29">
-        <v>557.8512849000001</v>
+        <v>489.7375749000001</v>
       </c>
       <c r="N29">
-        <v>312.6487150999997</v>
+        <v>380.7624250999997</v>
       </c>
       <c r="O29">
-        <v>68.78271732199993</v>
+        <v>83.76773352199993</v>
       </c>
       <c r="P29">
-        <v>243.8659977779997</v>
+        <v>296.9946915779998</v>
       </c>
       <c r="Q29">
-        <v>1836.065997778</v>
+        <v>1889.194691578</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07554210977325435</v>
+        <v>0.07552298824105692</v>
       </c>
       <c r="T29">
         <v>0.6864431464447326</v>
       </c>
       <c r="U29">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.06388200000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.560451725330425</v>
+        <v>1.777482563345783</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0725239178377546</v>
+        <v>0.07117775176775218</v>
       </c>
       <c r="C30">
-        <v>15067.49836059529</v>
+        <v>15617.37346177428</v>
       </c>
       <c r="D30">
-        <v>20548.24236059529</v>
+        <v>21098.11746177428</v>
       </c>
       <c r="E30">
         <v>-2885.056</v>
@@ -3753,37 +3753,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M30">
-        <v>578.5124436000001</v>
+        <v>535.4242152000002</v>
       </c>
       <c r="N30">
-        <v>291.9875563999997</v>
+        <v>335.0757847999996</v>
       </c>
       <c r="O30">
-        <v>64.23726240799994</v>
+        <v>73.71667265599991</v>
       </c>
       <c r="P30">
-        <v>227.7502939919997</v>
+        <v>261.3591121439997</v>
       </c>
       <c r="Q30">
-        <v>1819.950293992</v>
+        <v>1853.559112144</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07588466366354805</v>
+        <v>0.07586532189965581</v>
       </c>
       <c r="T30">
         <v>0.694349235557871</v>
       </c>
       <c r="U30">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.06388200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.504721306568624</v>
+        <v>1.625813654458711</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08463182170402625</v>
+        <v>0.07126024211953282</v>
       </c>
       <c r="C31">
-        <v>10880.8331121399</v>
+        <v>15330.20724893166</v>
       </c>
       <c r="D31">
-        <v>16613.8501121399</v>
+        <v>21063.22424893166</v>
       </c>
       <c r="E31">
         <v>-2632.783</v>
@@ -3835,45 +3835,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M31">
-        <v>957.6535352999999</v>
+        <v>554.5465086</v>
       </c>
       <c r="N31">
-        <v>-87.15353530000016</v>
+        <v>315.9534913999997</v>
       </c>
       <c r="O31">
-        <v>-19.17377776600004</v>
+        <v>69.50976810799995</v>
       </c>
       <c r="P31">
-        <v>-67.97975753400013</v>
+        <v>246.4437232919998</v>
       </c>
       <c r="Q31">
-        <v>1524.220242466</v>
+        <v>1838.643723292</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07642563504861581</v>
+        <v>0.07621729875990538</v>
       </c>
       <c r="T31">
-        <v>0.7068347687810861</v>
+        <v>0.7024780314065907</v>
       </c>
       <c r="U31">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
-        <v>0.1999783772948809</v>
+        <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.1047228304121001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.9089926240676406</v>
+        <v>1.569751114649791</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08548282170402624</v>
+        <v>0.07134273247131345</v>
       </c>
       <c r="C32">
-        <v>10407.9485193889</v>
+        <v>15043.15626210403</v>
       </c>
       <c r="D32">
-        <v>16393.2385193889</v>
+        <v>21028.44626210403</v>
       </c>
       <c r="E32">
         <v>-2380.51</v>
@@ -3917,45 +3917,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M32">
-        <v>990.676071</v>
+        <v>573.6688020000001</v>
       </c>
       <c r="N32">
-        <v>-120.1760710000002</v>
+        <v>296.8311979999996</v>
       </c>
       <c r="O32">
-        <v>-26.43873562000005</v>
+        <v>65.30286355999992</v>
       </c>
       <c r="P32">
-        <v>-93.73733538000016</v>
+        <v>231.5283344399997</v>
       </c>
       <c r="Q32">
-        <v>1498.46266462</v>
+        <v>1823.72833444</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0768631441207389</v>
+        <v>0.07657933210187635</v>
       </c>
       <c r="T32">
-        <v>0.7169324083351016</v>
+        <v>0.7108390785652737</v>
       </c>
       <c r="U32">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
-        <v>0.1933124313850516</v>
+        <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.1055954027316967</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8786928699320524</v>
+        <v>1.517426077494797</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08633382170402625</v>
+        <v>0.08236809888139497</v>
       </c>
       <c r="C33">
-        <v>9940.846050914795</v>
+        <v>10989.21999937774</v>
       </c>
       <c r="D33">
-        <v>16178.40905091479</v>
+        <v>17226.78299937774</v>
       </c>
       <c r="E33">
         <v>-2128.237</v>
@@ -3999,37 +3999,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M33">
-        <v>1023.6986067</v>
+        <v>927.5069118000001</v>
       </c>
       <c r="N33">
-        <v>-153.1986067000003</v>
+        <v>-57.00691180000035</v>
       </c>
       <c r="O33">
-        <v>-33.70369347400005</v>
+        <v>-12.54152059600008</v>
       </c>
       <c r="P33">
-        <v>-119.4949132260002</v>
+        <v>-44.46539120400028</v>
       </c>
       <c r="Q33">
-        <v>1472.705086774</v>
+        <v>1547.734608796</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07731333461524237</v>
+        <v>0.07709199719113904</v>
       </c>
       <c r="T33">
-        <v>0.7273227330935814</v>
+        <v>0.7226789189639501</v>
       </c>
       <c r="U33">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1870765465016628</v>
+        <v>0.2064782456751067</v>
       </c>
       <c r="W33">
-        <v>0.1064116800629323</v>
+        <v>0.09411168006293236</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8503479386439217</v>
+        <v>0.9385374803413941</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08718482170402625</v>
+        <v>0.08309609888139496</v>
       </c>
       <c r="C34">
-        <v>9479.301327093293</v>
+        <v>10533.73216714093</v>
       </c>
       <c r="D34">
-        <v>15969.13732709329</v>
+        <v>17023.56816714093</v>
       </c>
       <c r="E34">
         <v>-1875.964</v>
@@ -4081,37 +4081,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M34">
-        <v>1056.7211424</v>
+        <v>957.4264896000002</v>
       </c>
       <c r="N34">
-        <v>-186.2211424000002</v>
+        <v>-86.92648960000042</v>
       </c>
       <c r="O34">
-        <v>-40.96865132800004</v>
+        <v>-19.12382771200009</v>
       </c>
       <c r="P34">
-        <v>-145.2524910720001</v>
+        <v>-67.80266188800033</v>
       </c>
       <c r="Q34">
-        <v>1446.947508928</v>
+        <v>1524.397338112</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07777676600664299</v>
+        <v>0.07755217362042049</v>
       </c>
       <c r="T34">
-        <v>0.7380186556390752</v>
+        <v>0.7333065501251846</v>
       </c>
       <c r="U34">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1812304044234858</v>
+        <v>0.2000258004977596</v>
       </c>
       <c r="W34">
-        <v>0.1071769400609657</v>
+        <v>0.09487694006096571</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8237745655612992</v>
+        <v>0.9092081840807255</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1165794775941801</v>
+        <v>0.08382409888139497</v>
       </c>
       <c r="C35">
-        <v>4295.444796105956</v>
+        <v>10082.98286309441</v>
       </c>
       <c r="D35">
-        <v>11037.55379610596</v>
+        <v>16825.09186309441</v>
       </c>
       <c r="E35">
         <v>-1623.690999999999</v>
@@ -4163,45 +4163,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M35">
-        <v>1796.536942200001</v>
+        <v>987.3460674000003</v>
       </c>
       <c r="N35">
-        <v>-926.0369422000008</v>
+        <v>-116.8460674000005</v>
       </c>
       <c r="O35">
-        <v>-203.7281272840002</v>
+        <v>-25.70613482800011</v>
       </c>
       <c r="P35">
-        <v>-722.3088149160006</v>
+        <v>-91.13993257200039</v>
       </c>
       <c r="Q35">
-        <v>869.8911850839994</v>
+        <v>1501.060067428</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07904008473831503</v>
+        <v>0.07802608665953126</v>
       </c>
       <c r="T35">
-        <v>0.7671758503284501</v>
+        <v>0.7442514240076502</v>
       </c>
       <c r="U35">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1065995335255845</v>
+        <v>0.1939644126038881</v>
       </c>
       <c r="W35">
-        <v>0.1927958206651789</v>
+        <v>0.09559582066517888</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.4845433342072021</v>
+        <v>0.881656420926764</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1182794775941801</v>
+        <v>0.08455209888139496</v>
       </c>
       <c r="C36">
-        <v>3849.498299329431</v>
+        <v>9636.808259030107</v>
       </c>
       <c r="D36">
-        <v>10843.88029932943</v>
+        <v>16631.19025903011</v>
       </c>
       <c r="E36">
         <v>-1371.418</v>
@@ -4245,45 +4245,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M36">
-        <v>1850.9774556</v>
+        <v>1017.2656452</v>
       </c>
       <c r="N36">
-        <v>-980.4774556000007</v>
+        <v>-146.7656452000004</v>
       </c>
       <c r="O36">
-        <v>-215.7050402320002</v>
+        <v>-32.2884419440001</v>
       </c>
       <c r="P36">
-        <v>-764.7724153680006</v>
+        <v>-114.4772032560004</v>
       </c>
       <c r="Q36">
-        <v>827.4275846319995</v>
+        <v>1477.722796744</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07954372238586527</v>
+        <v>0.07851436069982717</v>
       </c>
       <c r="T36">
-        <v>0.7787997268485781</v>
+        <v>0.7555279607350388</v>
       </c>
       <c r="U36">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.1034642531277732</v>
+        <v>0.1882595769390679</v>
       </c>
       <c r="W36">
-        <v>0.1934724141750266</v>
+        <v>0.09627241417502656</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.4702920596716962</v>
+        <v>0.8557253497230357</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1199794775941801</v>
+        <v>0.08528009888139496</v>
       </c>
       <c r="C37">
-        <v>3410.231290444202</v>
+        <v>9195.051992881175</v>
       </c>
       <c r="D37">
-        <v>10656.8862904442</v>
+        <v>16441.70699288118</v>
       </c>
       <c r="E37">
         <v>-1119.144999999999</v>
@@ -4327,45 +4327,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M37">
-        <v>1905.417969000001</v>
+        <v>1047.185223</v>
       </c>
       <c r="N37">
-        <v>-1034.917969000001</v>
+        <v>-176.6852230000006</v>
       </c>
       <c r="O37">
-        <v>-227.6819531800002</v>
+        <v>-38.87074906000014</v>
       </c>
       <c r="P37">
-        <v>-807.2360158200006</v>
+        <v>-137.8144739400005</v>
       </c>
       <c r="Q37">
-        <v>784.9639841799994</v>
+        <v>1454.38552606</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08006285657641704</v>
+        <v>0.0790176585567476</v>
       </c>
       <c r="T37">
-        <v>0.7907812611077871</v>
+        <v>0.7671514678232702</v>
       </c>
       <c r="U37">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.1005081316098368</v>
+        <v>0.1828807318836659</v>
       </c>
       <c r="W37">
-        <v>0.1941103451985972</v>
+        <v>0.09691034519859723</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.4568551436810763</v>
+        <v>0.8312760540166632</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1216794775941801</v>
+        <v>0.08600809888139496</v>
       </c>
       <c r="C38">
-        <v>2977.304079907131</v>
+        <v>8757.564748195233</v>
       </c>
       <c r="D38">
-        <v>10476.23207990713</v>
+        <v>16256.49274819523</v>
       </c>
       <c r="E38">
         <v>-866.8719999999994</v>
@@ -4409,45 +4409,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M38">
-        <v>1959.8584824</v>
+        <v>1077.1048008</v>
       </c>
       <c r="N38">
-        <v>-1089.358482400001</v>
+        <v>-206.6048008000005</v>
       </c>
       <c r="O38">
-        <v>-239.6588661280001</v>
+        <v>-45.4530561760001</v>
       </c>
       <c r="P38">
-        <v>-849.6996162720005</v>
+        <v>-161.1517446240004</v>
       </c>
       <c r="Q38">
-        <v>742.5003837279995</v>
+        <v>1431.048255376</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08059821371042356</v>
+        <v>0.07953668447169678</v>
       </c>
       <c r="T38">
-        <v>0.8031372183125961</v>
+        <v>0.7791382095080087</v>
       </c>
       <c r="U38">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.0977162390651191</v>
+        <v>0.1778007115535641</v>
       </c>
       <c r="W38">
-        <v>0.1947128356097473</v>
+        <v>0.09751283560974731</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.4441647230232686</v>
+        <v>0.8081850525162004</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1233794775941801</v>
+        <v>0.1177545406391833</v>
       </c>
       <c r="C39">
-        <v>2550.399627722261</v>
+        <v>3150.145793298043</v>
       </c>
       <c r="D39">
-        <v>10301.60062772226</v>
+        <v>10901.34679329804</v>
       </c>
       <c r="E39">
         <v>-614.5990000000002</v>
@@ -4491,37 +4491,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M39">
-        <v>2014.2989958</v>
+        <v>1874.2874808</v>
       </c>
       <c r="N39">
-        <v>-1143.798995800001</v>
+        <v>-1003.7874808</v>
       </c>
       <c r="O39">
-        <v>-251.6357790760001</v>
+        <v>-220.8332457760001</v>
       </c>
       <c r="P39">
-        <v>-892.1632167240004</v>
+        <v>-782.9542350240004</v>
       </c>
       <c r="Q39">
-        <v>700.0367832759996</v>
+        <v>809.2457649759997</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08115056630900169</v>
+        <v>0.08103161876138777</v>
       </c>
       <c r="T39">
-        <v>0.8158854281270818</v>
+        <v>0.8136632508403643</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.0950752596309267</v>
+        <v>0.1021774951611254</v>
       </c>
       <c r="W39">
-        <v>0.195282758971646</v>
+        <v>0.180282758971646</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4321602710496668</v>
+        <v>0.4644431598232973</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1250794775941801</v>
+        <v>0.1193045406391833</v>
       </c>
       <c r="C40">
-        <v>2129.221686632061</v>
+        <v>2725.31608463108</v>
       </c>
       <c r="D40">
-        <v>10132.69568663206</v>
+        <v>10728.79008463108</v>
       </c>
       <c r="E40">
         <v>-362.3259999999991</v>
@@ -4573,37 +4573,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M40">
-        <v>2068.739509200001</v>
+        <v>1924.9438992</v>
       </c>
       <c r="N40">
-        <v>-1198.239509200001</v>
+        <v>-1054.443899200001</v>
       </c>
       <c r="O40">
-        <v>-263.6126920240002</v>
+        <v>-231.9776578240001</v>
       </c>
       <c r="P40">
-        <v>-934.6268171760007</v>
+        <v>-822.4662413760005</v>
       </c>
       <c r="Q40">
-        <v>657.5731828239993</v>
+        <v>769.7337586239995</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08172073673334045</v>
+        <v>0.08159987067689403</v>
       </c>
       <c r="T40">
-        <v>0.8290448705162283</v>
+        <v>0.8267868516603701</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.09257327911432335</v>
+        <v>0.09948861370951682</v>
       </c>
       <c r="W40">
-        <v>0.195822686367129</v>
+        <v>0.180822686367129</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4207876323378335</v>
+        <v>0.4522209714068947</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1267794775941801</v>
+        <v>0.1208545406391833</v>
       </c>
       <c r="C41">
-        <v>1713.493125027349</v>
+        <v>2305.864031223748</v>
       </c>
       <c r="D41">
-        <v>9969.240125027351</v>
+        <v>10561.61103122375</v>
       </c>
       <c r="E41">
         <v>-110.0529999999999</v>
@@ -4655,37 +4655,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M41">
-        <v>2123.1800226</v>
+        <v>1975.6003176</v>
       </c>
       <c r="N41">
-        <v>-1252.680022600001</v>
+        <v>-1105.1003176</v>
       </c>
       <c r="O41">
-        <v>-275.5896049720001</v>
+        <v>-243.1220698720001</v>
       </c>
       <c r="P41">
-        <v>-977.0904176280005</v>
+        <v>-861.9782477280003</v>
       </c>
       <c r="Q41">
-        <v>615.1095823719995</v>
+        <v>730.2217522719998</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08230960126995258</v>
+        <v>0.08218675380274475</v>
       </c>
       <c r="T41">
-        <v>0.8426357700328878</v>
+        <v>0.8403407344744745</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.09019960529087917</v>
+        <v>0.09693762361440103</v>
       </c>
       <c r="W41">
-        <v>0.1963349251782283</v>
+        <v>0.1813349251782283</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4099982058676326</v>
+        <v>0.440625561883641</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1284794775941801</v>
+        <v>0.1224045406391833</v>
       </c>
       <c r="C42">
-        <v>1302.954409604063</v>
+        <v>1891.542101726291</v>
       </c>
       <c r="D42">
-        <v>9810.974409604065</v>
+        <v>10399.56210172629</v>
       </c>
       <c r="E42">
         <v>142.2200000000012</v>
@@ -4737,37 +4737,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M42">
-        <v>2177.620536000001</v>
+        <v>2026.256736000001</v>
       </c>
       <c r="N42">
-        <v>-1307.120536000001</v>
+        <v>-1155.756736000001</v>
       </c>
       <c r="O42">
-        <v>-287.5665179200003</v>
+        <v>-254.2664819200002</v>
       </c>
       <c r="P42">
-        <v>-1019.554018080001</v>
+        <v>-901.4902540800006</v>
       </c>
       <c r="Q42">
-        <v>572.6459819199993</v>
+        <v>690.7097459199995</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08291809462445179</v>
+        <v>0.08279319969945717</v>
       </c>
       <c r="T42">
-        <v>0.8566796995334359</v>
+        <v>0.8543464133823825</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08794461515860717</v>
+        <v>0.09451418302404099</v>
       </c>
       <c r="W42">
-        <v>0.1968215520487726</v>
+        <v>0.1818215520487726</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3997482507209417</v>
+        <v>0.42960992283655</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1301794775941801</v>
+        <v>0.1239545406391833</v>
       </c>
       <c r="C43">
-        <v>897.362230292043</v>
+        <v>1482.117726915845</v>
       </c>
       <c r="D43">
-        <v>9657.655230292045</v>
+        <v>10242.41072691585</v>
       </c>
       <c r="E43">
         <v>394.4930000000004</v>
@@ -4819,37 +4819,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M43">
-        <v>2232.0610494</v>
+        <v>2076.9131544</v>
       </c>
       <c r="N43">
-        <v>-1361.5610494</v>
+        <v>-1206.4131544</v>
       </c>
       <c r="O43">
-        <v>-299.5434308680001</v>
+        <v>-265.4108939680001</v>
       </c>
       <c r="P43">
-        <v>-1062.017618532</v>
+        <v>-941.0022604320003</v>
       </c>
       <c r="Q43">
-        <v>530.1823814679997</v>
+        <v>651.1977395679997</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08354721487232386</v>
+        <v>0.08342020308419372</v>
       </c>
       <c r="T43">
-        <v>0.8711996944407824</v>
+        <v>0.8688268610668296</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08579962454498263</v>
+        <v>0.09220895904784489</v>
       </c>
       <c r="W43">
-        <v>0.1972844410231928</v>
+        <v>0.1822844410231927</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3899982933862847</v>
+        <v>0.4191316320356585</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1318794775941801</v>
+        <v>0.1255045406391833</v>
       </c>
       <c r="C44">
-        <v>496.4882521320014</v>
+        <v>1077.372186036</v>
       </c>
       <c r="D44">
-        <v>9509.054252132002</v>
+        <v>10089.938186036</v>
       </c>
       <c r="E44">
         <v>646.7659999999996</v>
@@ -4901,37 +4901,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M44">
-        <v>2286.5015628</v>
+        <v>2127.5695728</v>
       </c>
       <c r="N44">
-        <v>-1416.0015628</v>
+        <v>-1257.0695728</v>
       </c>
       <c r="O44">
-        <v>-311.5203438160001</v>
+        <v>-276.5553060160001</v>
       </c>
       <c r="P44">
-        <v>-1104.481218984</v>
+        <v>-980.5142667840003</v>
       </c>
       <c r="Q44">
-        <v>487.7187810159999</v>
+        <v>611.6857332159998</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08419802892184668</v>
+        <v>0.0840688272753005</v>
       </c>
       <c r="T44">
-        <v>0.8862203788276922</v>
+        <v>0.8838066345334989</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.08375677634153067</v>
+        <v>0.09001350764194382</v>
       </c>
       <c r="W44">
-        <v>0.1977252876654977</v>
+        <v>0.1827252876654977</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3807126197342303</v>
+        <v>0.4091523074633809</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1335794775941801</v>
+        <v>0.1270545406391833</v>
       </c>
       <c r="C45">
-        <v>100.1179806344626</v>
+        <v>677.0995911476421</v>
       </c>
       <c r="D45">
-        <v>9364.956980634464</v>
+        <v>9941.938591147644</v>
       </c>
       <c r="E45">
         <v>899.0390000000007</v>
@@ -4983,37 +4983,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M45">
-        <v>2340.9420762</v>
+        <v>2178.2259912</v>
       </c>
       <c r="N45">
-        <v>-1470.442076200001</v>
+        <v>-1307.725991200001</v>
       </c>
       <c r="O45">
-        <v>-323.4972567640002</v>
+        <v>-287.6997180640001</v>
       </c>
       <c r="P45">
-        <v>-1146.944819436</v>
+        <v>-1020.026273136001</v>
       </c>
       <c r="Q45">
-        <v>445.2551805639996</v>
+        <v>572.1737268639995</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08487167855205452</v>
+        <v>0.0847402102099549</v>
       </c>
       <c r="T45">
-        <v>0.9017681047720377</v>
+        <v>0.8993120140867183</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08180894433358808</v>
+        <v>0.08792017025492185</v>
       </c>
       <c r="W45">
-        <v>0.1981456298128117</v>
+        <v>0.1831456298128117</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3718588378799459</v>
+        <v>0.3996371375223721</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1352794775941801</v>
+        <v>0.1286045406391833</v>
       </c>
       <c r="C46">
-        <v>-291.9502712372159</v>
+        <v>281.1059595731549</v>
       </c>
       <c r="D46">
-        <v>9225.161728762785</v>
+        <v>9798.217959573156</v>
       </c>
       <c r="E46">
         <v>1151.312</v>
@@ -5065,37 +5065,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M46">
-        <v>2395.3825896</v>
+        <v>2228.8824096</v>
       </c>
       <c r="N46">
-        <v>-1524.882589600001</v>
+        <v>-1358.382409600001</v>
       </c>
       <c r="O46">
-        <v>-335.4741697120001</v>
+        <v>-298.8441301120001</v>
       </c>
       <c r="P46">
-        <v>-1189.408419888</v>
+        <v>-1059.538279488</v>
       </c>
       <c r="Q46">
-        <v>402.7915801119996</v>
+        <v>532.6617205119996</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08556938709762693</v>
+        <v>0.08543557110656125</v>
       </c>
       <c r="T46">
-        <v>0.9178711066429671</v>
+        <v>0.9153711571954098</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07994965014418835</v>
+        <v>0.08592198456731</v>
       </c>
       <c r="W46">
-        <v>0.1985468654988842</v>
+        <v>0.1835468654988842</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3634075006554016</v>
+        <v>0.3905544753059546</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1369794775941801</v>
+        <v>0.1301545406391833</v>
       </c>
       <c r="C47">
-        <v>-679.9063249225928</v>
+        <v>-110.7916343534125</v>
       </c>
       <c r="D47">
-        <v>9089.478675077409</v>
+        <v>9658.59336564659</v>
       </c>
       <c r="E47">
         <v>1403.585000000001</v>
@@ -5147,37 +5147,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M47">
-        <v>2449.823103000001</v>
+        <v>2279.538828</v>
       </c>
       <c r="N47">
-        <v>-1579.323103000001</v>
+        <v>-1409.038828</v>
       </c>
       <c r="O47">
-        <v>-347.4510826600002</v>
+        <v>-309.9885421600001</v>
       </c>
       <c r="P47">
-        <v>-1231.872020340001</v>
+        <v>-1099.05028584</v>
       </c>
       <c r="Q47">
-        <v>360.3279796599993</v>
+        <v>493.1497141599998</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08629246686303832</v>
+        <v>0.08615621785395326</v>
       </c>
       <c r="T47">
-        <v>0.9345596722182936</v>
+        <v>0.9320142691444172</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.07817299125209529</v>
+        <v>0.08401260713248089</v>
       </c>
       <c r="W47">
-        <v>0.1989302684877979</v>
+        <v>0.1839302684877978</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3553317784186149</v>
+        <v>0.3818754869658222</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1386794775941801</v>
+        <v>0.1317045406391834</v>
       </c>
       <c r="C48">
-        <v>-1063.928996208148</v>
+        <v>-498.7658360297628</v>
       </c>
       <c r="D48">
-        <v>8957.729003791856</v>
+        <v>9522.89216397024</v>
       </c>
       <c r="E48">
         <v>1655.858000000002</v>
@@ -5229,37 +5229,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M48">
-        <v>2504.263616400001</v>
+        <v>2330.195246400001</v>
       </c>
       <c r="N48">
-        <v>-1633.763616400001</v>
+        <v>-1459.695246400001</v>
       </c>
       <c r="O48">
-        <v>-359.4279956080003</v>
+        <v>-321.1329542080002</v>
       </c>
       <c r="P48">
-        <v>-1274.335620792001</v>
+        <v>-1138.562292192001</v>
       </c>
       <c r="Q48">
-        <v>317.864379207999</v>
+        <v>453.6377078079995</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08704232736050199</v>
+        <v>0.08690355522161906</v>
       </c>
       <c r="T48">
-        <v>0.9518663328149288</v>
+        <v>0.9492737926470916</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.07647357839878885</v>
+        <v>0.08218624610786174</v>
       </c>
       <c r="W48">
-        <v>0.1992970017815414</v>
+        <v>0.1842970017815414</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3476071745399493</v>
+        <v>0.373573845944826</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1403794775941801</v>
+        <v>0.1332545406391833</v>
       </c>
       <c r="C49">
-        <v>-1444.186881451784</v>
+        <v>-882.9797227574782</v>
       </c>
       <c r="D49">
-        <v>8829.744118548218</v>
+        <v>9390.951277242524</v>
       </c>
       <c r="E49">
         <v>1908.131000000001</v>
@@ -5311,37 +5311,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M49">
-        <v>2558.704129800001</v>
+        <v>2380.8516648</v>
       </c>
       <c r="N49">
-        <v>-1688.204129800001</v>
+        <v>-1510.351664800001</v>
       </c>
       <c r="O49">
-        <v>-371.4049085560002</v>
+        <v>-332.2773662560002</v>
       </c>
       <c r="P49">
-        <v>-1316.799221244001</v>
+        <v>-1178.074298544001</v>
       </c>
       <c r="Q49">
-        <v>275.4007787559992</v>
+        <v>414.1257014559994</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08782048448051147</v>
+        <v>0.08767909399938546</v>
       </c>
       <c r="T49">
-        <v>0.9698260749435124</v>
+        <v>0.9671846189234519</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.07484648098604867</v>
+        <v>0.08043760257365191</v>
       </c>
       <c r="W49">
-        <v>0.1996481294032107</v>
+        <v>0.1846481294032107</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3402112772093121</v>
+        <v>0.3656254662438723</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1420794775941801</v>
+        <v>0.1348045406391833</v>
       </c>
       <c r="C50">
-        <v>-1820.839077356997</v>
+        <v>-1263.587457519836</v>
       </c>
       <c r="D50">
-        <v>8705.364922643004</v>
+        <v>9262.616542480166</v>
       </c>
       <c r="E50">
         <v>2160.404</v>
@@ -5393,37 +5393,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M50">
-        <v>2613.144643200001</v>
+        <v>2431.5080832</v>
       </c>
       <c r="N50">
-        <v>-1742.644643200001</v>
+        <v>-1561.008083200001</v>
       </c>
       <c r="O50">
-        <v>-383.3818215040002</v>
+        <v>-343.4217783040001</v>
       </c>
       <c r="P50">
-        <v>-1359.262821696001</v>
+        <v>-1217.586304896</v>
       </c>
       <c r="Q50">
-        <v>232.9371783039994</v>
+        <v>374.6136951039996</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.0886285707205213</v>
+        <v>0.08848446119168134</v>
       </c>
       <c r="T50">
-        <v>0.9884765763847337</v>
+        <v>0.9857843231335182</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.07328717929883932</v>
+        <v>0.07876181918670083</v>
       </c>
       <c r="W50">
-        <v>0.1999846267073105</v>
+        <v>0.1849846267073105</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3331235422674514</v>
+        <v>0.3580082690304583</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1437794775941801</v>
+        <v>0.1363545406391833</v>
       </c>
       <c r="C51">
-        <v>-2194.035840757932</v>
+        <v>-1640.734889875948</v>
       </c>
       <c r="D51">
-        <v>8584.441159242069</v>
+        <v>9137.742110124052</v>
       </c>
       <c r="E51">
         <v>2412.677</v>
@@ -5475,37 +5475,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M51">
-        <v>2667.5851566</v>
+        <v>2482.1645016</v>
       </c>
       <c r="N51">
-        <v>-1797.0851566</v>
+        <v>-1611.6645016</v>
       </c>
       <c r="O51">
-        <v>-395.3587344520001</v>
+        <v>-354.5661903520001</v>
       </c>
       <c r="P51">
-        <v>-1401.726422148</v>
+        <v>-1257.098311248</v>
       </c>
       <c r="Q51">
-        <v>190.4735778519998</v>
+        <v>335.1016887519997</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08946834661700209</v>
+        <v>0.08932141141112607</v>
       </c>
       <c r="T51">
-        <v>1.007858470039336</v>
+        <v>1.005113427508685</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07179152257845486</v>
+        <v>0.07715443512166613</v>
       </c>
       <c r="W51">
-        <v>0.2003073894275695</v>
+        <v>0.1853073894275695</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3263251026293402</v>
+        <v>0.3507019778257551</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1454794775941801</v>
+        <v>0.1379045406391833</v>
       </c>
       <c r="C52">
-        <v>-2563.919194168522</v>
+        <v>-2014.560108895601</v>
       </c>
       <c r="D52">
-        <v>8466.83080583148</v>
+        <v>9016.189891104401</v>
       </c>
       <c r="E52">
         <v>2664.950000000001</v>
@@ -5557,37 +5557,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M52">
-        <v>2722.02567</v>
+        <v>2532.820920000001</v>
       </c>
       <c r="N52">
-        <v>-1851.525670000001</v>
+        <v>-1662.320920000001</v>
       </c>
       <c r="O52">
-        <v>-407.3356474000001</v>
+        <v>-365.7106024000002</v>
       </c>
       <c r="P52">
-        <v>-1444.1900226</v>
+        <v>-1296.610317600001</v>
       </c>
       <c r="Q52">
-        <v>148.0099773999996</v>
+        <v>295.5896823999994</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09034171354934215</v>
+        <v>0.0901918396393486</v>
       </c>
       <c r="T52">
-        <v>1.028015639440123</v>
+        <v>1.025215696058859</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.07035569212688575</v>
+        <v>0.0756113464192328</v>
       </c>
       <c r="W52">
-        <v>0.2006172416390181</v>
+        <v>0.185617241639018</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3197986005767535</v>
+        <v>0.3436879382692399</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1471794775941801</v>
+        <v>0.1394545406391833</v>
       </c>
       <c r="C53">
-        <v>-2930.623482226702</v>
+        <v>-2385.19395254184</v>
       </c>
       <c r="D53">
-        <v>8352.399517773301</v>
+        <v>8897.829047458163</v>
       </c>
       <c r="E53">
         <v>2917.223000000002</v>
@@ -5639,37 +5639,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M53">
-        <v>2776.466183400001</v>
+        <v>2583.4773384</v>
       </c>
       <c r="N53">
-        <v>-1905.966183400001</v>
+        <v>-1712.977338400001</v>
       </c>
       <c r="O53">
-        <v>-419.3125603480002</v>
+        <v>-376.8550144480001</v>
       </c>
       <c r="P53">
-        <v>-1486.653623052001</v>
+        <v>-1336.122323952</v>
       </c>
       <c r="Q53">
-        <v>105.5463769479993</v>
+        <v>256.0776760479996</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09125072811157363</v>
+        <v>0.0910977955503557</v>
       </c>
       <c r="T53">
-        <v>1.048995550449105</v>
+        <v>1.046138465366182</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.06897616875184877</v>
+        <v>0.07412877099924783</v>
       </c>
       <c r="W53">
-        <v>0.2009149427833511</v>
+        <v>0.185914942783351</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3135280397811308</v>
+        <v>0.3369489590874902</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1488794775941801</v>
+        <v>0.1410045406391833</v>
       </c>
       <c r="C54">
-        <v>-3294.275883617536</v>
+        <v>-2752.76047745168</v>
       </c>
       <c r="D54">
-        <v>8241.020116382466</v>
+        <v>8782.535522548322</v>
       </c>
       <c r="E54">
         <v>3169.496000000001</v>
@@ -5721,37 +5721,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M54">
-        <v>2830.906696800001</v>
+        <v>2634.1337568</v>
       </c>
       <c r="N54">
-        <v>-1960.406696800001</v>
+        <v>-1763.633756800001</v>
       </c>
       <c r="O54">
-        <v>-431.2894732960002</v>
+        <v>-387.9994264960001</v>
       </c>
       <c r="P54">
-        <v>-1529.117223504001</v>
+        <v>-1375.634330304001</v>
       </c>
       <c r="Q54">
-        <v>63.08277649599927</v>
+        <v>216.5656696959995</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09219761828056475</v>
+        <v>0.09204149962432145</v>
       </c>
       <c r="T54">
-        <v>1.070849624416795</v>
+        <v>1.067933016727978</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.06764970396815938</v>
+        <v>0.07270321771080077</v>
       </c>
       <c r="W54">
-        <v>0.2012011938836712</v>
+        <v>0.1862011938836712</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3074986544007244</v>
+        <v>0.3304691714127308</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1505794775941801</v>
+        <v>0.1425545406391833</v>
       </c>
       <c r="C55">
-        <v>-3654.996882576281</v>
+        <v>-3117.377392660908</v>
       </c>
       <c r="D55">
-        <v>8132.572117423722</v>
+        <v>8670.191607339095</v>
       </c>
       <c r="E55">
         <v>3421.769000000002</v>
@@ -5803,37 +5803,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M55">
-        <v>2885.347210200001</v>
+        <v>2684.790175200001</v>
       </c>
       <c r="N55">
-        <v>-2014.847210200001</v>
+        <v>-1814.290175200001</v>
       </c>
       <c r="O55">
-        <v>-443.2663862440003</v>
+        <v>-399.1438385440002</v>
       </c>
       <c r="P55">
-        <v>-1571.580823956001</v>
+        <v>-1415.146336656001</v>
       </c>
       <c r="Q55">
-        <v>20.619176043999</v>
+        <v>177.0536633439995</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09318480164823634</v>
+        <v>0.09302536131845596</v>
       </c>
       <c r="T55">
-        <v>1.093633658978854</v>
+        <v>1.090654995807297</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06637329445932617</v>
+        <v>0.07133145888606866</v>
       </c>
       <c r="W55">
-        <v>0.2014766430556774</v>
+        <v>0.1864766430556774</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3016967929969372</v>
+        <v>0.3242339040275849</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1522794775941801</v>
+        <v>0.1441045406391833</v>
       </c>
       <c r="C56">
-        <v>-4012.900703646392</v>
+        <v>-3479.156460460768</v>
       </c>
       <c r="D56">
-        <v>8026.94129635361</v>
+        <v>8560.685539539234</v>
       </c>
       <c r="E56">
         <v>3674.042000000001</v>
@@ -5885,37 +5885,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M56">
-        <v>2939.787723600001</v>
+        <v>2735.446593600001</v>
       </c>
       <c r="N56">
-        <v>-2069.287723600001</v>
+        <v>-1864.946593600001</v>
       </c>
       <c r="O56">
-        <v>-455.2432991920003</v>
+        <v>-410.2882505920002</v>
       </c>
       <c r="P56">
-        <v>-1614.044424408001</v>
+        <v>-1454.658343008001</v>
       </c>
       <c r="Q56">
-        <v>-21.84442440800103</v>
+        <v>137.5416569919994</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09421490603189364</v>
+        <v>0.0940519996079876</v>
       </c>
       <c r="T56">
-        <v>1.117408303739264</v>
+        <v>1.114364887020499</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.06514415937674606</v>
+        <v>0.07001050594373408</v>
       </c>
       <c r="W56">
-        <v>0.2017418904064982</v>
+        <v>0.1867418904064982</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2961098153488456</v>
+        <v>0.3182295724715185</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1539794775941801</v>
+        <v>0.1456545406391833</v>
       </c>
       <c r="C57">
-        <v>-4368.095712990642</v>
+        <v>-3838.203867256185</v>
       </c>
       <c r="D57">
-        <v>7924.019287009362</v>
+        <v>8453.911132743819</v>
       </c>
       <c r="E57">
         <v>3926.315000000002</v>
@@ -5967,37 +5967,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M57">
-        <v>2994.228237000001</v>
+        <v>2786.103012</v>
       </c>
       <c r="N57">
-        <v>-2123.728237000001</v>
+        <v>-1915.603012000001</v>
       </c>
       <c r="O57">
-        <v>-467.2202121400003</v>
+        <v>-421.4326626400002</v>
       </c>
       <c r="P57">
-        <v>-1656.508024860001</v>
+        <v>-1494.170349360001</v>
       </c>
       <c r="Q57">
-        <v>-64.30802486000084</v>
+        <v>98.02965063999955</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.0952907928326024</v>
+        <v>0.09512426626594289</v>
       </c>
       <c r="T57">
-        <v>1.142239599377915</v>
+        <v>1.13912855117651</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06395972011535069</v>
+        <v>0.06873758765384799</v>
       </c>
       <c r="W57">
-        <v>0.2019974923991073</v>
+        <v>0.1869974923991073</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2907260005243212</v>
+        <v>0.3124435802447636</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1556794775941801</v>
+        <v>0.1472045406391833</v>
       </c>
       <c r="C58">
-        <v>-4720.684789219125</v>
+        <v>-4194.620567012371</v>
       </c>
       <c r="D58">
-        <v>7823.703210780877</v>
+        <v>8349.767432987632</v>
       </c>
       <c r="E58">
         <v>4178.588000000002</v>
@@ -6049,37 +6049,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M58">
-        <v>3048.668750400001</v>
+        <v>2836.7594304</v>
       </c>
       <c r="N58">
-        <v>-2178.168750400001</v>
+        <v>-1966.259430400001</v>
       </c>
       <c r="O58">
-        <v>-479.1971250880002</v>
+        <v>-432.5770746880002</v>
       </c>
       <c r="P58">
-        <v>-1698.971625312001</v>
+        <v>-1533.682355712001</v>
       </c>
       <c r="Q58">
-        <v>-106.7716253120009</v>
+        <v>58.51764428799947</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.0964155835787979</v>
+        <v>0.09624527231744159</v>
       </c>
       <c r="T58">
-        <v>1.168199590272867</v>
+        <v>1.165017836430522</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06281758225614799</v>
+        <v>0.06751013073145785</v>
       </c>
       <c r="W58">
-        <v>0.2022439657491233</v>
+        <v>0.1872439657491233</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2855344648006726</v>
+        <v>0.3068642305975358</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1573794775941801</v>
+        <v>0.1487545406391833</v>
       </c>
       <c r="C59">
-        <v>-5070.765666402001</v>
+        <v>-4548.502599624875</v>
       </c>
       <c r="D59">
-        <v>7725.895333598001</v>
+        <v>8248.158400375129</v>
       </c>
       <c r="E59">
         <v>4430.861000000003</v>
@@ -6131,37 +6131,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M59">
-        <v>3103.109263800001</v>
+        <v>2887.415848800001</v>
       </c>
       <c r="N59">
-        <v>-2232.609263800001</v>
+        <v>-2016.915848800001</v>
       </c>
       <c r="O59">
-        <v>-491.1740380360002</v>
+        <v>-443.7214867360002</v>
       </c>
       <c r="P59">
-        <v>-1741.435225764001</v>
+        <v>-1573.194362064001</v>
       </c>
       <c r="Q59">
-        <v>-149.2352257640007</v>
+        <v>19.00563793599918</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09759269017365367</v>
+        <v>0.09741841818528907</v>
       </c>
       <c r="T59">
-        <v>1.195367022604795</v>
+        <v>1.192111274487045</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.0617155194095489</v>
+        <v>0.06632574247301122</v>
       </c>
       <c r="W59">
-        <v>0.2024817909114194</v>
+        <v>0.1874817909114193</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2805250882252224</v>
+        <v>0.3014806476045965</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1590794775941801</v>
+        <v>0.1503045406391833</v>
       </c>
       <c r="C60">
-        <v>-5418.431251670792</v>
+        <v>-4899.941386323417</v>
       </c>
       <c r="D60">
-        <v>7630.502748329209</v>
+        <v>8148.992613676583</v>
       </c>
       <c r="E60">
         <v>4683.134</v>
@@ -6213,37 +6213,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M60">
-        <v>3157.5497772</v>
+        <v>2938.0722672</v>
       </c>
       <c r="N60">
-        <v>-2287.049777200001</v>
+        <v>-2067.5722672</v>
       </c>
       <c r="O60">
-        <v>-503.1509509840002</v>
+        <v>-454.865898784</v>
       </c>
       <c r="P60">
-        <v>-1783.898826216001</v>
+        <v>-1612.706368416</v>
       </c>
       <c r="Q60">
-        <v>-191.6988262160005</v>
+        <v>-20.50636841600021</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09882584946350256</v>
+        <v>0.09864742814208166</v>
       </c>
       <c r="T60">
-        <v>1.223828142190623</v>
+        <v>1.220494876260546</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.06065145873007393</v>
+        <v>0.06518219518899381</v>
       </c>
       <c r="W60">
-        <v>0.2027114152060501</v>
+        <v>0.1877114152060501</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2756884487730632</v>
+        <v>0.2962827054045173</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1607794775941801</v>
+        <v>0.1518545406391833</v>
       </c>
       <c r="C61">
-        <v>-5763.769919577981</v>
+        <v>-5249.0240040195</v>
       </c>
       <c r="D61">
-        <v>7537.437080422022</v>
+        <v>8052.182995980501</v>
       </c>
       <c r="E61">
         <v>4935.407000000001</v>
@@ -6295,37 +6295,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M61">
-        <v>3211.990290600001</v>
+        <v>2988.728685600001</v>
       </c>
       <c r="N61">
-        <v>-2341.490290600001</v>
+        <v>-2118.228685600001</v>
       </c>
       <c r="O61">
-        <v>-515.1278639320002</v>
+        <v>-466.0103108320002</v>
       </c>
       <c r="P61">
-        <v>-1826.362426668</v>
+        <v>-1652.218374768001</v>
       </c>
       <c r="Q61">
-        <v>-234.1624266680003</v>
+        <v>-60.01837476800074</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1001191628650514</v>
+        <v>0.09993638980408365</v>
       </c>
       <c r="T61">
-        <v>1.253677609073321</v>
+        <v>1.250263043974218</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05962346790414046</v>
+        <v>0.06407741221968881</v>
       </c>
       <c r="W61">
-        <v>0.2029332556262865</v>
+        <v>0.1879332556262865</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2710157632006386</v>
+        <v>0.2912609646349491</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1624794775941801</v>
+        <v>0.1534045406391833</v>
       </c>
       <c r="C62">
-        <v>-6106.865785175087</v>
+        <v>-5595.833440328139</v>
       </c>
       <c r="D62">
-        <v>7446.614214824915</v>
+        <v>7957.646559671862</v>
       </c>
       <c r="E62">
         <v>5187.68</v>
@@ -6377,37 +6377,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M62">
-        <v>3266.430804000001</v>
+        <v>3039.385104</v>
       </c>
       <c r="N62">
-        <v>-2395.930804000001</v>
+        <v>-2168.885104000001</v>
       </c>
       <c r="O62">
-        <v>-527.1047768800001</v>
+        <v>-477.1547228800002</v>
       </c>
       <c r="P62">
-        <v>-1868.82602712</v>
+        <v>-1691.730381120001</v>
       </c>
       <c r="Q62">
-        <v>-276.6260271200003</v>
+        <v>-99.53038112000058</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1014771419366777</v>
+        <v>0.1012897995491857</v>
       </c>
       <c r="T62">
-        <v>1.285019549300154</v>
+        <v>1.281519620073573</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05862974343907146</v>
+        <v>0.06300945534936067</v>
       </c>
       <c r="W62">
-        <v>0.2031477013658484</v>
+        <v>0.1881477013658484</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2664988338139612</v>
+        <v>0.2864066152243666</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1641794775941801</v>
+        <v>0.1549545406391833</v>
       </c>
       <c r="C63">
-        <v>-6447.798957583012</v>
+        <v>-5940.448830833622</v>
       </c>
       <c r="D63">
-        <v>7357.954042416989</v>
+        <v>7865.304169166379</v>
       </c>
       <c r="E63">
         <v>5439.953000000001</v>
@@ -6459,37 +6459,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M63">
-        <v>3320.871317400001</v>
+        <v>3090.0415224</v>
       </c>
       <c r="N63">
-        <v>-2450.371317400001</v>
+        <v>-2219.541522400001</v>
       </c>
       <c r="O63">
-        <v>-539.0816898280003</v>
+        <v>-488.2991349280002</v>
       </c>
       <c r="P63">
-        <v>-1911.289627572001</v>
+        <v>-1731.242387472001</v>
       </c>
       <c r="Q63">
-        <v>-319.0896275720008</v>
+        <v>-139.0423874720007</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1029047609606951</v>
+        <v>0.1027126149222418</v>
       </c>
       <c r="T63">
-        <v>1.317968768512978</v>
+        <v>1.314379097511358</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05766860010400471</v>
+        <v>0.06197651345838755</v>
       </c>
       <c r="W63">
-        <v>0.2033551160975558</v>
+        <v>0.1883551160975558</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2621300004727486</v>
+        <v>0.2817114248108524</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1658794775941801</v>
+        <v>0.1565045406391833</v>
       </c>
       <c r="C64">
-        <v>-6786.645775661302</v>
+        <v>-6282.945680025065</v>
       </c>
       <c r="D64">
-        <v>7271.380224338699</v>
+        <v>7775.080319974936</v>
       </c>
       <c r="E64">
         <v>5692.226000000001</v>
@@ -6541,37 +6541,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M64">
-        <v>3375.311830800001</v>
+        <v>3140.6979408</v>
       </c>
       <c r="N64">
-        <v>-2504.811830800001</v>
+        <v>-2270.197940800001</v>
       </c>
       <c r="O64">
-        <v>-551.0586027760003</v>
+        <v>-499.4435469760002</v>
       </c>
       <c r="P64">
-        <v>-1953.753228024001</v>
+        <v>-1770.754393824001</v>
       </c>
       <c r="Q64">
-        <v>-361.5532280240009</v>
+        <v>-178.5543938240005</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1044075178280818</v>
+        <v>0.1042103153149324</v>
       </c>
       <c r="T64">
-        <v>1.352652157158057</v>
+        <v>1.348968021130078</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05673846139264981</v>
+        <v>0.06097689227357485</v>
       </c>
       <c r="W64">
-        <v>0.2035558400314662</v>
+        <v>0.1885558400314662</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2579020972393172</v>
+        <v>0.2771676921526128</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1675794775941801</v>
+        <v>0.1580545406391833</v>
       </c>
       <c r="C65">
-        <v>-7123.479027233536</v>
+        <v>-6623.396067198115</v>
       </c>
       <c r="D65">
-        <v>7186.819972766467</v>
+        <v>7686.902932801887</v>
       </c>
       <c r="E65">
         <v>5944.499000000002</v>
@@ -6623,37 +6623,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M65">
-        <v>3429.752344200001</v>
+        <v>3191.354359200001</v>
       </c>
       <c r="N65">
-        <v>-2559.252344200001</v>
+        <v>-2320.854359200001</v>
       </c>
       <c r="O65">
-        <v>-563.0355157240002</v>
+        <v>-510.5879590240001</v>
       </c>
       <c r="P65">
-        <v>-1996.216828476001</v>
+        <v>-1810.266400176</v>
       </c>
       <c r="Q65">
-        <v>-404.0168284760009</v>
+        <v>-218.0664001760003</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1059915047964083</v>
+        <v>0.1057889724856062</v>
       </c>
       <c r="T65">
-        <v>1.389210323567734</v>
+        <v>1.385426616295755</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05583785089435377</v>
+        <v>0.0600090050946292</v>
       </c>
       <c r="W65">
-        <v>0.2037501917769985</v>
+        <v>0.1887501917769984</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2538084131561534</v>
+        <v>0.2727682049755874</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1692794775941801</v>
+        <v>0.1596045406391833</v>
       </c>
       <c r="C66">
-        <v>-7458.368153192087</v>
+        <v>-6961.868838502969</v>
       </c>
       <c r="D66">
-        <v>7104.203846807915</v>
+        <v>7600.703161497032</v>
       </c>
       <c r="E66">
         <v>6196.772000000001</v>
@@ -6705,37 +6705,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M66">
-        <v>3484.1928576</v>
+        <v>3242.0107776</v>
       </c>
       <c r="N66">
-        <v>-2613.692857600001</v>
+        <v>-2371.5107776</v>
       </c>
       <c r="O66">
-        <v>-575.0124286720002</v>
+        <v>-521.7323710720001</v>
       </c>
       <c r="P66">
-        <v>-2038.680428928001</v>
+        <v>-1849.778406528</v>
       </c>
       <c r="Q66">
-        <v>-446.4804289280007</v>
+        <v>-257.5784065280002</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.107663491040753</v>
+        <v>0.1074553328324286</v>
       </c>
       <c r="T66">
-        <v>1.427799499222393</v>
+        <v>1.423910688970637</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05496538447412949</v>
+        <v>0.05907136439002562</v>
       </c>
       <c r="W66">
-        <v>0.2039384700304829</v>
+        <v>0.1889384700304829</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2498426567005886</v>
+        <v>0.2685062017728438</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1709794775941801</v>
+        <v>0.1611545406391833</v>
       </c>
       <c r="C67">
-        <v>-7791.379437685166</v>
+        <v>-7298.429786214121</v>
       </c>
       <c r="D67">
-        <v>7023.465562314836</v>
+        <v>7516.415213785881</v>
       </c>
       <c r="E67">
         <v>6449.045000000002</v>
@@ -6787,37 +6787,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M67">
-        <v>3538.633371000001</v>
+        <v>3292.667196000001</v>
       </c>
       <c r="N67">
-        <v>-2668.133371000001</v>
+        <v>-2422.167196000001</v>
       </c>
       <c r="O67">
-        <v>-586.9893416200002</v>
+        <v>-532.8767831200003</v>
       </c>
       <c r="P67">
-        <v>-2081.144029380001</v>
+        <v>-1889.290412880001</v>
       </c>
       <c r="Q67">
-        <v>-488.9440293800005</v>
+        <v>-297.0904128800009</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1094310193562031</v>
+        <v>0.109216913770498</v>
       </c>
       <c r="T67">
-        <v>1.468593770628747</v>
+        <v>1.464593851512656</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0541197631745275</v>
+        <v>0.0581625741686406</v>
       </c>
       <c r="W67">
-        <v>0.204120955106937</v>
+        <v>0.189120955106937</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2459989235205796</v>
+        <v>0.2643753371301845</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1726794775941801</v>
+        <v>0.1627045406391833</v>
       </c>
       <c r="C68">
-        <v>-8122.57618548087</v>
+        <v>-7633.141816202817</v>
       </c>
       <c r="D68">
-        <v>6944.541814519133</v>
+        <v>7433.976183797186</v>
       </c>
       <c r="E68">
         <v>6701.318000000003</v>
@@ -6869,37 +6869,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M68">
-        <v>3593.073884400001</v>
+        <v>3343.323614400001</v>
       </c>
       <c r="N68">
-        <v>-2722.573884400002</v>
+        <v>-2472.823614400001</v>
       </c>
       <c r="O68">
-        <v>-598.9662545680004</v>
+        <v>-544.0211951680003</v>
       </c>
       <c r="P68">
-        <v>-2123.607629832001</v>
+        <v>-1928.802419232001</v>
       </c>
       <c r="Q68">
-        <v>-531.4076298320012</v>
+        <v>-336.6024192320008</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1113025199255032</v>
+        <v>0.1110821171166891</v>
       </c>
       <c r="T68">
-        <v>1.511787705059005</v>
+        <v>1.507670141263028</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05329976676279223</v>
+        <v>0.05728132304487333</v>
       </c>
       <c r="W68">
-        <v>0.2042979103325895</v>
+        <v>0.1892979103325894</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2422716671036009</v>
+        <v>0.2603696502039696</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1743794775941801</v>
+        <v>0.1642545406391833</v>
       </c>
       <c r="C69">
-        <v>-8452.018887505737</v>
+        <v>-7966.065104508241</v>
       </c>
       <c r="D69">
-        <v>6867.372112494268</v>
+        <v>7353.325895491763</v>
       </c>
       <c r="E69">
         <v>6953.591000000004</v>
@@ -6951,37 +6951,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M69">
-        <v>3647.514397800001</v>
+        <v>3393.980032800001</v>
       </c>
       <c r="N69">
-        <v>-2777.014397800001</v>
+        <v>-2523.480032800001</v>
       </c>
       <c r="O69">
-        <v>-610.9431675160004</v>
+        <v>-555.1656072160002</v>
       </c>
       <c r="P69">
-        <v>-2166.071230284001</v>
+        <v>-1968.314425584001</v>
       </c>
       <c r="Q69">
-        <v>-573.8712302840011</v>
+        <v>-376.1144255840006</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1132874447717305</v>
+        <v>0.1130603630899221</v>
       </c>
       <c r="T69">
-        <v>1.557599453697156</v>
+        <v>1.553357115240696</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05250424785588488</v>
+        <v>0.05642637792480058</v>
       </c>
       <c r="W69">
-        <v>0.2044695833127</v>
+        <v>0.1894695833127001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2386556720722041</v>
+        <v>0.2564835360218209</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1760794775941801</v>
+        <v>0.1658045406391833</v>
       </c>
       <c r="C70">
-        <v>-8779.765375467525</v>
+        <v>-8297.257243826312</v>
       </c>
       <c r="D70">
-        <v>6791.898624532477</v>
+        <v>7274.406756173689</v>
       </c>
       <c r="E70">
         <v>7205.864000000001</v>
@@ -7033,37 +7033,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M70">
-        <v>3701.954911200001</v>
+        <v>3444.6364512</v>
       </c>
       <c r="N70">
-        <v>-2831.454911200001</v>
+        <v>-2574.136451200001</v>
       </c>
       <c r="O70">
-        <v>-622.9200804640003</v>
+        <v>-566.3100192640002</v>
       </c>
       <c r="P70">
-        <v>-2208.534830736001</v>
+        <v>-2007.826431936001</v>
       </c>
       <c r="Q70">
-        <v>-616.3348307360009</v>
+        <v>-415.6264319360007</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1153964274208471</v>
+        <v>0.1151622494364822</v>
       </c>
       <c r="T70">
-        <v>1.606274436625192</v>
+        <v>1.601899525091967</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05173212656388658</v>
+        <v>0.05559657824943588</v>
       </c>
       <c r="W70">
-        <v>0.2046362070875133</v>
+        <v>0.1896362070875133</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.235146029835848</v>
+        <v>0.2527117193156175</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1777794775941801</v>
+        <v>0.1673545406391833</v>
       </c>
       <c r="C71">
-        <v>-9105.87096639288</v>
+        <v>-8626.773380665583</v>
       </c>
       <c r="D71">
-        <v>6718.066033607123</v>
+        <v>7197.16361933442</v>
       </c>
       <c r="E71">
         <v>7458.137000000002</v>
@@ -7115,37 +7115,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M71">
-        <v>3756.395424600001</v>
+        <v>3495.292869600001</v>
       </c>
       <c r="N71">
-        <v>-2885.895424600001</v>
+        <v>-2624.792869600001</v>
       </c>
       <c r="O71">
-        <v>-634.8969934120003</v>
+        <v>-577.4544313120002</v>
       </c>
       <c r="P71">
-        <v>-2250.998431188001</v>
+        <v>-2047.338438288001</v>
       </c>
       <c r="Q71">
-        <v>-658.7984311880007</v>
+        <v>-455.1384382880005</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1176414734666809</v>
+        <v>0.1173997413537881</v>
       </c>
       <c r="T71">
-        <v>1.658089741032457</v>
+        <v>1.65357370332074</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05098238559919257</v>
+        <v>0.05479083073857449</v>
       </c>
       <c r="W71">
-        <v>0.2047980011876943</v>
+        <v>0.1897980011876942</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2317381163599663</v>
+        <v>0.249049230629884</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1794794775941801</v>
+        <v>0.1689045406391833</v>
       </c>
       <c r="C72">
-        <v>-9430.388597838992</v>
+        <v>-8954.666343856599</v>
       </c>
       <c r="D72">
-        <v>6645.821402161013</v>
+        <v>7121.543656143405</v>
       </c>
       <c r="E72">
         <v>7710.410000000003</v>
@@ -7197,37 +7197,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M72">
-        <v>3810.835938000001</v>
+        <v>3545.949288000001</v>
       </c>
       <c r="N72">
-        <v>-2940.335938000001</v>
+        <v>-2675.449288000002</v>
       </c>
       <c r="O72">
-        <v>-646.8739063600002</v>
+        <v>-588.5988433600004</v>
       </c>
       <c r="P72">
-        <v>-2293.462031640001</v>
+        <v>-2086.850444640001</v>
       </c>
       <c r="Q72">
-        <v>-701.2620316400009</v>
+        <v>-494.6504446400011</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1200361892489036</v>
+        <v>0.1197863993989143</v>
       </c>
       <c r="T72">
-        <v>1.713359399066872</v>
+        <v>1.708692826764765</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05025406580491839</v>
+        <v>0.05400810458516627</v>
       </c>
       <c r="W72">
-        <v>0.2049551725992986</v>
+        <v>0.1899551725992986</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2284275718405382</v>
+        <v>0.2454913844780284</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1811794775941801</v>
+        <v>0.1704545406391833</v>
       </c>
       <c r="C73">
-        <v>-9753.368954473908</v>
+        <v>-9280.986765044092</v>
       </c>
       <c r="D73">
-        <v>6575.114045526094</v>
+        <v>7047.49623495591</v>
       </c>
       <c r="E73">
         <v>7962.683000000001</v>
@@ -7279,37 +7279,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M73">
-        <v>3865.2764514</v>
+        <v>3596.605706400001</v>
       </c>
       <c r="N73">
-        <v>-2994.776451400001</v>
+        <v>-2726.105706400001</v>
       </c>
       <c r="O73">
-        <v>-658.8508193080003</v>
+        <v>-599.7432554080001</v>
       </c>
       <c r="P73">
-        <v>-2335.925632092001</v>
+        <v>-2126.362450992001</v>
       </c>
       <c r="Q73">
-        <v>-743.7256320920008</v>
+        <v>-534.1624509920005</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1225960578436933</v>
+        <v>0.122337654550601</v>
       </c>
       <c r="T73">
-        <v>1.772440757655384</v>
+        <v>1.767613269066998</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04954626206118715</v>
+        <v>0.05324742705579774</v>
       </c>
       <c r="W73">
-        <v>0.2051079166471958</v>
+        <v>0.1901079166471958</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2252102820963052</v>
+        <v>0.2420337593445353</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1828794775941801</v>
+        <v>0.1720045406391833</v>
       </c>
       <c r="C74">
-        <v>-10074.86058666147</v>
+        <v>-9605.783191739518</v>
       </c>
       <c r="D74">
-        <v>6505.895413338533</v>
+        <v>6974.972808260485</v>
       </c>
       <c r="E74">
         <v>8214.956000000002</v>
@@ -7361,37 +7361,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M74">
-        <v>3919.716964800001</v>
+        <v>3647.2621248</v>
       </c>
       <c r="N74">
-        <v>-3049.216964800001</v>
+        <v>-2776.7621248</v>
       </c>
       <c r="O74">
-        <v>-670.8277322560002</v>
+        <v>-610.8876674560001</v>
       </c>
       <c r="P74">
-        <v>-2378.389232544001</v>
+        <v>-2165.874457344</v>
       </c>
       <c r="Q74">
-        <v>-786.1892325440006</v>
+        <v>-573.6744573440003</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1253387741952538</v>
+        <v>0.1250711422131225</v>
       </c>
       <c r="T74">
-        <v>1.835742213285934</v>
+        <v>1.830742314390819</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04885811953255955</v>
+        <v>0.05250787945780055</v>
       </c>
       <c r="W74">
-        <v>0.2052564178048737</v>
+        <v>0.1902564178048737</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2220823615116344</v>
+        <v>0.2386721793536389</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1845794775941801</v>
+        <v>0.1735545406391833</v>
       </c>
       <c r="C75">
-        <v>-10394.91002163395</v>
+        <v>-9929.102193464341</v>
       </c>
       <c r="D75">
-        <v>6438.118978366047</v>
+        <v>6903.926806535658</v>
       </c>
       <c r="E75">
         <v>8467.228999999999</v>
@@ -7443,37 +7443,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M75">
-        <v>3974.1574782</v>
+        <v>3697.9185432</v>
       </c>
       <c r="N75">
-        <v>-3103.657478200001</v>
+        <v>-2827.4185432</v>
       </c>
       <c r="O75">
-        <v>-682.8046452040002</v>
+        <v>-622.0320795040001</v>
       </c>
       <c r="P75">
-        <v>-2420.852832996</v>
+        <v>-2205.386463696</v>
       </c>
       <c r="Q75">
-        <v>-828.6528329960004</v>
+        <v>-613.1864636960001</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.128284654721004</v>
+        <v>0.1280071104432381</v>
       </c>
       <c r="T75">
-        <v>1.903732665629858</v>
+        <v>1.898547585294183</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04818883022389436</v>
+        <v>0.0517885934378307</v>
       </c>
       <c r="W75">
-        <v>0.2054008504376836</v>
+        <v>0.1904008504376836</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2190401373813379</v>
+        <v>0.2354026974446849</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1862794775941801</v>
+        <v>0.1751045406391833</v>
       </c>
       <c r="C76">
-        <v>-10713.56186778741</v>
+        <v>-10250.98846147181</v>
       </c>
       <c r="D76">
-        <v>6371.740132212589</v>
+        <v>6834.313538528187</v>
       </c>
       <c r="E76">
         <v>8719.502</v>
@@ -7525,37 +7525,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M76">
-        <v>4028.597991600001</v>
+        <v>3748.5749616</v>
       </c>
       <c r="N76">
-        <v>-3158.097991600001</v>
+        <v>-2878.0749616</v>
       </c>
       <c r="O76">
-        <v>-694.7815581520001</v>
+        <v>-633.176491552</v>
       </c>
       <c r="P76">
-        <v>-2463.316433448001</v>
+        <v>-2244.898470048</v>
       </c>
       <c r="Q76">
-        <v>-871.1164334480006</v>
+        <v>-652.6984700480004</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1314571414410426</v>
+        <v>0.1311689223833627</v>
       </c>
       <c r="T76">
-        <v>1.976953152769467</v>
+        <v>1.971568646267036</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04753762981546335</v>
+        <v>0.05108874758056271</v>
       </c>
       <c r="W76">
-        <v>0.205541379485823</v>
+        <v>0.190541379485823</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2160801355248334</v>
+        <v>0.2322215799116487</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1879794775941801</v>
+        <v>0.1766545406391833</v>
       </c>
       <c r="C77">
-        <v>-11030.85891259093</v>
+        <v>-10571.4849024959</v>
       </c>
       <c r="D77">
-        <v>6306.716087409069</v>
+        <v>6766.090097504103</v>
       </c>
       <c r="E77">
         <v>8971.775000000001</v>
@@ -7607,37 +7607,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M77">
-        <v>4083.038505000001</v>
+        <v>3799.231380000001</v>
       </c>
       <c r="N77">
-        <v>-3212.538505000001</v>
+        <v>-2928.731380000001</v>
       </c>
       <c r="O77">
-        <v>-706.7584711000003</v>
+        <v>-644.3209036000003</v>
       </c>
       <c r="P77">
-        <v>-2505.780033900001</v>
+        <v>-2284.410476400001</v>
       </c>
       <c r="Q77">
-        <v>-913.5800339000009</v>
+        <v>-692.2104764000007</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1348834270986843</v>
+        <v>0.1345836792786972</v>
       </c>
       <c r="T77">
-        <v>2.056031278880246</v>
+        <v>2.050431392117718</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04690379475125717</v>
+        <v>0.05040756427948853</v>
       </c>
       <c r="W77">
-        <v>0.2056781610926787</v>
+        <v>0.1906781610926787</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2131990670511689</v>
+        <v>0.2291252921794933</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1896794775941801</v>
+        <v>0.1782045406391833</v>
       </c>
       <c r="C78">
-        <v>-11346.84221456146</v>
+        <v>-10890.63272694061</v>
       </c>
       <c r="D78">
-        <v>6243.00578543854</v>
+        <v>6699.215273059392</v>
       </c>
       <c r="E78">
         <v>9224.048000000003</v>
@@ -7689,37 +7689,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M78">
-        <v>4137.479018400001</v>
+        <v>3849.887798400001</v>
       </c>
       <c r="N78">
-        <v>-3266.979018400001</v>
+        <v>-2979.387798400001</v>
       </c>
       <c r="O78">
-        <v>-718.7353840480002</v>
+        <v>-655.4653156480002</v>
       </c>
       <c r="P78">
-        <v>-2548.243634352001</v>
+        <v>-2323.922482752001</v>
       </c>
       <c r="Q78">
-        <v>-956.0436343520012</v>
+        <v>-731.7224827520006</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1385952365611295</v>
+        <v>0.1382829992486429</v>
       </c>
       <c r="T78">
-        <v>2.14169924883359</v>
+        <v>2.135866033455956</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04628663955716168</v>
+        <v>0.04974430685475841</v>
       </c>
       <c r="W78">
-        <v>0.2058113431835645</v>
+        <v>0.1908113431835645</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2103938161689167</v>
+        <v>0.2261104857034474</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1913794775941801</v>
+        <v>0.1797545406391833</v>
       </c>
       <c r="C79">
-        <v>-11661.5511897196</v>
+        <v>-11208.47153189068</v>
       </c>
       <c r="D79">
-        <v>6180.569810280407</v>
+        <v>6633.64946810932</v>
       </c>
       <c r="E79">
         <v>9476.321000000004</v>
@@ -7771,37 +7771,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M79">
-        <v>4191.919531800001</v>
+        <v>3900.544216800001</v>
       </c>
       <c r="N79">
-        <v>-3321.419531800001</v>
+        <v>-3030.044216800001</v>
       </c>
       <c r="O79">
-        <v>-730.7122969960002</v>
+        <v>-666.6097276960002</v>
       </c>
       <c r="P79">
-        <v>-2590.707234804001</v>
+        <v>-2363.434489104001</v>
       </c>
       <c r="Q79">
-        <v>-998.507234804001</v>
+        <v>-771.2344891040009</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1426298120637873</v>
+        <v>0.1423039992159752</v>
       </c>
       <c r="T79">
-        <v>2.234816607478529</v>
+        <v>2.228729774040998</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04568551436810762</v>
+        <v>0.04909827689560571</v>
       </c>
       <c r="W79">
-        <v>0.2059410659993624</v>
+        <v>0.1909410659993624</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2076614289459439</v>
+        <v>0.223173985889117</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1930794775941801</v>
+        <v>0.1813045406391833</v>
       </c>
       <c r="C80">
-        <v>-11975.02369290893</v>
+        <v>-11525.03937929485</v>
       </c>
       <c r="D80">
-        <v>6119.370307091076</v>
+        <v>6569.354620705151</v>
       </c>
       <c r="E80">
         <v>9728.594000000001</v>
@@ -7853,37 +7853,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M80">
-        <v>4246.360045200001</v>
+        <v>3951.2006352</v>
       </c>
       <c r="N80">
-        <v>-3375.860045200001</v>
+        <v>-3080.700635200001</v>
       </c>
       <c r="O80">
-        <v>-742.6892099440003</v>
+        <v>-677.7541397440002</v>
       </c>
       <c r="P80">
-        <v>-2633.170835256001</v>
+        <v>-2402.946495456001</v>
       </c>
       <c r="Q80">
-        <v>-1040.970835256001</v>
+        <v>-810.7464954560007</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1470311671575958</v>
+        <v>0.1466905446348832</v>
       </c>
       <c r="T80">
-        <v>2.336399180545734</v>
+        <v>2.330035672861043</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04509980264543959</v>
+        <v>0.04846881180720052</v>
       </c>
       <c r="W80">
-        <v>0.2060674625891142</v>
+        <v>0.1910674625891141</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2049991029338163</v>
+        <v>0.2203127809418205</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1947794775941801</v>
+        <v>0.1828545406391834</v>
       </c>
       <c r="C81">
-        <v>-12287.29609433143</v>
+        <v>-11840.37286964617</v>
       </c>
       <c r="D81">
-        <v>6059.37090566857</v>
+        <v>6506.294130353835</v>
       </c>
       <c r="E81">
         <v>9980.867000000002</v>
@@ -7935,37 +7935,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M81">
-        <v>4300.800558600001</v>
+        <v>4001.857053600001</v>
       </c>
       <c r="N81">
-        <v>-3430.300558600001</v>
+        <v>-3131.357053600001</v>
       </c>
       <c r="O81">
-        <v>-754.6661228920002</v>
+        <v>-688.8985517920001</v>
       </c>
       <c r="P81">
-        <v>-2675.634435708001</v>
+        <v>-2442.458501808001</v>
       </c>
       <c r="Q81">
-        <v>-1083.434435708001</v>
+        <v>-850.2585018080006</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1518516989270051</v>
+        <v>0.1514948562841633</v>
       </c>
       <c r="T81">
-        <v>2.447656284381246</v>
+        <v>2.440989752521094</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04452891906764921</v>
+        <v>0.04785528254381823</v>
       </c>
       <c r="W81">
-        <v>0.2061906592652013</v>
+        <v>0.1911906592652013</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2024041775802238</v>
+        <v>0.2175240115628102</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2205785832131313</v>
+        <v>0.1844045406391833</v>
       </c>
       <c r="C82">
-        <v>-13324.40693014584</v>
+        <v>-12154.50721145905</v>
       </c>
       <c r="D82">
-        <v>5274.533069854166</v>
+        <v>6444.432788540953</v>
       </c>
       <c r="E82">
         <v>10233.14</v>
@@ -8017,45 +8017,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M82">
-        <v>4960.696272000001</v>
+        <v>4052.513472000001</v>
       </c>
       <c r="N82">
-        <v>-4090.196272000001</v>
+        <v>-3182.013472000001</v>
       </c>
       <c r="O82">
-        <v>-899.8431798400003</v>
+        <v>-700.0429638400003</v>
       </c>
       <c r="P82">
-        <v>-3190.353092160001</v>
+        <v>-2481.970508160001</v>
       </c>
       <c r="Q82">
-        <v>-1598.153092160001</v>
+        <v>-889.7705081600013</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1576498119681115</v>
+        <v>0.1567795990983715</v>
       </c>
       <c r="T82">
-        <v>2.58147580793631</v>
+        <v>2.563039240147148</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03860546776083693</v>
+        <v>0.0472570915120205</v>
       </c>
       <c r="W82">
-        <v>0.2363107760243863</v>
+        <v>0.1913107760243863</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.1754793989128951</v>
+        <v>0.2148049614182749</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2225785832131314</v>
+        <v>0.1859545406391833</v>
       </c>
       <c r="C83">
-        <v>-13629.1151083259</v>
+        <v>-12467.47628682016</v>
       </c>
       <c r="D83">
-        <v>5222.097891674109</v>
+        <v>6383.736713179848</v>
       </c>
       <c r="E83">
         <v>10485.413</v>
@@ -8099,45 +8099,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M83">
-        <v>5022.704975400002</v>
+        <v>4103.169890400001</v>
       </c>
       <c r="N83">
-        <v>-4152.204975400002</v>
+        <v>-3232.669890400001</v>
       </c>
       <c r="O83">
-        <v>-913.4850945880004</v>
+        <v>-711.1873758880002</v>
       </c>
       <c r="P83">
-        <v>-3238.719880812002</v>
+        <v>-2521.482514512001</v>
       </c>
       <c r="Q83">
-        <v>-1646.519880812001</v>
+        <v>-929.2825145120012</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1635366441769595</v>
+        <v>0.1626206306298647</v>
       </c>
       <c r="T83">
-        <v>2.717342955722432</v>
+        <v>2.697936042260156</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03812885704774017</v>
+        <v>0.04667367062915604</v>
       </c>
       <c r="W83">
-        <v>0.2364279269376655</v>
+        <v>0.1914279269376655</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.1733129865806372</v>
+        <v>0.2121530483143457</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2245785832131313</v>
+        <v>0.1875045406391833</v>
       </c>
       <c r="C84">
-        <v>-13932.79101156727</v>
+        <v>-12779.31271326951</v>
       </c>
       <c r="D84">
-        <v>5170.694988432735</v>
+        <v>6324.173286730492</v>
       </c>
       <c r="E84">
         <v>10737.686</v>
@@ -8181,45 +8181,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M84">
-        <v>5084.713678800001</v>
+        <v>4153.8263088</v>
       </c>
       <c r="N84">
-        <v>-4214.213678800001</v>
+        <v>-3283.3263088</v>
       </c>
       <c r="O84">
-        <v>-927.1270093360001</v>
+        <v>-722.3317879360001</v>
       </c>
       <c r="P84">
-        <v>-3287.086669464001</v>
+        <v>-2560.994520864</v>
       </c>
       <c r="Q84">
-        <v>-1694.886669464001</v>
+        <v>-968.7945208640001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1700775688534573</v>
+        <v>0.1691106656648572</v>
       </c>
       <c r="T84">
-        <v>2.868306453262567</v>
+        <v>2.847821377941275</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03766387098618237</v>
+        <v>0.04610447952392244</v>
       </c>
       <c r="W84">
-        <v>0.2365422205115964</v>
+        <v>0.1915422205115964</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.1711994135735563</v>
+        <v>0.2095658160178293</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2265785832131313</v>
+        <v>0.1890545406391834</v>
       </c>
       <c r="C85">
-        <v>-14235.46482584938</v>
+        <v>-13090.04790224941</v>
       </c>
       <c r="D85">
-        <v>5120.294174150625</v>
+        <v>6265.711097750597</v>
       </c>
       <c r="E85">
         <v>10989.959</v>
@@ -8263,45 +8263,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M85">
-        <v>5146.722382200001</v>
+        <v>4204.482727200001</v>
       </c>
       <c r="N85">
-        <v>-4276.222382200001</v>
+        <v>-3333.982727200001</v>
       </c>
       <c r="O85">
-        <v>-940.7689240840003</v>
+        <v>-733.4761999840002</v>
       </c>
       <c r="P85">
-        <v>-3335.453458116001</v>
+        <v>-2600.506527216001</v>
       </c>
       <c r="Q85">
-        <v>-1743.253458116001</v>
+        <v>-1008.306527216001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1773880140801312</v>
+        <v>0.1763642342333783</v>
       </c>
       <c r="T85">
-        <v>3.037030362278012</v>
+        <v>3.015340282526057</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03721008940803559</v>
+        <v>0.0455490038670077</v>
       </c>
       <c r="W85">
-        <v>0.2366537600235049</v>
+        <v>0.1916537600235049</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.1691367700365254</v>
+        <v>0.2070409266682169</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2285785832131313</v>
+        <v>0.1906045406391833</v>
       </c>
       <c r="C86">
-        <v>-14537.16557157413</v>
+        <v>-13399.71211434104</v>
       </c>
       <c r="D86">
-        <v>5070.866428425873</v>
+        <v>6208.319885658964</v>
       </c>
       <c r="E86">
         <v>11242.232</v>
@@ -8345,45 +8345,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M86">
-        <v>5208.7310856</v>
+        <v>4255.1391456</v>
       </c>
       <c r="N86">
-        <v>-4338.2310856</v>
+        <v>-3384.6391456</v>
       </c>
       <c r="O86">
-        <v>-954.4108388320001</v>
+        <v>-744.6206120320001</v>
       </c>
       <c r="P86">
-        <v>-3383.820246768</v>
+        <v>-2640.018533568</v>
       </c>
       <c r="Q86">
-        <v>-1791.620246768</v>
+        <v>-1047.818533568</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1856122649601394</v>
+        <v>0.1845244988729643</v>
       </c>
       <c r="T86">
-        <v>3.226844759920386</v>
+        <v>3.203799050183934</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03676711215317802</v>
+        <v>0.04500675382097191</v>
       </c>
       <c r="W86">
-        <v>0.2367626438327488</v>
+        <v>0.1917626438327488</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.1671232370599002</v>
+        <v>0.2045761537316906</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2305785832131313</v>
+        <v>0.1921545406391833</v>
       </c>
       <c r="C87">
-        <v>-14837.92115928639</v>
+        <v>-13708.33451149312</v>
       </c>
       <c r="D87">
-        <v>5022.383840713607</v>
+        <v>6151.970488506879</v>
       </c>
       <c r="E87">
         <v>11494.505</v>
@@ -8427,45 +8427,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M87">
-        <v>5270.739789000001</v>
+        <v>4305.795564000001</v>
       </c>
       <c r="N87">
-        <v>-4400.239789000001</v>
+        <v>-3435.295564000001</v>
       </c>
       <c r="O87">
-        <v>-968.0527535800003</v>
+        <v>-755.7650240800002</v>
       </c>
       <c r="P87">
-        <v>-3432.187035420001</v>
+        <v>-2679.530539920001</v>
       </c>
       <c r="Q87">
-        <v>-1839.987035420001</v>
+        <v>-1087.330539920001</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1949330826241487</v>
+        <v>0.1937727987978287</v>
       </c>
       <c r="T87">
-        <v>3.441967743915079</v>
+        <v>3.41738565352953</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0363345578925524</v>
+        <v>0.04447726259954871</v>
       </c>
       <c r="W87">
-        <v>0.2368689656700106</v>
+        <v>0.1918689656700106</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.1651570813297837</v>
+        <v>0.2021693754524941</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2325785832131313</v>
+        <v>0.2239339875155095</v>
       </c>
       <c r="C88">
-        <v>-15137.75844222832</v>
+        <v>-14925.82539096335</v>
       </c>
       <c r="D88">
-        <v>4974.819557771679</v>
+        <v>5186.752609036651</v>
       </c>
       <c r="E88">
         <v>11746.778</v>
@@ -8509,37 +8509,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M88">
-        <v>5332.748492400001</v>
+        <v>5115.793712400001</v>
       </c>
       <c r="N88">
-        <v>-4462.248492400001</v>
+        <v>-4245.293712400001</v>
       </c>
       <c r="O88">
-        <v>-981.6946683280003</v>
+        <v>-933.9646167280002</v>
       </c>
       <c r="P88">
-        <v>-3480.553824072001</v>
+        <v>-3311.329095672001</v>
       </c>
       <c r="Q88">
-        <v>-1888.353824072001</v>
+        <v>-1719.129095672001</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2055854456687307</v>
+        <v>0.2052669049714318</v>
       </c>
       <c r="T88">
-        <v>3.687822582766156</v>
+        <v>3.682838451996115</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03591206303333667</v>
+        <v>0.03743505128750702</v>
       </c>
       <c r="W88">
-        <v>0.2369728149064058</v>
+        <v>0.2269728149064059</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1632366501515303</v>
+        <v>0.1701593240341228</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2345785832131314</v>
+        <v>0.2258339875155095</v>
       </c>
       <c r="C89">
-        <v>-15436.70326593532</v>
+        <v>-15226.29972697628</v>
       </c>
       <c r="D89">
-        <v>4928.14773406468</v>
+        <v>5138.551273023726</v>
       </c>
       <c r="E89">
         <v>11999.051</v>
@@ -8591,37 +8591,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M89">
-        <v>5394.757195800002</v>
+        <v>5175.279685800001</v>
       </c>
       <c r="N89">
-        <v>-4524.257195800002</v>
+        <v>-4304.779685800001</v>
       </c>
       <c r="O89">
-        <v>-995.3365830760004</v>
+        <v>-947.0515308760002</v>
       </c>
       <c r="P89">
-        <v>-3528.920612724001</v>
+        <v>-3357.728154924001</v>
       </c>
       <c r="Q89">
-        <v>-1936.720612724001</v>
+        <v>-1765.528154924001</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2178766337970946</v>
+        <v>0.2175335899692342</v>
       </c>
       <c r="T89">
-        <v>3.971501242978937</v>
+        <v>3.966133717534277</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03549928069962015</v>
+        <v>0.0370047633416736</v>
       </c>
       <c r="W89">
-        <v>0.2370742768040334</v>
+        <v>0.2270742768040334</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1613603668164553</v>
+        <v>0.1682034697348801</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2365785832131314</v>
+        <v>0.2277339875155095</v>
       </c>
       <c r="C90">
-        <v>-15734.7805150663</v>
+        <v>-15525.88642622379</v>
       </c>
       <c r="D90">
-        <v>4882.343484933699</v>
+        <v>5091.237573776209</v>
       </c>
       <c r="E90">
         <v>12251.324</v>
@@ -8673,37 +8673,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M90">
-        <v>5456.765899200001</v>
+        <v>5234.7656592</v>
       </c>
       <c r="N90">
-        <v>-4586.265899200001</v>
+        <v>-4364.2656592</v>
       </c>
       <c r="O90">
-        <v>-1008.978497824</v>
+        <v>-960.138445024</v>
       </c>
       <c r="P90">
-        <v>-3577.287401376001</v>
+        <v>-3404.127214176</v>
       </c>
       <c r="Q90">
-        <v>-1985.087401376001</v>
+        <v>-1811.927214176</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2322163532801859</v>
+        <v>0.2318447224666704</v>
       </c>
       <c r="T90">
-        <v>4.302459679893849</v>
+        <v>4.296644860662134</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03509587978257903</v>
+        <v>0.0365842546673364</v>
       </c>
       <c r="W90">
-        <v>0.2371734327494421</v>
+        <v>0.2271734327494421</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1595267262844502</v>
+        <v>0.166292066669711</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2385785832131314</v>
+        <v>0.2296339875155095</v>
       </c>
       <c r="C91">
-        <v>-16032.01415764638</v>
+        <v>-15824.60978400428</v>
       </c>
       <c r="D91">
-        <v>4837.382842353619</v>
+        <v>5044.787215995725</v>
       </c>
       <c r="E91">
         <v>12503.597</v>
@@ -8755,37 +8755,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M91">
-        <v>5518.774602600001</v>
+        <v>5294.2516326</v>
       </c>
       <c r="N91">
-        <v>-4648.274602600001</v>
+        <v>-4423.7516326</v>
       </c>
       <c r="O91">
-        <v>-1022.620412572</v>
+        <v>-973.2253591720001</v>
       </c>
       <c r="P91">
-        <v>-3625.654190028001</v>
+        <v>-3450.526273428</v>
       </c>
       <c r="Q91">
-        <v>-2033.454190028001</v>
+        <v>-1858.326273428</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2491632944874755</v>
+        <v>0.2487578790545495</v>
       </c>
       <c r="T91">
-        <v>4.693592378066017</v>
+        <v>4.687248938904146</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03470154405468488</v>
+        <v>0.03617319562613037</v>
       </c>
       <c r="W91">
-        <v>0.2372703604713585</v>
+        <v>0.2272703604713585</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1577342911576586</v>
+        <v>0.1644236164824109</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2405785832131313</v>
+        <v>0.2315339875155095</v>
       </c>
       <c r="C92">
-        <v>-16328.42728688736</v>
+        <v>-16122.4932169911</v>
       </c>
       <c r="D92">
-        <v>4793.242713112644</v>
+        <v>4999.176783008906</v>
       </c>
       <c r="E92">
         <v>12755.87</v>
@@ -8837,37 +8837,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M92">
-        <v>5580.783306000001</v>
+        <v>5353.737606000001</v>
       </c>
       <c r="N92">
-        <v>-4710.283306000001</v>
+        <v>-4483.237606000001</v>
       </c>
       <c r="O92">
-        <v>-1036.26232732</v>
+        <v>-986.3122733200001</v>
       </c>
       <c r="P92">
-        <v>-3674.020978680001</v>
+        <v>-3496.92533268</v>
       </c>
       <c r="Q92">
-        <v>-2081.820978680001</v>
+        <v>-1904.72533268</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2694996239362231</v>
+        <v>0.2690536669600045</v>
       </c>
       <c r="T92">
-        <v>5.16295161587262</v>
+        <v>5.155973832794562</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03431597134296615</v>
+        <v>0.03577127123028449</v>
       </c>
       <c r="W92">
-        <v>0.2373651342438989</v>
+        <v>0.2273651342438989</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1559816879225735</v>
+        <v>0.162596687410384</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2425785832131314</v>
+        <v>0.2334339875155095</v>
       </c>
       <c r="C93">
-        <v>-16624.04216073929</v>
+        <v>-16419.55930259537</v>
       </c>
       <c r="D93">
-        <v>4749.900839260714</v>
+        <v>4954.383697404634</v>
       </c>
       <c r="E93">
         <v>13008.143</v>
@@ -8919,37 +8919,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M93">
-        <v>5642.792009400002</v>
+        <v>5413.223579400002</v>
       </c>
       <c r="N93">
-        <v>-4772.292009400002</v>
+        <v>-4542.723579400002</v>
       </c>
       <c r="O93">
-        <v>-1049.904242068</v>
+        <v>-999.3991874680004</v>
       </c>
       <c r="P93">
-        <v>-3722.387767332001</v>
+        <v>-3543.324391932001</v>
       </c>
       <c r="Q93">
-        <v>-2130.187767332001</v>
+        <v>-1951.124391932001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2943551377069145</v>
+        <v>0.2938596299555606</v>
       </c>
       <c r="T93">
-        <v>5.736612906525133</v>
+        <v>5.728859814216181</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0339388727567797</v>
+        <v>0.03537818033764399</v>
       </c>
       <c r="W93">
-        <v>0.2374578250763835</v>
+        <v>0.2274578250763836</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1542676034399078</v>
+        <v>0.1608099106256545</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2445785832131314</v>
+        <v>0.2353339875155095</v>
       </c>
       <c r="C94">
-        <v>-16918.88023931545</v>
+        <v>-16715.82981623145</v>
       </c>
       <c r="D94">
-        <v>4707.335760684548</v>
+        <v>4910.386183768557</v>
       </c>
       <c r="E94">
         <v>13260.416</v>
@@ -9001,37 +9001,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M94">
-        <v>5704.800712800002</v>
+        <v>5472.709552800002</v>
       </c>
       <c r="N94">
-        <v>-4834.300712800002</v>
+        <v>-4602.209552800002</v>
       </c>
       <c r="O94">
-        <v>-1063.546156816</v>
+        <v>-1012.486101616</v>
       </c>
       <c r="P94">
-        <v>-3770.754555984001</v>
+        <v>-3589.723451184002</v>
       </c>
       <c r="Q94">
-        <v>-2178.554555984001</v>
+        <v>-1997.523451184001</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3254245299202789</v>
+        <v>0.3248670837000058</v>
       </c>
       <c r="T94">
-        <v>6.453689519840777</v>
+        <v>6.444967290993205</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03356997196594515</v>
+        <v>0.03499363489919134</v>
       </c>
       <c r="W94">
-        <v>0.2375485008907707</v>
+        <v>0.2275485008907707</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.152590781663387</v>
+        <v>0.1590619768145061</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2465785832131313</v>
+        <v>0.2372339875155095</v>
       </c>
       <c r="C95">
-        <v>-17212.96222032296</v>
+        <v>-17011.32576661417</v>
       </c>
       <c r="D95">
-        <v>4665.526779677046</v>
+        <v>4867.163233385833</v>
       </c>
       <c r="E95">
         <v>13512.689</v>
@@ -9083,37 +9083,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M95">
-        <v>5766.809416200002</v>
+        <v>5532.195526200001</v>
       </c>
       <c r="N95">
-        <v>-4896.309416200002</v>
+        <v>-4661.695526200001</v>
       </c>
       <c r="O95">
-        <v>-1077.188071564</v>
+        <v>-1025.573015764</v>
       </c>
       <c r="P95">
-        <v>-3819.121344636001</v>
+        <v>-3636.122510436001</v>
       </c>
       <c r="Q95">
-        <v>-2226.921344636001</v>
+        <v>-2043.922510436001</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3653708913374616</v>
+        <v>0.3647338099428638</v>
       </c>
       <c r="T95">
-        <v>7.375645165532317</v>
+        <v>7.365676903992235</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03320900452545111</v>
+        <v>0.03461735925511401</v>
       </c>
       <c r="W95">
-        <v>0.2376372266876441</v>
+        <v>0.2276372266876441</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1509500205702323</v>
+        <v>0.157351632977791</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2485785832131314</v>
+        <v>0.2391339875155095</v>
       </c>
       <c r="C96">
-        <v>-17506.30807262183</v>
+        <v>-17306.06742920825</v>
       </c>
       <c r="D96">
-        <v>4624.453927378171</v>
+        <v>4824.694570791748</v>
       </c>
       <c r="E96">
         <v>13764.962</v>
@@ -9165,37 +9165,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M96">
-        <v>5828.818119600001</v>
+        <v>5591.681499600001</v>
       </c>
       <c r="N96">
-        <v>-4958.318119600001</v>
+        <v>-4721.181499600001</v>
       </c>
       <c r="O96">
-        <v>-1090.829986312</v>
+        <v>-1038.659929912</v>
       </c>
       <c r="P96">
-        <v>-3867.488133288001</v>
+        <v>-3682.521569688001</v>
       </c>
       <c r="Q96">
-        <v>-2275.288133288002</v>
+        <v>-2090.321569688001</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.418632706560372</v>
+        <v>0.4178894449333412</v>
       </c>
       <c r="T96">
-        <v>8.604919359787706</v>
+        <v>8.593289721324277</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03285571724326546</v>
+        <v>0.03424908947580429</v>
       </c>
       <c r="W96">
-        <v>0.2377240647016054</v>
+        <v>0.2277240647016054</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1493441692875703</v>
+        <v>0.1556776794354741</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2505785832131314</v>
+        <v>0.2410339875155095</v>
       </c>
       <c r="C97">
-        <v>-17798.93706802704</v>
+        <v>-17600.07437794161</v>
       </c>
       <c r="D97">
-        <v>4584.097931972966</v>
+        <v>4782.960622058393</v>
       </c>
       <c r="E97">
         <v>14017.235</v>
@@ -9247,37 +9247,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M97">
-        <v>5890.826823000001</v>
+        <v>5651.167473000001</v>
       </c>
       <c r="N97">
-        <v>-5020.326823000001</v>
+        <v>-4780.667473000001</v>
       </c>
       <c r="O97">
-        <v>-1104.47190106</v>
+        <v>-1051.74684406</v>
       </c>
       <c r="P97">
-        <v>-3915.854921940001</v>
+        <v>-3728.920628940001</v>
       </c>
       <c r="Q97">
-        <v>-2323.654921940001</v>
+        <v>-2136.720628940001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4931992478724467</v>
+        <v>0.4923073339200096</v>
       </c>
       <c r="T97">
-        <v>10.32590323174525</v>
+        <v>10.31194766558914</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0325098675880732</v>
+        <v>0.03388857274448003</v>
       </c>
       <c r="W97">
-        <v>0.2378090745468516</v>
+        <v>0.2278090745468516</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1477721254003328</v>
+        <v>0.1540389670203638</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2525785832131314</v>
+        <v>0.2429339875155095</v>
       </c>
       <c r="C98">
-        <v>-18090.86781145966</v>
+        <v>-17893.36551528684</v>
       </c>
       <c r="D98">
-        <v>4544.440188540339</v>
+        <v>4741.942484713161</v>
       </c>
       <c r="E98">
         <v>14269.508</v>
@@ -9329,37 +9329,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M98">
-        <v>5952.835526400001</v>
+        <v>5710.653446400001</v>
       </c>
       <c r="N98">
-        <v>-5082.335526400001</v>
+        <v>-4840.153446400001</v>
       </c>
       <c r="O98">
-        <v>-1118.113815808</v>
+        <v>-1064.833758208</v>
       </c>
       <c r="P98">
-        <v>-3964.221710592001</v>
+        <v>-3775.319688192</v>
       </c>
       <c r="Q98">
-        <v>-2372.021710592001</v>
+        <v>-2183.119688192</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.605049059840557</v>
+        <v>0.6039341674000106</v>
       </c>
       <c r="T98">
-        <v>12.90737903968154</v>
+        <v>12.88993458198639</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03217122313403077</v>
+        <v>0.03353556677839171</v>
       </c>
       <c r="W98">
-        <v>0.2378923133536553</v>
+        <v>0.2278923133536552</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1462328324274126</v>
+        <v>0.1524343944472351</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2545785832131313</v>
+        <v>0.2448339875155095</v>
       </c>
       <c r="C99">
-        <v>-18382.11826954653</v>
+        <v>-18185.95910080808</v>
       </c>
       <c r="D99">
-        <v>4505.46273045347</v>
+        <v>4701.62189919192</v>
       </c>
       <c r="E99">
         <v>14521.781</v>
@@ -9411,37 +9411,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M99">
-        <v>6014.844229800001</v>
+        <v>5770.139419800001</v>
       </c>
       <c r="N99">
-        <v>-5144.344229800001</v>
+        <v>-4899.639419800001</v>
       </c>
       <c r="O99">
-        <v>-1131.755730556</v>
+        <v>-1077.920672356</v>
       </c>
       <c r="P99">
-        <v>-4012.588499244001</v>
+        <v>-3821.718747444001</v>
       </c>
       <c r="Q99">
-        <v>-2420.388499244001</v>
+        <v>-2229.518747444001</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7914654131207428</v>
+        <v>0.789978889866681</v>
       </c>
       <c r="T99">
-        <v>17.20983871957538</v>
+        <v>17.18657944264852</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03183956103986551</v>
+        <v>0.03318983928583096</v>
       </c>
       <c r="W99">
-        <v>0.2379738358964011</v>
+        <v>0.2279738358964011</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1447252774539342</v>
+        <v>0.1508629058446862</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2565785832131314</v>
+        <v>0.2467339875155095</v>
       </c>
       <c r="C100">
-        <v>-18672.70579776053</v>
+        <v>-18477.87277826366</v>
       </c>
       <c r="D100">
-        <v>4467.148202239476</v>
+        <v>4661.98122173634</v>
       </c>
       <c r="E100">
         <v>14774.054</v>
@@ -9493,37 +9493,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M100">
-        <v>6076.852933200001</v>
+        <v>5829.625393200001</v>
       </c>
       <c r="N100">
-        <v>-5206.352933200001</v>
+        <v>-4959.125393200001</v>
       </c>
       <c r="O100">
-        <v>-1145.397645304</v>
+        <v>-1091.007586504</v>
       </c>
       <c r="P100">
-        <v>-4060.955287896</v>
+        <v>-3868.117806696001</v>
       </c>
       <c r="Q100">
-        <v>-2468.755287896</v>
+        <v>-2275.917806696</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.164298119681114</v>
+        <v>1.162068334800021</v>
       </c>
       <c r="T100">
-        <v>25.81475807936307</v>
+        <v>25.77986916397278</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03151466755986688</v>
+        <v>0.03285116745638371</v>
       </c>
       <c r="W100">
-        <v>0.2380536947137847</v>
+        <v>0.2280536947137847</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1432484889084858</v>
+        <v>0.1493234884381078</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2585785832131314</v>
+        <v>0.2486339875155095</v>
       </c>
       <c r="C101">
-        <v>-18962.64716618776</v>
+        <v>-18769.12360134923</v>
       </c>
       <c r="D101">
-        <v>4429.47983381224</v>
+        <v>4623.00339865077</v>
       </c>
       <c r="E101">
         <v>15026.327</v>
@@ -9575,37 +9575,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M101">
-        <v>6138.861636600001</v>
+        <v>5889.111366600001</v>
       </c>
       <c r="N101">
-        <v>-5268.361636600001</v>
+        <v>-5018.611366600001</v>
       </c>
       <c r="O101">
-        <v>-1159.039560052</v>
+        <v>-1104.094500652</v>
       </c>
       <c r="P101">
-        <v>-4109.322076548</v>
+        <v>-3914.516865948</v>
       </c>
       <c r="Q101">
-        <v>-2517.122076548</v>
+        <v>-2322.316865948001</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.282796239362228</v>
+        <v>2.278336669600042</v>
       </c>
       <c r="T101">
-        <v>51.62951615872615</v>
+        <v>51.55973832794556</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.03119633758451469</v>
+        <v>0.0325193374820768</v>
       </c>
       <c r="W101">
-        <v>0.2381319402217263</v>
+        <v>0.2281319402217263</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1418015344750668</v>
+        <v>0.1478151703730765</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/norway/norway_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06886802191789448</v>
+        <v>0.06875161226967512</v>
       </c>
       <c r="C2">
-        <v>23707.24722273858</v>
+        <v>23509.34494810757</v>
       </c>
       <c r="D2">
-        <v>22124.34722273858</v>
+        <v>22178.71794810757</v>
       </c>
       <c r="E2">
-        <v>-9948.700000000001</v>
+        <v>-9696.427000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>252.273</v>
       </c>
       <c r="G2">
         <v>1582.9</v>
@@ -1457,28 +1457,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>12.6893319</v>
       </c>
       <c r="N2">
-        <v>870.4999999999998</v>
+        <v>857.8106680999998</v>
       </c>
       <c r="O2">
-        <v>191.51</v>
+        <v>188.718346982</v>
       </c>
       <c r="P2">
-        <v>678.9899999999998</v>
+        <v>669.0923211179999</v>
       </c>
       <c r="Q2">
-        <v>2271.19</v>
+        <v>2261.292321118</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06886802191789448</v>
+        <v>0.0690497699693688</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5369461886690254</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>68.60093241000338</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06875161226967512</v>
+        <v>0.06863520262145574</v>
       </c>
       <c r="C3">
-        <v>23509.34494810757</v>
+        <v>23311.71056463428</v>
       </c>
       <c r="D3">
-        <v>22178.71794810757</v>
+        <v>22233.35656463428</v>
       </c>
       <c r="E3">
-        <v>-9696.427000000001</v>
+        <v>-9444.154</v>
       </c>
       <c r="F3">
-        <v>252.273</v>
+        <v>504.546</v>
       </c>
       <c r="G3">
         <v>1582.9</v>
@@ -1539,28 +1539,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M3">
-        <v>12.6893319</v>
+        <v>25.3786638</v>
       </c>
       <c r="N3">
-        <v>857.8106680999998</v>
+        <v>845.1213361999997</v>
       </c>
       <c r="O3">
-        <v>188.718346982</v>
+        <v>185.926693964</v>
       </c>
       <c r="P3">
-        <v>669.0923211179999</v>
+        <v>659.1946422359998</v>
       </c>
       <c r="Q3">
-        <v>2261.292321118</v>
+        <v>2251.394642236</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0690497699693688</v>
+        <v>0.06923522716475076</v>
       </c>
       <c r="T3">
-        <v>0.5369461886690254</v>
+        <v>0.5412292647748445</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>68.60093241000338</v>
+        <v>34.30046620500168</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06863520262145574</v>
+        <v>0.06851879297323638</v>
       </c>
       <c r="C4">
-        <v>23311.71056463428</v>
+        <v>23114.34605710666</v>
       </c>
       <c r="D4">
-        <v>22233.35656463428</v>
+        <v>22288.26505710666</v>
       </c>
       <c r="E4">
-        <v>-9444.154</v>
+        <v>-9191.881000000001</v>
       </c>
       <c r="F4">
-        <v>504.546</v>
+        <v>756.8190000000001</v>
       </c>
       <c r="G4">
         <v>1582.9</v>
@@ -1621,28 +1621,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M4">
-        <v>25.3786638</v>
+        <v>38.0679957</v>
       </c>
       <c r="N4">
-        <v>845.1213361999997</v>
+        <v>832.4320042999998</v>
       </c>
       <c r="O4">
-        <v>185.926693964</v>
+        <v>183.1350409459999</v>
       </c>
       <c r="P4">
-        <v>659.1946422359998</v>
+        <v>649.2969633539999</v>
       </c>
       <c r="Q4">
-        <v>2251.394642236</v>
+        <v>2241.496963354</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06923522716475076</v>
+        <v>0.06942450821983132</v>
       </c>
       <c r="T4">
-        <v>0.5412292647748445</v>
+        <v>0.545600651728206</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.30046620500168</v>
+        <v>22.86697747000112</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06851879297323638</v>
+        <v>0.06840238332501701</v>
       </c>
       <c r="C5">
-        <v>23114.34605710666</v>
+        <v>22917.25342996812</v>
       </c>
       <c r="D5">
-        <v>22288.26505710666</v>
+        <v>22343.44542996812</v>
       </c>
       <c r="E5">
-        <v>-9191.881000000001</v>
+        <v>-8939.608</v>
       </c>
       <c r="F5">
-        <v>756.8190000000001</v>
+        <v>1009.092</v>
       </c>
       <c r="G5">
         <v>1582.9</v>
@@ -1703,28 +1703,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M5">
-        <v>38.0679957</v>
+        <v>50.7573276</v>
       </c>
       <c r="N5">
-        <v>832.4320042999998</v>
+        <v>819.7426723999997</v>
       </c>
       <c r="O5">
-        <v>183.1350409459999</v>
+        <v>180.3433879279999</v>
       </c>
       <c r="P5">
-        <v>649.2969633539999</v>
+        <v>639.3992844719997</v>
       </c>
       <c r="Q5">
-        <v>2241.496963354</v>
+        <v>2231.599284472</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06942450821983132</v>
+        <v>0.06961773263022605</v>
       </c>
       <c r="T5">
-        <v>0.545600651728206</v>
+        <v>0.550063109243096</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.86697747000112</v>
+        <v>17.15023310250084</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06840238332501701</v>
+        <v>0.06828597367679765</v>
       </c>
       <c r="C6">
-        <v>22917.25342996812</v>
+        <v>22720.43470756142</v>
       </c>
       <c r="D6">
-        <v>22343.44542996812</v>
+        <v>22398.89970756142</v>
       </c>
       <c r="E6">
-        <v>-8939.608</v>
+        <v>-8687.335000000001</v>
       </c>
       <c r="F6">
-        <v>1009.092</v>
+        <v>1261.365</v>
       </c>
       <c r="G6">
         <v>1582.9</v>
@@ -1785,28 +1785,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M6">
-        <v>50.7573276</v>
+        <v>63.44665950000001</v>
       </c>
       <c r="N6">
-        <v>819.7426723999997</v>
+        <v>807.0533404999998</v>
       </c>
       <c r="O6">
-        <v>180.3433879279999</v>
+        <v>177.5517349099999</v>
       </c>
       <c r="P6">
-        <v>639.3992844719997</v>
+        <v>629.5016055899998</v>
       </c>
       <c r="Q6">
-        <v>2231.599284472</v>
+        <v>2221.70160559</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06961773263022605</v>
+        <v>0.06981502492294489</v>
       </c>
       <c r="T6">
-        <v>0.550063109243096</v>
+        <v>0.5546195132319837</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.15023310250084</v>
+        <v>13.72018648200067</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06828597367679765</v>
+        <v>0.06816956402857828</v>
       </c>
       <c r="C7">
-        <v>22720.43470756142</v>
+        <v>22523.8919343762</v>
       </c>
       <c r="D7">
-        <v>22398.89970756142</v>
+        <v>22454.6299343762</v>
       </c>
       <c r="E7">
-        <v>-8687.335000000001</v>
+        <v>-8435.062</v>
       </c>
       <c r="F7">
-        <v>1261.365</v>
+        <v>1513.638</v>
       </c>
       <c r="G7">
         <v>1582.9</v>
@@ -1867,28 +1867,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M7">
-        <v>63.44665950000001</v>
+        <v>76.13599140000001</v>
       </c>
       <c r="N7">
-        <v>807.0533404999998</v>
+        <v>794.3640085999998</v>
       </c>
       <c r="O7">
-        <v>177.5517349099999</v>
+        <v>174.760081892</v>
       </c>
       <c r="P7">
-        <v>629.5016055899998</v>
+        <v>619.6039267079998</v>
       </c>
       <c r="Q7">
-        <v>2221.70160559</v>
+        <v>2211.803926708</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06981502492294489</v>
+        <v>0.07001651492401945</v>
       </c>
       <c r="T7">
-        <v>0.5546195132319837</v>
+        <v>0.5592728619865922</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.72018648200067</v>
+        <v>11.43348873500056</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06816956402857828</v>
+        <v>0.06805315438035892</v>
       </c>
       <c r="C8">
-        <v>22523.8919343762</v>
+        <v>22327.62717530025</v>
       </c>
       <c r="D8">
-        <v>22454.6299343762</v>
+        <v>22510.63817530025</v>
       </c>
       <c r="E8">
-        <v>-8435.062</v>
+        <v>-8182.789000000001</v>
       </c>
       <c r="F8">
-        <v>1513.638</v>
+        <v>1765.911</v>
       </c>
       <c r="G8">
         <v>1582.9</v>
@@ -1949,28 +1949,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M8">
-        <v>76.13599140000001</v>
+        <v>88.82532329999999</v>
       </c>
       <c r="N8">
-        <v>794.3640085999998</v>
+        <v>781.6746766999997</v>
       </c>
       <c r="O8">
-        <v>174.760081892</v>
+        <v>171.968428874</v>
       </c>
       <c r="P8">
-        <v>619.6039267079998</v>
+        <v>609.7062478259998</v>
       </c>
       <c r="Q8">
-        <v>2211.803926708</v>
+        <v>2201.906247826</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07001651492401945</v>
+        <v>0.07022233804339667</v>
       </c>
       <c r="T8">
-        <v>0.5592728619865922</v>
+        <v>0.5640262827574289</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.43348873500056</v>
+        <v>9.800133201429055</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0680531543803589</v>
+        <v>0.06803034473213955</v>
       </c>
       <c r="C9">
-        <v>22327.62717530026</v>
+        <v>22086.36134739576</v>
       </c>
       <c r="D9">
-        <v>22510.63817530026</v>
+        <v>22521.64534739576</v>
       </c>
       <c r="E9">
-        <v>-8182.789000000001</v>
+        <v>-7930.516000000001</v>
       </c>
       <c r="F9">
-        <v>1765.911</v>
+        <v>2018.184</v>
       </c>
       <c r="G9">
         <v>1582.9</v>
@@ -2031,45 +2031,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M9">
-        <v>88.82532330000001</v>
+        <v>104.5419312</v>
       </c>
       <c r="N9">
-        <v>781.6746766999997</v>
+        <v>765.9580687999998</v>
       </c>
       <c r="O9">
-        <v>171.968428874</v>
+        <v>168.5107751359999</v>
       </c>
       <c r="P9">
-        <v>609.7062478259998</v>
+        <v>597.4472936639997</v>
       </c>
       <c r="Q9">
-        <v>2201.906247826</v>
+        <v>2189.647293664</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07022233804339667</v>
+        <v>0.07043263557841255</v>
       </c>
       <c r="T9">
-        <v>0.5640262827574291</v>
+        <v>0.5688830387624144</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.800133201429054</v>
+        <v>8.326802365403402</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06803034473213955</v>
+        <v>0.06792563508392019</v>
       </c>
       <c r="C10">
-        <v>22086.36134739576</v>
+        <v>21884.75615691423</v>
       </c>
       <c r="D10">
-        <v>22521.64534739576</v>
+        <v>22572.31315691422</v>
       </c>
       <c r="E10">
-        <v>-7930.516000000001</v>
+        <v>-7678.243</v>
       </c>
       <c r="F10">
-        <v>2018.184</v>
+        <v>2270.457</v>
       </c>
       <c r="G10">
         <v>1582.9</v>
@@ -2113,28 +2113,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M10">
-        <v>104.5419312</v>
+        <v>117.6096726</v>
       </c>
       <c r="N10">
-        <v>765.9580687999998</v>
+        <v>752.8903273999997</v>
       </c>
       <c r="O10">
-        <v>168.5107751359999</v>
+        <v>165.6358720279999</v>
       </c>
       <c r="P10">
-        <v>597.4472936639997</v>
+        <v>587.2544553719997</v>
       </c>
       <c r="Q10">
-        <v>2189.647293664</v>
+        <v>2179.454455372</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07043263557841255</v>
+        <v>0.07064755503727492</v>
       </c>
       <c r="T10">
-        <v>0.5688830387624144</v>
+        <v>0.5738465366576193</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.326802365403402</v>
+        <v>7.401602102580801</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06792563508392019</v>
+        <v>0.06795352543570081</v>
       </c>
       <c r="C11">
-        <v>21884.75615691423</v>
+        <v>21618.96507093231</v>
       </c>
       <c r="D11">
-        <v>22572.31315691422</v>
+        <v>22558.7950709323</v>
       </c>
       <c r="E11">
-        <v>-7678.243</v>
+        <v>-7425.970000000001</v>
       </c>
       <c r="F11">
-        <v>2270.457</v>
+        <v>2522.73</v>
       </c>
       <c r="G11">
         <v>1582.9</v>
@@ -2195,45 +2195,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M11">
-        <v>117.6096726</v>
+        <v>134.966055</v>
       </c>
       <c r="N11">
-        <v>752.8903273999997</v>
+        <v>735.5339449999998</v>
       </c>
       <c r="O11">
-        <v>165.6358720279999</v>
+        <v>161.8174679</v>
       </c>
       <c r="P11">
-        <v>587.2544553719997</v>
+        <v>573.7164770999998</v>
       </c>
       <c r="Q11">
-        <v>2179.454455372</v>
+        <v>2165.9164771</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07064755503727492</v>
+        <v>0.07086725048411201</v>
       </c>
       <c r="T11">
-        <v>0.5738465366576193</v>
+        <v>0.578920334506051</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.401602102580801</v>
+        <v>6.449769906959196</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06795352543570081</v>
+        <v>0.06786207578748145</v>
       </c>
       <c r="C12">
-        <v>21618.96507093231</v>
+        <v>21411.0771226935</v>
       </c>
       <c r="D12">
-        <v>22558.7950709323</v>
+        <v>22603.1801226935</v>
       </c>
       <c r="E12">
-        <v>-7425.97</v>
+        <v>-7173.697</v>
       </c>
       <c r="F12">
-        <v>2522.73</v>
+        <v>2775.003</v>
       </c>
       <c r="G12">
         <v>1582.9</v>
@@ -2277,28 +2277,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M12">
-        <v>134.966055</v>
+        <v>148.4626605</v>
       </c>
       <c r="N12">
-        <v>735.5339449999998</v>
+        <v>722.0373394999998</v>
       </c>
       <c r="O12">
-        <v>161.8174679</v>
+        <v>158.84821469</v>
       </c>
       <c r="P12">
-        <v>573.7164770999998</v>
+        <v>563.1891248099998</v>
       </c>
       <c r="Q12">
-        <v>2165.9164771</v>
+        <v>2155.38912481</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07086725048411201</v>
+        <v>0.07109188290728252</v>
       </c>
       <c r="T12">
-        <v>0.578920334506051</v>
+        <v>0.5841081502836609</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.449769906959196</v>
+        <v>5.863427188144724</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06786207578748145</v>
+        <v>0.06784550613926207</v>
       </c>
       <c r="C13">
-        <v>21411.0771226935</v>
+        <v>21166.86489172902</v>
       </c>
       <c r="D13">
-        <v>22603.1801226935</v>
+        <v>22611.24089172902</v>
       </c>
       <c r="E13">
-        <v>-7173.697</v>
+        <v>-6921.424000000001</v>
       </c>
       <c r="F13">
-        <v>2775.003</v>
+        <v>3027.276</v>
       </c>
       <c r="G13">
         <v>1582.9</v>
@@ -2359,45 +2359,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M13">
-        <v>148.4626605</v>
+        <v>164.3810868</v>
       </c>
       <c r="N13">
-        <v>722.0373394999998</v>
+        <v>706.1189131999997</v>
       </c>
       <c r="O13">
-        <v>158.84821469</v>
+        <v>155.3461609039999</v>
       </c>
       <c r="P13">
-        <v>563.1891248099998</v>
+        <v>550.7727522959998</v>
       </c>
       <c r="Q13">
-        <v>2155.38912481</v>
+        <v>2142.972752296</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07109188290728252</v>
+        <v>0.07132162061279781</v>
       </c>
       <c r="T13">
-        <v>0.5841081502836609</v>
+        <v>0.5894138709653074</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.863427188144724</v>
+        <v>5.295621393835435</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06784550613926207</v>
+        <v>0.0677602964910427</v>
       </c>
       <c r="C14">
-        <v>21166.86489172902</v>
+        <v>20956.13548032788</v>
       </c>
       <c r="D14">
-        <v>22611.24089172902</v>
+        <v>22652.78448032788</v>
       </c>
       <c r="E14">
-        <v>-6921.424000000001</v>
+        <v>-6669.151</v>
       </c>
       <c r="F14">
-        <v>3027.276</v>
+        <v>3279.549</v>
       </c>
       <c r="G14">
         <v>1582.9</v>
@@ -2441,28 +2441,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M14">
-        <v>164.3810868</v>
+        <v>178.0795107</v>
       </c>
       <c r="N14">
-        <v>706.1189131999997</v>
+        <v>692.4204892999998</v>
       </c>
       <c r="O14">
-        <v>155.3461609039999</v>
+        <v>152.332507646</v>
       </c>
       <c r="P14">
-        <v>550.7727522959998</v>
+        <v>540.0879816539998</v>
       </c>
       <c r="Q14">
-        <v>2142.972752296</v>
+        <v>2132.287981654</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07132162061279781</v>
+        <v>0.07155663964487667</v>
       </c>
       <c r="T14">
-        <v>0.5894138709653074</v>
+        <v>0.5948415622373364</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.295621393835435</v>
+        <v>4.88826590200194</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0677602964910427</v>
+        <v>0.06767508684282333</v>
       </c>
       <c r="C15">
-        <v>20956.13548032788</v>
+        <v>20745.55900582532</v>
       </c>
       <c r="D15">
-        <v>22652.78448032788</v>
+        <v>22694.48100582532</v>
       </c>
       <c r="E15">
-        <v>-6669.151</v>
+        <v>-6416.878000000001</v>
       </c>
       <c r="F15">
-        <v>3279.549</v>
+        <v>3531.822000000001</v>
       </c>
       <c r="G15">
         <v>1582.9</v>
@@ -2523,28 +2523,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M15">
-        <v>178.0795107</v>
+        <v>191.7779346</v>
       </c>
       <c r="N15">
-        <v>692.4204892999998</v>
+        <v>678.7220653999998</v>
       </c>
       <c r="O15">
-        <v>152.332507646</v>
+        <v>149.3188543879999</v>
       </c>
       <c r="P15">
-        <v>540.0879816539998</v>
+        <v>529.4032110119998</v>
       </c>
       <c r="Q15">
-        <v>2132.287981654</v>
+        <v>2121.603211012</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07155663964487667</v>
+        <v>0.07179712423584109</v>
       </c>
       <c r="T15">
-        <v>0.5948415622373364</v>
+        <v>0.6003954788877849</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.88826590200194</v>
+        <v>4.539104051858944</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06767508684282333</v>
+        <v>0.06770687719460397</v>
       </c>
       <c r="C16">
-        <v>20745.55900582532</v>
+        <v>20477.71176265923</v>
       </c>
       <c r="D16">
-        <v>22694.48100582532</v>
+        <v>22678.90676265923</v>
       </c>
       <c r="E16">
-        <v>-6416.878000000001</v>
+        <v>-6164.605</v>
       </c>
       <c r="F16">
-        <v>3531.822000000001</v>
+        <v>3784.095000000001</v>
       </c>
       <c r="G16">
         <v>1582.9</v>
@@ -2605,45 +2605,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M16">
-        <v>191.7779346</v>
+        <v>209.2604535000001</v>
       </c>
       <c r="N16">
-        <v>678.7220653999998</v>
+        <v>661.2395464999997</v>
       </c>
       <c r="O16">
-        <v>149.3188543879999</v>
+        <v>145.4727002299999</v>
       </c>
       <c r="P16">
-        <v>529.4032110119998</v>
+        <v>515.7668462699999</v>
       </c>
       <c r="Q16">
-        <v>2121.603211012</v>
+        <v>2107.96684627</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07179712423584109</v>
+        <v>0.07204326728776937</v>
       </c>
       <c r="T16">
-        <v>0.6003954788877849</v>
+        <v>0.6060800759300086</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.539104051858944</v>
+        <v>4.159887763982121</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06770687719460397</v>
+        <v>0.06762946754638459</v>
       </c>
       <c r="C17">
-        <v>20477.71176265923</v>
+        <v>20263.39952288748</v>
       </c>
       <c r="D17">
-        <v>22678.90676265923</v>
+        <v>22716.86752288748</v>
       </c>
       <c r="E17">
-        <v>-6164.605</v>
+        <v>-5912.332</v>
       </c>
       <c r="F17">
-        <v>3784.095</v>
+        <v>4036.368</v>
       </c>
       <c r="G17">
         <v>1582.9</v>
@@ -2687,28 +2687,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M17">
-        <v>209.2604535</v>
+        <v>223.2111504</v>
       </c>
       <c r="N17">
-        <v>661.2395464999997</v>
+        <v>647.2888495999997</v>
       </c>
       <c r="O17">
-        <v>145.4727002299999</v>
+        <v>142.4035469119999</v>
       </c>
       <c r="P17">
-        <v>515.7668462699999</v>
+        <v>504.8853026879998</v>
       </c>
       <c r="Q17">
-        <v>2107.96684627</v>
+        <v>2097.085302688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07204326728776937</v>
+        <v>0.07229527088855309</v>
       </c>
       <c r="T17">
-        <v>0.6060800759300086</v>
+        <v>0.6119000205208567</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.159887763982121</v>
+        <v>3.899894778733239</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06762946754638459</v>
+        <v>0.06755205789816522</v>
       </c>
       <c r="C18">
-        <v>20263.39952288748</v>
+        <v>20049.21457632308</v>
       </c>
       <c r="D18">
-        <v>22716.86752288748</v>
+        <v>22754.95557632307</v>
       </c>
       <c r="E18">
-        <v>-5912.332</v>
+        <v>-5660.059</v>
       </c>
       <c r="F18">
-        <v>4036.368</v>
+        <v>4288.641000000001</v>
       </c>
       <c r="G18">
         <v>1582.9</v>
@@ -2769,28 +2769,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M18">
-        <v>223.2111504</v>
+        <v>237.1618473</v>
       </c>
       <c r="N18">
-        <v>647.2888495999997</v>
+        <v>633.3381526999997</v>
       </c>
       <c r="O18">
-        <v>142.4035469119999</v>
+        <v>139.3343935939999</v>
       </c>
       <c r="P18">
-        <v>504.8853026879998</v>
+        <v>494.0037591059997</v>
       </c>
       <c r="Q18">
-        <v>2097.085302688</v>
+        <v>2086.203759106</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07229527088855309</v>
+        <v>0.07255334686525931</v>
       </c>
       <c r="T18">
-        <v>0.6119000205208567</v>
+        <v>0.6178602047403999</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.899894778733239</v>
+        <v>3.670489203513636</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06755205789816522</v>
+        <v>0.06747464824994587</v>
       </c>
       <c r="C19">
-        <v>20049.21457632308</v>
+        <v>19835.15756431674</v>
       </c>
       <c r="D19">
-        <v>22754.95557632307</v>
+        <v>22793.17156431674</v>
       </c>
       <c r="E19">
-        <v>-5660.059</v>
+        <v>-5407.786</v>
       </c>
       <c r="F19">
-        <v>4288.641000000001</v>
+        <v>4540.914000000001</v>
       </c>
       <c r="G19">
         <v>1582.9</v>
@@ -2851,28 +2851,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M19">
-        <v>237.1618473</v>
+        <v>251.1125442000001</v>
       </c>
       <c r="N19">
-        <v>633.3381526999997</v>
+        <v>619.3874557999998</v>
       </c>
       <c r="O19">
-        <v>139.3343935939999</v>
+        <v>136.265240276</v>
       </c>
       <c r="P19">
-        <v>494.0037591059997</v>
+        <v>483.1222155239998</v>
       </c>
       <c r="Q19">
-        <v>2086.203759106</v>
+        <v>2075.322215524</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07255334686525931</v>
+        <v>0.07281771737798276</v>
       </c>
       <c r="T19">
-        <v>0.6178602047403999</v>
+        <v>0.6239657593067612</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.670489203513636</v>
+        <v>3.466573136651768</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06747464824994587</v>
+        <v>0.0673972386017265</v>
       </c>
       <c r="C20">
-        <v>19835.15756431674</v>
+        <v>19621.22913253493</v>
       </c>
       <c r="D20">
-        <v>22793.17156431674</v>
+        <v>22831.51613253493</v>
       </c>
       <c r="E20">
-        <v>-5407.786</v>
+        <v>-5155.513</v>
       </c>
       <c r="F20">
-        <v>4540.914000000001</v>
+        <v>4793.187000000001</v>
       </c>
       <c r="G20">
         <v>1582.9</v>
@@ -2933,28 +2933,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M20">
-        <v>251.1125442000001</v>
+        <v>265.0632411</v>
       </c>
       <c r="N20">
-        <v>619.3874557999998</v>
+        <v>605.4367588999997</v>
       </c>
       <c r="O20">
-        <v>136.265240276</v>
+        <v>133.1960869579999</v>
       </c>
       <c r="P20">
-        <v>483.1222155239998</v>
+        <v>472.2406719419998</v>
       </c>
       <c r="Q20">
-        <v>2075.322215524</v>
+        <v>2064.440671942</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07281771737798276</v>
+        <v>0.07308861555768703</v>
       </c>
       <c r="T20">
-        <v>0.6239657593067611</v>
+        <v>0.6302220683068598</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.466573136651768</v>
+        <v>3.284121918933254</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0673972386017265</v>
+        <v>0.06731982895350712</v>
       </c>
       <c r="C21">
-        <v>19621.22913253493</v>
+        <v>19407.42993099619</v>
       </c>
       <c r="D21">
-        <v>22831.51613253493</v>
+        <v>22869.98993099619</v>
       </c>
       <c r="E21">
-        <v>-5155.513</v>
+        <v>-4903.24</v>
       </c>
       <c r="F21">
-        <v>4793.187000000001</v>
+        <v>5045.460000000001</v>
       </c>
       <c r="G21">
         <v>1582.9</v>
@@ -3015,28 +3015,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M21">
-        <v>265.0632411</v>
+        <v>279.0139380000001</v>
       </c>
       <c r="N21">
-        <v>605.4367588999997</v>
+        <v>591.4860619999997</v>
       </c>
       <c r="O21">
-        <v>133.1960869579999</v>
+        <v>130.1269336399999</v>
       </c>
       <c r="P21">
-        <v>472.2406719419998</v>
+        <v>461.3591283599998</v>
       </c>
       <c r="Q21">
-        <v>2064.440671942</v>
+        <v>2053.55912836</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07308861555768703</v>
+        <v>0.0733662861918839</v>
       </c>
       <c r="T21">
-        <v>0.6302220683068598</v>
+        <v>0.6366347850319609</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.284121918933254</v>
+        <v>3.119915822986591</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06731982895350712</v>
+        <v>0.06765191930528777</v>
       </c>
       <c r="C22">
-        <v>19407.42993099619</v>
+        <v>18991.01137284977</v>
       </c>
       <c r="D22">
-        <v>22869.98993099619</v>
+        <v>22705.84437284977</v>
       </c>
       <c r="E22">
-        <v>-4903.24</v>
+        <v>-4650.967</v>
       </c>
       <c r="F22">
-        <v>5045.460000000001</v>
+        <v>5297.733000000001</v>
       </c>
       <c r="G22">
         <v>1582.9</v>
@@ -3097,45 +3097,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M22">
-        <v>279.0139380000001</v>
+        <v>306.2089674000001</v>
       </c>
       <c r="N22">
-        <v>591.4860619999997</v>
+        <v>564.2910325999997</v>
       </c>
       <c r="O22">
-        <v>130.1269336399999</v>
+        <v>124.1440271719999</v>
       </c>
       <c r="P22">
-        <v>461.3591283599998</v>
+        <v>440.1470054279997</v>
       </c>
       <c r="Q22">
-        <v>2053.55912836</v>
+        <v>2032.347005428</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0733662861918839</v>
+        <v>0.07365098646238957</v>
       </c>
       <c r="T22">
-        <v>0.6366347850319609</v>
+        <v>0.6432098490159254</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.119915822986591</v>
+        <v>2.842829873309581</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06765191930528776</v>
+        <v>0.0675940096570684</v>
       </c>
       <c r="C23">
-        <v>18991.01137284978</v>
+        <v>18767.19211428922</v>
       </c>
       <c r="D23">
-        <v>22705.84437284978</v>
+        <v>22734.29811428922</v>
       </c>
       <c r="E23">
-        <v>-4650.967000000001</v>
+        <v>-4398.694</v>
       </c>
       <c r="F23">
-        <v>5297.733</v>
+        <v>5550.006</v>
       </c>
       <c r="G23">
         <v>1582.9</v>
@@ -3179,28 +3179,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M23">
-        <v>306.2089674</v>
+        <v>320.7903468000001</v>
       </c>
       <c r="N23">
-        <v>564.2910325999998</v>
+        <v>549.7096531999997</v>
       </c>
       <c r="O23">
-        <v>124.144027172</v>
+        <v>120.9361237039999</v>
       </c>
       <c r="P23">
-        <v>440.1470054279998</v>
+        <v>428.7735294959998</v>
       </c>
       <c r="Q23">
-        <v>2032.347005428</v>
+        <v>2020.973529496</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07365098646238956</v>
+        <v>0.07394298673983127</v>
       </c>
       <c r="T23">
-        <v>0.6432098490159253</v>
+        <v>0.6499535043840939</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.842829873309581</v>
+        <v>2.713610333613691</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0675940096570684</v>
+        <v>0.06753610000884902</v>
       </c>
       <c r="C24">
-        <v>18767.19211428922</v>
+        <v>18543.44425859992</v>
       </c>
       <c r="D24">
-        <v>22734.29811428922</v>
+        <v>22762.82325859992</v>
       </c>
       <c r="E24">
-        <v>-4398.694</v>
+        <v>-4146.420999999999</v>
       </c>
       <c r="F24">
-        <v>5550.006</v>
+        <v>5802.279000000001</v>
       </c>
       <c r="G24">
         <v>1582.9</v>
@@ -3261,28 +3261,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M24">
-        <v>320.7903468000001</v>
+        <v>335.3717262000001</v>
       </c>
       <c r="N24">
-        <v>549.7096531999997</v>
+        <v>535.1282737999996</v>
       </c>
       <c r="O24">
-        <v>120.9361237039999</v>
+        <v>117.7282202359999</v>
       </c>
       <c r="P24">
-        <v>428.7735294959998</v>
+        <v>417.4000535639997</v>
       </c>
       <c r="Q24">
-        <v>2020.973529496</v>
+        <v>2009.600053564</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07394298673983127</v>
+        <v>0.07424257144006366</v>
       </c>
       <c r="T24">
-        <v>0.6499535043840939</v>
+        <v>0.6568723196319554</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.713610333613691</v>
+        <v>2.595627275630487</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06753610000884902</v>
+        <v>0.06813339036062967</v>
       </c>
       <c r="C25">
-        <v>18543.44425859992</v>
+        <v>18000.35232198334</v>
       </c>
       <c r="D25">
-        <v>22762.82325859992</v>
+        <v>22472.00432198335</v>
       </c>
       <c r="E25">
-        <v>-4146.420999999999</v>
+        <v>-3894.147999999999</v>
       </c>
       <c r="F25">
-        <v>5802.279000000001</v>
+        <v>6054.552000000001</v>
       </c>
       <c r="G25">
         <v>1582.9</v>
@@ -3343,45 +3343,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M25">
-        <v>335.3717262000001</v>
+        <v>371.1440376000001</v>
       </c>
       <c r="N25">
-        <v>535.1282737999996</v>
+        <v>499.3559623999997</v>
       </c>
       <c r="O25">
-        <v>117.7282202359999</v>
+        <v>109.8583117279999</v>
       </c>
       <c r="P25">
-        <v>417.4000535639997</v>
+        <v>389.4976506719997</v>
       </c>
       <c r="Q25">
-        <v>2009.600053564</v>
+        <v>1981.697650672</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07424257144006366</v>
+        <v>0.07455003994819692</v>
       </c>
       <c r="T25">
-        <v>0.6568723196319554</v>
+        <v>0.6639732089652868</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.595627275630487</v>
+        <v>2.345450584708516</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06813339036062967</v>
+        <v>0.0681027807124103</v>
       </c>
       <c r="C26">
-        <v>18000.35232198335</v>
+        <v>17762.80229946779</v>
       </c>
       <c r="D26">
-        <v>22472.00432198335</v>
+        <v>22486.72729946779</v>
       </c>
       <c r="E26">
-        <v>-3894.148</v>
+        <v>-3641.875</v>
       </c>
       <c r="F26">
-        <v>6054.552000000001</v>
+        <v>6306.825000000001</v>
       </c>
       <c r="G26">
         <v>1582.9</v>
@@ -3425,28 +3425,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M26">
-        <v>371.1440376</v>
+        <v>386.6083725</v>
       </c>
       <c r="N26">
-        <v>499.3559623999997</v>
+        <v>483.8916274999997</v>
       </c>
       <c r="O26">
-        <v>109.8583117279999</v>
+        <v>106.4561580499999</v>
       </c>
       <c r="P26">
-        <v>389.4976506719998</v>
+        <v>377.4354694499998</v>
       </c>
       <c r="Q26">
-        <v>1981.697650672</v>
+        <v>1969.63546945</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07455003994819692</v>
+        <v>0.07486570761654705</v>
       </c>
       <c r="T26">
-        <v>0.6639732089652868</v>
+        <v>0.671263455347507</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.345450584708517</v>
+        <v>2.251632561320176</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0681027807124103</v>
+        <v>0.06864001106419092</v>
       </c>
       <c r="C27">
-        <v>17762.80229946779</v>
+        <v>17254.89631998807</v>
       </c>
       <c r="D27">
-        <v>22486.72729946779</v>
+        <v>22231.09431998807</v>
       </c>
       <c r="E27">
-        <v>-3641.875</v>
+        <v>-3389.602</v>
       </c>
       <c r="F27">
-        <v>6306.825000000001</v>
+        <v>6559.098000000001</v>
       </c>
       <c r="G27">
         <v>1582.9</v>
@@ -3507,45 +3507,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M27">
-        <v>386.6083725</v>
+        <v>420.4381818000001</v>
       </c>
       <c r="N27">
-        <v>483.8916274999997</v>
+        <v>450.0618181999997</v>
       </c>
       <c r="O27">
-        <v>106.4561580499999</v>
+        <v>99.01360000399993</v>
       </c>
       <c r="P27">
-        <v>377.4354694499998</v>
+        <v>351.0482181959998</v>
       </c>
       <c r="Q27">
-        <v>1969.63546945</v>
+        <v>1943.248218196</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07486570761654705</v>
+        <v>0.07518990684350124</v>
       </c>
       <c r="T27">
-        <v>0.671263455347507</v>
+        <v>0.6787507354157332</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.251632561320176</v>
+        <v>2.070458958492241</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06864001106419092</v>
+        <v>0.07027392141597155</v>
       </c>
       <c r="C28">
-        <v>17254.89631998807</v>
+        <v>16259.67722690394</v>
       </c>
       <c r="D28">
-        <v>22231.09431998807</v>
+        <v>21488.14822690394</v>
       </c>
       <c r="E28">
-        <v>-3389.602</v>
+        <v>-3137.329</v>
       </c>
       <c r="F28">
-        <v>6559.098000000001</v>
+        <v>6811.371000000001</v>
       </c>
       <c r="G28">
         <v>1582.9</v>
@@ -3589,45 +3589,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M28">
-        <v>420.4381818000001</v>
+        <v>489.7375749000001</v>
       </c>
       <c r="N28">
-        <v>450.0618181999997</v>
+        <v>380.7624250999997</v>
       </c>
       <c r="O28">
-        <v>99.01360000399993</v>
+        <v>83.76773352199993</v>
       </c>
       <c r="P28">
-        <v>351.0482181959998</v>
+        <v>296.9946915779998</v>
       </c>
       <c r="Q28">
-        <v>1943.248218196</v>
+        <v>1889.194691578</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07518990684350124</v>
+        <v>0.07552298824105692</v>
       </c>
       <c r="T28">
-        <v>0.6787507354157332</v>
+        <v>0.6864431464447326</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.070458958492241</v>
+        <v>1.777482563345783</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07027392141597155</v>
+        <v>0.07117775176775218</v>
       </c>
       <c r="C29">
-        <v>16259.67722690394</v>
+        <v>15617.37346177428</v>
       </c>
       <c r="D29">
-        <v>21488.14822690394</v>
+        <v>21098.11746177428</v>
       </c>
       <c r="E29">
-        <v>-3137.329</v>
+        <v>-2885.056</v>
       </c>
       <c r="F29">
-        <v>6811.371000000001</v>
+        <v>7063.644000000001</v>
       </c>
       <c r="G29">
         <v>1582.9</v>
@@ -3671,45 +3671,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M29">
-        <v>489.7375749000001</v>
+        <v>535.4242152000002</v>
       </c>
       <c r="N29">
-        <v>380.7624250999997</v>
+        <v>335.0757847999996</v>
       </c>
       <c r="O29">
-        <v>83.76773352199993</v>
+        <v>73.71667265599991</v>
       </c>
       <c r="P29">
-        <v>296.9946915779998</v>
+        <v>261.3591121439997</v>
       </c>
       <c r="Q29">
-        <v>1889.194691578</v>
+        <v>1853.559112144</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07552298824105692</v>
+        <v>0.07586532189965581</v>
       </c>
       <c r="T29">
-        <v>0.6864431464447326</v>
+        <v>0.694349235557871</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.777482563345783</v>
+        <v>1.625813654458711</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07117775176775218</v>
+        <v>0.07126024211953282</v>
       </c>
       <c r="C30">
-        <v>15617.37346177428</v>
+        <v>15330.20724893166</v>
       </c>
       <c r="D30">
-        <v>21098.11746177428</v>
+        <v>21063.22424893166</v>
       </c>
       <c r="E30">
-        <v>-2885.056</v>
+        <v>-2632.782999999999</v>
       </c>
       <c r="F30">
-        <v>7063.644000000001</v>
+        <v>7315.917000000002</v>
       </c>
       <c r="G30">
         <v>1582.9</v>
@@ -3753,28 +3753,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M30">
-        <v>535.4242152000002</v>
+        <v>554.5465086000003</v>
       </c>
       <c r="N30">
-        <v>335.0757847999996</v>
+        <v>315.9534913999995</v>
       </c>
       <c r="O30">
-        <v>73.71667265599991</v>
+        <v>69.50976810799989</v>
       </c>
       <c r="P30">
-        <v>261.3591121439997</v>
+        <v>246.4437232919996</v>
       </c>
       <c r="Q30">
-        <v>1853.559112144</v>
+        <v>1838.643723292</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07586532189965581</v>
+        <v>0.07621729875990538</v>
       </c>
       <c r="T30">
-        <v>0.694349235557871</v>
+        <v>0.7024780314065907</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.625813654458711</v>
+        <v>1.56975111464979</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07126024211953282</v>
+        <v>0.07134273247131345</v>
       </c>
       <c r="C31">
-        <v>15330.20724893166</v>
+        <v>15043.15626210403</v>
       </c>
       <c r="D31">
-        <v>21063.22424893166</v>
+        <v>21028.44626210403</v>
       </c>
       <c r="E31">
-        <v>-2632.783</v>
+        <v>-2380.51</v>
       </c>
       <c r="F31">
-        <v>7315.917</v>
+        <v>7568.190000000001</v>
       </c>
       <c r="G31">
         <v>1582.9</v>
@@ -3835,28 +3835,28 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M31">
-        <v>554.5465086</v>
+        <v>573.6688020000001</v>
       </c>
       <c r="N31">
-        <v>315.9534913999997</v>
+        <v>296.8311979999996</v>
       </c>
       <c r="O31">
-        <v>69.50976810799995</v>
+        <v>65.30286355999992</v>
       </c>
       <c r="P31">
-        <v>246.4437232919998</v>
+        <v>231.5283344399997</v>
       </c>
       <c r="Q31">
-        <v>1838.643723292</v>
+        <v>1823.72833444</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07621729875990538</v>
+        <v>0.07657933210187635</v>
       </c>
       <c r="T31">
-        <v>0.7024780314065907</v>
+        <v>0.7108390785652737</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.569751114649791</v>
+        <v>1.517426077494797</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07134273247131345</v>
+        <v>0.08236809888139497</v>
       </c>
       <c r="C32">
-        <v>15043.15626210403</v>
+        <v>10989.21999937774</v>
       </c>
       <c r="D32">
-        <v>21028.44626210403</v>
+        <v>17226.78299937774</v>
       </c>
       <c r="E32">
-        <v>-2380.51</v>
+        <v>-2128.237</v>
       </c>
       <c r="F32">
-        <v>7568.190000000001</v>
+        <v>7820.463000000001</v>
       </c>
       <c r="G32">
         <v>1582.9</v>
@@ -3917,45 +3917,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M32">
-        <v>573.6688020000001</v>
+        <v>927.5069118000001</v>
       </c>
       <c r="N32">
-        <v>296.8311979999996</v>
+        <v>-57.00691180000035</v>
       </c>
       <c r="O32">
-        <v>65.30286355999992</v>
+        <v>-12.54152059600008</v>
       </c>
       <c r="P32">
-        <v>231.5283344399997</v>
+        <v>-44.46539120400028</v>
       </c>
       <c r="Q32">
-        <v>1823.72833444</v>
+        <v>1547.734608796</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07657933210187635</v>
+        <v>0.07709199719113904</v>
       </c>
       <c r="T32">
-        <v>0.7108390785652737</v>
+        <v>0.7226789189639501</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.22</v>
+        <v>0.2064782456751067</v>
       </c>
       <c r="W32">
-        <v>0.05912400000000001</v>
+        <v>0.09411168006293236</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.517426077494797</v>
+        <v>0.9385374803413941</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08236809888139497</v>
+        <v>0.08309609888139496</v>
       </c>
       <c r="C33">
-        <v>10989.21999937774</v>
+        <v>10533.73216714093</v>
       </c>
       <c r="D33">
-        <v>17226.78299937774</v>
+        <v>17023.56816714093</v>
       </c>
       <c r="E33">
-        <v>-2128.237</v>
+        <v>-1875.964</v>
       </c>
       <c r="F33">
-        <v>7820.463000000001</v>
+        <v>8072.736000000001</v>
       </c>
       <c r="G33">
         <v>1582.9</v>
@@ -3999,37 +3999,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M33">
-        <v>927.5069118000001</v>
+        <v>957.4264896000002</v>
       </c>
       <c r="N33">
-        <v>-57.00691180000035</v>
+        <v>-86.92648960000042</v>
       </c>
       <c r="O33">
-        <v>-12.54152059600008</v>
+        <v>-19.12382771200009</v>
       </c>
       <c r="P33">
-        <v>-44.46539120400028</v>
+        <v>-67.80266188800033</v>
       </c>
       <c r="Q33">
-        <v>1547.734608796</v>
+        <v>1524.397338112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07709199719113904</v>
+        <v>0.07755217362042049</v>
       </c>
       <c r="T33">
-        <v>0.7226789189639501</v>
+        <v>0.7333065501251846</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.2064782456751067</v>
+        <v>0.2000258004977596</v>
       </c>
       <c r="W33">
-        <v>0.09411168006293236</v>
+        <v>0.09487694006096571</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9385374803413941</v>
+        <v>0.9092081840807255</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08309609888139496</v>
+        <v>0.08382409888139497</v>
       </c>
       <c r="C34">
-        <v>10533.73216714093</v>
+        <v>10082.98286309441</v>
       </c>
       <c r="D34">
-        <v>17023.56816714093</v>
+        <v>16825.09186309441</v>
       </c>
       <c r="E34">
-        <v>-1875.964</v>
+        <v>-1623.690999999999</v>
       </c>
       <c r="F34">
-        <v>8072.736000000001</v>
+        <v>8325.009000000002</v>
       </c>
       <c r="G34">
         <v>1582.9</v>
@@ -4081,37 +4081,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M34">
-        <v>957.4264896000002</v>
+        <v>987.3460674000003</v>
       </c>
       <c r="N34">
-        <v>-86.92648960000042</v>
+        <v>-116.8460674000005</v>
       </c>
       <c r="O34">
-        <v>-19.12382771200009</v>
+        <v>-25.70613482800011</v>
       </c>
       <c r="P34">
-        <v>-67.80266188800033</v>
+        <v>-91.13993257200039</v>
       </c>
       <c r="Q34">
-        <v>1524.397338112</v>
+        <v>1501.060067428</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07755217362042049</v>
+        <v>0.07802608665953126</v>
       </c>
       <c r="T34">
-        <v>0.7333065501251846</v>
+        <v>0.7442514240076502</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.2000258004977596</v>
+        <v>0.1939644126038881</v>
       </c>
       <c r="W34">
-        <v>0.09487694006096571</v>
+        <v>0.09559582066517888</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9092081840807255</v>
+        <v>0.881656420926764</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08382409888139497</v>
+        <v>0.08455209888139496</v>
       </c>
       <c r="C35">
-        <v>10082.98286309441</v>
+        <v>9636.808259030107</v>
       </c>
       <c r="D35">
-        <v>16825.09186309441</v>
+        <v>16631.19025903011</v>
       </c>
       <c r="E35">
-        <v>-1623.690999999999</v>
+        <v>-1371.418</v>
       </c>
       <c r="F35">
-        <v>8325.009000000002</v>
+        <v>8577.282000000001</v>
       </c>
       <c r="G35">
         <v>1582.9</v>
@@ -4163,37 +4163,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M35">
-        <v>987.3460674000003</v>
+        <v>1017.2656452</v>
       </c>
       <c r="N35">
-        <v>-116.8460674000005</v>
+        <v>-146.7656452000004</v>
       </c>
       <c r="O35">
-        <v>-25.70613482800011</v>
+        <v>-32.2884419440001</v>
       </c>
       <c r="P35">
-        <v>-91.13993257200039</v>
+        <v>-114.4772032560004</v>
       </c>
       <c r="Q35">
-        <v>1501.060067428</v>
+        <v>1477.722796744</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07802608665953126</v>
+        <v>0.07851436069982717</v>
       </c>
       <c r="T35">
-        <v>0.7442514240076502</v>
+        <v>0.7555279607350388</v>
       </c>
       <c r="U35">
         <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1939644126038881</v>
+        <v>0.1882595769390679</v>
       </c>
       <c r="W35">
-        <v>0.09559582066517888</v>
+        <v>0.09627241417502656</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.881656420926764</v>
+        <v>0.8557253497230357</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08455209888139496</v>
+        <v>0.08528009888139496</v>
       </c>
       <c r="C36">
-        <v>9636.808259030107</v>
+        <v>9195.051992881175</v>
       </c>
       <c r="D36">
-        <v>16631.19025903011</v>
+        <v>16441.70699288118</v>
       </c>
       <c r="E36">
-        <v>-1371.418</v>
+        <v>-1119.144999999999</v>
       </c>
       <c r="F36">
-        <v>8577.282000000001</v>
+        <v>8829.555000000002</v>
       </c>
       <c r="G36">
         <v>1582.9</v>
@@ -4245,37 +4245,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M36">
-        <v>1017.2656452</v>
+        <v>1047.185223</v>
       </c>
       <c r="N36">
-        <v>-146.7656452000004</v>
+        <v>-176.6852230000006</v>
       </c>
       <c r="O36">
-        <v>-32.2884419440001</v>
+        <v>-38.87074906000014</v>
       </c>
       <c r="P36">
-        <v>-114.4772032560004</v>
+        <v>-137.8144739400005</v>
       </c>
       <c r="Q36">
-        <v>1477.722796744</v>
+        <v>1454.38552606</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07851436069982717</v>
+        <v>0.0790176585567476</v>
       </c>
       <c r="T36">
-        <v>0.7555279607350388</v>
+        <v>0.7671514678232702</v>
       </c>
       <c r="U36">
         <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.1882595769390679</v>
+        <v>0.1828807318836659</v>
       </c>
       <c r="W36">
-        <v>0.09627241417502656</v>
+        <v>0.09691034519859723</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8557253497230357</v>
+        <v>0.8312760540166632</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08528009888139496</v>
+        <v>0.08600809888139498</v>
       </c>
       <c r="C37">
-        <v>9195.051992881175</v>
+        <v>8757.564748195229</v>
       </c>
       <c r="D37">
-        <v>16441.70699288118</v>
+        <v>16256.49274819523</v>
       </c>
       <c r="E37">
-        <v>-1119.144999999999</v>
+        <v>-866.8719999999994</v>
       </c>
       <c r="F37">
-        <v>8829.555000000002</v>
+        <v>9081.828000000001</v>
       </c>
       <c r="G37">
         <v>1582.9</v>
@@ -4327,37 +4327,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M37">
-        <v>1047.185223</v>
+        <v>1077.1048008</v>
       </c>
       <c r="N37">
-        <v>-176.6852230000006</v>
+        <v>-206.6048008000005</v>
       </c>
       <c r="O37">
-        <v>-38.87074906000014</v>
+        <v>-45.4530561760001</v>
       </c>
       <c r="P37">
-        <v>-137.8144739400005</v>
+        <v>-161.1517446240004</v>
       </c>
       <c r="Q37">
-        <v>1454.38552606</v>
+        <v>1431.048255376</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0790176585567476</v>
+        <v>0.07953668447169679</v>
       </c>
       <c r="T37">
-        <v>0.7671514678232702</v>
+        <v>0.7791382095080088</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.1828807318836659</v>
+        <v>0.1778007115535641</v>
       </c>
       <c r="W37">
-        <v>0.09691034519859723</v>
+        <v>0.09751283560974731</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8312760540166632</v>
+        <v>0.8081850525162004</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08600809888139496</v>
+        <v>0.1177545406391833</v>
       </c>
       <c r="C38">
-        <v>8757.564748195233</v>
+        <v>3150.145793298043</v>
       </c>
       <c r="D38">
-        <v>16256.49274819523</v>
+        <v>10901.34679329804</v>
       </c>
       <c r="E38">
-        <v>-866.8719999999994</v>
+        <v>-614.5990000000002</v>
       </c>
       <c r="F38">
-        <v>9081.828000000001</v>
+        <v>9334.101000000001</v>
       </c>
       <c r="G38">
         <v>1582.9</v>
@@ -4409,45 +4409,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M38">
-        <v>1077.1048008</v>
+        <v>1874.2874808</v>
       </c>
       <c r="N38">
-        <v>-206.6048008000005</v>
+        <v>-1003.7874808</v>
       </c>
       <c r="O38">
-        <v>-45.4530561760001</v>
+        <v>-220.8332457760001</v>
       </c>
       <c r="P38">
-        <v>-161.1517446240004</v>
+        <v>-782.9542350240004</v>
       </c>
       <c r="Q38">
-        <v>1431.048255376</v>
+        <v>809.2457649759997</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07953668447169678</v>
+        <v>0.08103161876138777</v>
       </c>
       <c r="T38">
-        <v>0.7791382095080087</v>
+        <v>0.8136632508403643</v>
       </c>
       <c r="U38">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1778007115535641</v>
+        <v>0.1021774951611254</v>
       </c>
       <c r="W38">
-        <v>0.09751283560974731</v>
+        <v>0.180282758971646</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8081850525162004</v>
+        <v>0.4644431598232973</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1177545406391833</v>
+        <v>0.1193045406391833</v>
       </c>
       <c r="C39">
-        <v>3150.145793298043</v>
+        <v>2725.31608463108</v>
       </c>
       <c r="D39">
-        <v>10901.34679329804</v>
+        <v>10728.79008463108</v>
       </c>
       <c r="E39">
-        <v>-614.5990000000002</v>
+        <v>-362.3259999999991</v>
       </c>
       <c r="F39">
-        <v>9334.101000000001</v>
+        <v>9586.374000000002</v>
       </c>
       <c r="G39">
         <v>1582.9</v>
@@ -4491,37 +4491,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M39">
-        <v>1874.2874808</v>
+        <v>1924.9438992</v>
       </c>
       <c r="N39">
-        <v>-1003.7874808</v>
+        <v>-1054.443899200001</v>
       </c>
       <c r="O39">
-        <v>-220.8332457760001</v>
+        <v>-231.9776578240001</v>
       </c>
       <c r="P39">
-        <v>-782.9542350240004</v>
+        <v>-822.4662413760005</v>
       </c>
       <c r="Q39">
-        <v>809.2457649759997</v>
+        <v>769.7337586239995</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08103161876138777</v>
+        <v>0.08159987067689403</v>
       </c>
       <c r="T39">
-        <v>0.8136632508403643</v>
+        <v>0.8267868516603701</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1021774951611254</v>
+        <v>0.09948861370951682</v>
       </c>
       <c r="W39">
-        <v>0.180282758971646</v>
+        <v>0.180822686367129</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4644431598232973</v>
+        <v>0.4522209714068947</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1193045406391833</v>
+        <v>0.1208545406391833</v>
       </c>
       <c r="C40">
-        <v>2725.31608463108</v>
+        <v>2305.864031223748</v>
       </c>
       <c r="D40">
-        <v>10728.79008463108</v>
+        <v>10561.61103122375</v>
       </c>
       <c r="E40">
-        <v>-362.3259999999991</v>
+        <v>-110.0529999999999</v>
       </c>
       <c r="F40">
-        <v>9586.374000000002</v>
+        <v>9838.647000000001</v>
       </c>
       <c r="G40">
         <v>1582.9</v>
@@ -4573,37 +4573,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M40">
-        <v>1924.9438992</v>
+        <v>1975.6003176</v>
       </c>
       <c r="N40">
-        <v>-1054.443899200001</v>
+        <v>-1105.1003176</v>
       </c>
       <c r="O40">
-        <v>-231.9776578240001</v>
+        <v>-243.1220698720001</v>
       </c>
       <c r="P40">
-        <v>-822.4662413760005</v>
+        <v>-861.9782477280003</v>
       </c>
       <c r="Q40">
-        <v>769.7337586239995</v>
+        <v>730.2217522719998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08159987067689403</v>
+        <v>0.08218675380274475</v>
       </c>
       <c r="T40">
-        <v>0.8267868516603701</v>
+        <v>0.8403407344744745</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.09948861370951682</v>
+        <v>0.09693762361440103</v>
       </c>
       <c r="W40">
-        <v>0.180822686367129</v>
+        <v>0.1813349251782283</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4522209714068947</v>
+        <v>0.440625561883641</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1208545406391833</v>
+        <v>0.1224045406391833</v>
       </c>
       <c r="C41">
-        <v>2305.864031223748</v>
+        <v>1891.542101726291</v>
       </c>
       <c r="D41">
-        <v>10561.61103122375</v>
+        <v>10399.56210172629</v>
       </c>
       <c r="E41">
-        <v>-110.0529999999999</v>
+        <v>142.2200000000012</v>
       </c>
       <c r="F41">
-        <v>9838.647000000001</v>
+        <v>10090.92</v>
       </c>
       <c r="G41">
         <v>1582.9</v>
@@ -4655,37 +4655,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M41">
-        <v>1975.6003176</v>
+        <v>2026.256736000001</v>
       </c>
       <c r="N41">
-        <v>-1105.1003176</v>
+        <v>-1155.756736000001</v>
       </c>
       <c r="O41">
-        <v>-243.1220698720001</v>
+        <v>-254.2664819200002</v>
       </c>
       <c r="P41">
-        <v>-861.9782477280003</v>
+        <v>-901.4902540800006</v>
       </c>
       <c r="Q41">
-        <v>730.2217522719998</v>
+        <v>690.7097459199995</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08218675380274475</v>
+        <v>0.08279319969945717</v>
       </c>
       <c r="T41">
-        <v>0.8403407344744745</v>
+        <v>0.8543464133823825</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.09693762361440103</v>
+        <v>0.09451418302404099</v>
       </c>
       <c r="W41">
-        <v>0.1813349251782283</v>
+        <v>0.1818215520487726</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.440625561883641</v>
+        <v>0.42960992283655</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1224045406391833</v>
+        <v>0.1239545406391833</v>
       </c>
       <c r="C42">
-        <v>1891.542101726291</v>
+        <v>1482.117726915845</v>
       </c>
       <c r="D42">
-        <v>10399.56210172629</v>
+        <v>10242.41072691585</v>
       </c>
       <c r="E42">
-        <v>142.2200000000012</v>
+        <v>394.4930000000004</v>
       </c>
       <c r="F42">
-        <v>10090.92</v>
+        <v>10343.193</v>
       </c>
       <c r="G42">
         <v>1582.9</v>
@@ -4737,37 +4737,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M42">
-        <v>2026.256736000001</v>
+        <v>2076.9131544</v>
       </c>
       <c r="N42">
-        <v>-1155.756736000001</v>
+        <v>-1206.4131544</v>
       </c>
       <c r="O42">
-        <v>-254.2664819200002</v>
+        <v>-265.4108939680001</v>
       </c>
       <c r="P42">
-        <v>-901.4902540800006</v>
+        <v>-941.0022604320003</v>
       </c>
       <c r="Q42">
-        <v>690.7097459199995</v>
+        <v>651.1977395679997</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08279319969945717</v>
+        <v>0.08342020308419372</v>
       </c>
       <c r="T42">
-        <v>0.8543464133823825</v>
+        <v>0.8688268610668296</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.09451418302404099</v>
+        <v>0.09220895904784489</v>
       </c>
       <c r="W42">
-        <v>0.1818215520487726</v>
+        <v>0.1822844410231927</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.42960992283655</v>
+        <v>0.4191316320356585</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1239545406391833</v>
+        <v>0.1255045406391833</v>
       </c>
       <c r="C43">
-        <v>1482.117726915845</v>
+        <v>1077.372186035995</v>
       </c>
       <c r="D43">
-        <v>10242.41072691585</v>
+        <v>10089.938186036</v>
       </c>
       <c r="E43">
-        <v>394.4930000000004</v>
+        <v>646.7660000000014</v>
       </c>
       <c r="F43">
-        <v>10343.193</v>
+        <v>10595.466</v>
       </c>
       <c r="G43">
         <v>1582.9</v>
@@ -4819,37 +4819,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M43">
-        <v>2076.9131544</v>
+        <v>2127.569572800001</v>
       </c>
       <c r="N43">
-        <v>-1206.4131544</v>
+        <v>-1257.069572800001</v>
       </c>
       <c r="O43">
-        <v>-265.4108939680001</v>
+        <v>-276.5553060160001</v>
       </c>
       <c r="P43">
-        <v>-941.0022604320003</v>
+        <v>-980.5142667840006</v>
       </c>
       <c r="Q43">
-        <v>651.1977395679997</v>
+        <v>611.6857332159994</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08342020308419372</v>
+        <v>0.08406882727530052</v>
       </c>
       <c r="T43">
-        <v>0.8688268610668296</v>
+        <v>0.8838066345334992</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09220895904784489</v>
+        <v>0.0900135076419438</v>
       </c>
       <c r="W43">
-        <v>0.1822844410231927</v>
+        <v>0.1827252876654977</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4191316320356585</v>
+        <v>0.4091523074633809</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1255045406391833</v>
+        <v>0.1270545406391833</v>
       </c>
       <c r="C44">
-        <v>1077.372186036</v>
+        <v>677.0995911476421</v>
       </c>
       <c r="D44">
-        <v>10089.938186036</v>
+        <v>9941.938591147644</v>
       </c>
       <c r="E44">
-        <v>646.7659999999996</v>
+        <v>899.0390000000007</v>
       </c>
       <c r="F44">
-        <v>10595.466</v>
+        <v>10847.739</v>
       </c>
       <c r="G44">
         <v>1582.9</v>
@@ -4901,37 +4901,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M44">
-        <v>2127.5695728</v>
+        <v>2178.2259912</v>
       </c>
       <c r="N44">
-        <v>-1257.0695728</v>
+        <v>-1307.725991200001</v>
       </c>
       <c r="O44">
-        <v>-276.5553060160001</v>
+        <v>-287.6997180640001</v>
       </c>
       <c r="P44">
-        <v>-980.5142667840003</v>
+        <v>-1020.026273136001</v>
       </c>
       <c r="Q44">
-        <v>611.6857332159998</v>
+        <v>572.1737268639995</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0840688272753005</v>
+        <v>0.0847402102099549</v>
       </c>
       <c r="T44">
-        <v>0.8838066345334989</v>
+        <v>0.8993120140867183</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09001350764194382</v>
+        <v>0.08792017025492185</v>
       </c>
       <c r="W44">
-        <v>0.1827252876654977</v>
+        <v>0.1831456298128117</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4091523074633809</v>
+        <v>0.3996371375223721</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1270545406391833</v>
+        <v>0.1286045406391833</v>
       </c>
       <c r="C45">
-        <v>677.0995911476421</v>
+        <v>281.1059595731549</v>
       </c>
       <c r="D45">
-        <v>9941.938591147644</v>
+        <v>9798.217959573156</v>
       </c>
       <c r="E45">
-        <v>899.0390000000007</v>
+        <v>1151.312</v>
       </c>
       <c r="F45">
-        <v>10847.739</v>
+        <v>11100.012</v>
       </c>
       <c r="G45">
         <v>1582.9</v>
@@ -4983,37 +4983,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M45">
-        <v>2178.2259912</v>
+        <v>2228.8824096</v>
       </c>
       <c r="N45">
-        <v>-1307.725991200001</v>
+        <v>-1358.382409600001</v>
       </c>
       <c r="O45">
-        <v>-287.6997180640001</v>
+        <v>-298.8441301120001</v>
       </c>
       <c r="P45">
-        <v>-1020.026273136001</v>
+        <v>-1059.538279488</v>
       </c>
       <c r="Q45">
-        <v>572.1737268639995</v>
+        <v>532.6617205119996</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0847402102099549</v>
+        <v>0.08543557110656125</v>
       </c>
       <c r="T45">
-        <v>0.8993120140867183</v>
+        <v>0.9153711571954098</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08792017025492185</v>
+        <v>0.08592198456731</v>
       </c>
       <c r="W45">
-        <v>0.1831456298128117</v>
+        <v>0.1835468654988842</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3996371375223721</v>
+        <v>0.3905544753059546</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1286045406391833</v>
+        <v>0.1301545406391833</v>
       </c>
       <c r="C46">
-        <v>281.1059595731549</v>
+        <v>-110.7916343534125</v>
       </c>
       <c r="D46">
-        <v>9798.217959573156</v>
+        <v>9658.59336564659</v>
       </c>
       <c r="E46">
-        <v>1151.312</v>
+        <v>1403.585000000001</v>
       </c>
       <c r="F46">
-        <v>11100.012</v>
+        <v>11352.285</v>
       </c>
       <c r="G46">
         <v>1582.9</v>
@@ -5065,37 +5065,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M46">
-        <v>2228.8824096</v>
+        <v>2279.538828</v>
       </c>
       <c r="N46">
-        <v>-1358.382409600001</v>
+        <v>-1409.038828</v>
       </c>
       <c r="O46">
-        <v>-298.8441301120001</v>
+        <v>-309.9885421600001</v>
       </c>
       <c r="P46">
-        <v>-1059.538279488</v>
+        <v>-1099.05028584</v>
       </c>
       <c r="Q46">
-        <v>532.6617205119996</v>
+        <v>493.1497141599998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08543557110656125</v>
+        <v>0.08615621785395326</v>
       </c>
       <c r="T46">
-        <v>0.9153711571954098</v>
+        <v>0.9320142691444172</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08592198456731</v>
+        <v>0.08401260713248089</v>
       </c>
       <c r="W46">
-        <v>0.1835468654988842</v>
+        <v>0.1839302684877978</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3905544753059546</v>
+        <v>0.3818754869658222</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1301545406391833</v>
+        <v>0.1317045406391834</v>
       </c>
       <c r="C47">
-        <v>-110.7916343534125</v>
+        <v>-498.7658360297628</v>
       </c>
       <c r="D47">
-        <v>9658.59336564659</v>
+        <v>9522.89216397024</v>
       </c>
       <c r="E47">
-        <v>1403.585000000001</v>
+        <v>1655.858000000002</v>
       </c>
       <c r="F47">
-        <v>11352.285</v>
+        <v>11604.558</v>
       </c>
       <c r="G47">
         <v>1582.9</v>
@@ -5147,37 +5147,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M47">
-        <v>2279.538828</v>
+        <v>2330.195246400001</v>
       </c>
       <c r="N47">
-        <v>-1409.038828</v>
+        <v>-1459.695246400001</v>
       </c>
       <c r="O47">
-        <v>-309.9885421600001</v>
+        <v>-321.1329542080002</v>
       </c>
       <c r="P47">
-        <v>-1099.05028584</v>
+        <v>-1138.562292192001</v>
       </c>
       <c r="Q47">
-        <v>493.1497141599998</v>
+        <v>453.6377078079995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08615621785395326</v>
+        <v>0.08690355522161906</v>
       </c>
       <c r="T47">
-        <v>0.9320142691444172</v>
+        <v>0.9492737926470916</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08401260713248089</v>
+        <v>0.08218624610786174</v>
       </c>
       <c r="W47">
-        <v>0.1839302684877978</v>
+        <v>0.1842970017815414</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3818754869658222</v>
+        <v>0.373573845944826</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1317045406391834</v>
+        <v>0.1332545406391833</v>
       </c>
       <c r="C48">
-        <v>-498.7658360297628</v>
+        <v>-882.9797227574782</v>
       </c>
       <c r="D48">
-        <v>9522.89216397024</v>
+        <v>9390.951277242524</v>
       </c>
       <c r="E48">
-        <v>1655.858000000002</v>
+        <v>1908.131000000001</v>
       </c>
       <c r="F48">
-        <v>11604.558</v>
+        <v>11856.831</v>
       </c>
       <c r="G48">
         <v>1582.9</v>
@@ -5229,37 +5229,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M48">
-        <v>2330.195246400001</v>
+        <v>2380.8516648</v>
       </c>
       <c r="N48">
-        <v>-1459.695246400001</v>
+        <v>-1510.351664800001</v>
       </c>
       <c r="O48">
-        <v>-321.1329542080002</v>
+        <v>-332.2773662560002</v>
       </c>
       <c r="P48">
-        <v>-1138.562292192001</v>
+        <v>-1178.074298544001</v>
       </c>
       <c r="Q48">
-        <v>453.6377078079995</v>
+        <v>414.1257014559994</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08690355522161906</v>
+        <v>0.08767909399938546</v>
       </c>
       <c r="T48">
-        <v>0.9492737926470916</v>
+        <v>0.9671846189234519</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08218624610786174</v>
+        <v>0.08043760257365191</v>
       </c>
       <c r="W48">
-        <v>0.1842970017815414</v>
+        <v>0.1846481294032107</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.373573845944826</v>
+        <v>0.3656254662438723</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1332545406391833</v>
+        <v>0.1348045406391833</v>
       </c>
       <c r="C49">
-        <v>-882.9797227574782</v>
+        <v>-1263.587457519838</v>
       </c>
       <c r="D49">
-        <v>9390.951277242524</v>
+        <v>9262.616542480166</v>
       </c>
       <c r="E49">
-        <v>1908.131000000001</v>
+        <v>2160.404000000002</v>
       </c>
       <c r="F49">
-        <v>11856.831</v>
+        <v>12109.104</v>
       </c>
       <c r="G49">
         <v>1582.9</v>
@@ -5311,37 +5311,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M49">
-        <v>2380.8516648</v>
+        <v>2431.508083200001</v>
       </c>
       <c r="N49">
-        <v>-1510.351664800001</v>
+        <v>-1561.008083200001</v>
       </c>
       <c r="O49">
-        <v>-332.2773662560002</v>
+        <v>-343.4217783040002</v>
       </c>
       <c r="P49">
-        <v>-1178.074298544001</v>
+        <v>-1217.586304896001</v>
       </c>
       <c r="Q49">
-        <v>414.1257014559994</v>
+        <v>374.6136951039991</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08767909399938546</v>
+        <v>0.08848446119168134</v>
       </c>
       <c r="T49">
-        <v>0.9671846189234519</v>
+        <v>0.9857843231335183</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08043760257365191</v>
+        <v>0.07876181918670082</v>
       </c>
       <c r="W49">
-        <v>0.1846481294032107</v>
+        <v>0.1849846267073105</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3656254662438723</v>
+        <v>0.3580082690304582</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1348045406391833</v>
+        <v>0.1363545406391833</v>
       </c>
       <c r="C50">
-        <v>-1263.587457519836</v>
+        <v>-1640.734889875948</v>
       </c>
       <c r="D50">
-        <v>9262.616542480166</v>
+        <v>9137.742110124052</v>
       </c>
       <c r="E50">
-        <v>2160.404</v>
+        <v>2412.677</v>
       </c>
       <c r="F50">
-        <v>12109.104</v>
+        <v>12361.377</v>
       </c>
       <c r="G50">
         <v>1582.9</v>
@@ -5393,37 +5393,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M50">
-        <v>2431.5080832</v>
+        <v>2482.1645016</v>
       </c>
       <c r="N50">
-        <v>-1561.008083200001</v>
+        <v>-1611.6645016</v>
       </c>
       <c r="O50">
-        <v>-343.4217783040001</v>
+        <v>-354.5661903520001</v>
       </c>
       <c r="P50">
-        <v>-1217.586304896</v>
+        <v>-1257.098311248</v>
       </c>
       <c r="Q50">
-        <v>374.6136951039996</v>
+        <v>335.1016887519997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08848446119168134</v>
+        <v>0.08932141141112607</v>
       </c>
       <c r="T50">
-        <v>0.9857843231335182</v>
+        <v>1.005113427508685</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.07876181918670083</v>
+        <v>0.07715443512166613</v>
       </c>
       <c r="W50">
-        <v>0.1849846267073105</v>
+        <v>0.1853073894275695</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3580082690304583</v>
+        <v>0.3507019778257551</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1363545406391833</v>
+        <v>0.1379045406391833</v>
       </c>
       <c r="C51">
-        <v>-1640.734889875948</v>
+        <v>-2014.560108895601</v>
       </c>
       <c r="D51">
-        <v>9137.742110124052</v>
+        <v>9016.189891104401</v>
       </c>
       <c r="E51">
-        <v>2412.677</v>
+        <v>2664.950000000001</v>
       </c>
       <c r="F51">
-        <v>12361.377</v>
+        <v>12613.65</v>
       </c>
       <c r="G51">
         <v>1582.9</v>
@@ -5475,37 +5475,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M51">
-        <v>2482.1645016</v>
+        <v>2532.820920000001</v>
       </c>
       <c r="N51">
-        <v>-1611.6645016</v>
+        <v>-1662.320920000001</v>
       </c>
       <c r="O51">
-        <v>-354.5661903520001</v>
+        <v>-365.7106024000002</v>
       </c>
       <c r="P51">
-        <v>-1257.098311248</v>
+        <v>-1296.610317600001</v>
       </c>
       <c r="Q51">
-        <v>335.1016887519997</v>
+        <v>295.5896823999994</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08932141141112607</v>
+        <v>0.0901918396393486</v>
       </c>
       <c r="T51">
-        <v>1.005113427508685</v>
+        <v>1.025215696058859</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07715443512166613</v>
+        <v>0.0756113464192328</v>
       </c>
       <c r="W51">
-        <v>0.1853073894275695</v>
+        <v>0.185617241639018</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3507019778257551</v>
+        <v>0.3436879382692399</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1379045406391833</v>
+        <v>0.1394545406391833</v>
       </c>
       <c r="C52">
-        <v>-2014.560108895601</v>
+        <v>-2385.19395254184</v>
       </c>
       <c r="D52">
-        <v>9016.189891104401</v>
+        <v>8897.829047458163</v>
       </c>
       <c r="E52">
-        <v>2664.950000000001</v>
+        <v>2917.223000000002</v>
       </c>
       <c r="F52">
-        <v>12613.65</v>
+        <v>12865.923</v>
       </c>
       <c r="G52">
         <v>1582.9</v>
@@ -5557,37 +5557,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M52">
-        <v>2532.820920000001</v>
+        <v>2583.4773384</v>
       </c>
       <c r="N52">
-        <v>-1662.320920000001</v>
+        <v>-1712.977338400001</v>
       </c>
       <c r="O52">
-        <v>-365.7106024000002</v>
+        <v>-376.8550144480001</v>
       </c>
       <c r="P52">
-        <v>-1296.610317600001</v>
+        <v>-1336.122323952</v>
       </c>
       <c r="Q52">
-        <v>295.5896823999994</v>
+        <v>256.0776760479996</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0901918396393486</v>
+        <v>0.0910977955503557</v>
       </c>
       <c r="T52">
-        <v>1.025215696058859</v>
+        <v>1.046138465366182</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.0756113464192328</v>
+        <v>0.07412877099924783</v>
       </c>
       <c r="W52">
-        <v>0.185617241639018</v>
+        <v>0.185914942783351</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3436879382692399</v>
+        <v>0.3369489590874902</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1394545406391833</v>
+        <v>0.1410045406391833</v>
       </c>
       <c r="C53">
-        <v>-2385.19395254184</v>
+        <v>-2752.76047745168</v>
       </c>
       <c r="D53">
-        <v>8897.829047458163</v>
+        <v>8782.535522548322</v>
       </c>
       <c r="E53">
-        <v>2917.223000000002</v>
+        <v>3169.496000000001</v>
       </c>
       <c r="F53">
-        <v>12865.923</v>
+        <v>13118.196</v>
       </c>
       <c r="G53">
         <v>1582.9</v>
@@ -5639,37 +5639,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M53">
-        <v>2583.4773384</v>
+        <v>2634.1337568</v>
       </c>
       <c r="N53">
-        <v>-1712.977338400001</v>
+        <v>-1763.633756800001</v>
       </c>
       <c r="O53">
-        <v>-376.8550144480001</v>
+        <v>-387.9994264960001</v>
       </c>
       <c r="P53">
-        <v>-1336.122323952</v>
+        <v>-1375.634330304001</v>
       </c>
       <c r="Q53">
-        <v>256.0776760479996</v>
+        <v>216.5656696959995</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0910977955503557</v>
+        <v>0.09204149962432145</v>
       </c>
       <c r="T53">
-        <v>1.046138465366182</v>
+        <v>1.067933016727978</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07412877099924783</v>
+        <v>0.07270321771080077</v>
       </c>
       <c r="W53">
-        <v>0.185914942783351</v>
+        <v>0.1862011938836712</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3369489590874902</v>
+        <v>0.3304691714127308</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1410045406391833</v>
+        <v>0.1425545406391833</v>
       </c>
       <c r="C54">
-        <v>-2752.76047745168</v>
+        <v>-3117.377392660908</v>
       </c>
       <c r="D54">
-        <v>8782.535522548322</v>
+        <v>8670.191607339095</v>
       </c>
       <c r="E54">
-        <v>3169.496000000001</v>
+        <v>3421.769000000002</v>
       </c>
       <c r="F54">
-        <v>13118.196</v>
+        <v>13370.469</v>
       </c>
       <c r="G54">
         <v>1582.9</v>
@@ -5721,37 +5721,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M54">
-        <v>2634.1337568</v>
+        <v>2684.790175200001</v>
       </c>
       <c r="N54">
-        <v>-1763.633756800001</v>
+        <v>-1814.290175200001</v>
       </c>
       <c r="O54">
-        <v>-387.9994264960001</v>
+        <v>-399.1438385440002</v>
       </c>
       <c r="P54">
-        <v>-1375.634330304001</v>
+        <v>-1415.146336656001</v>
       </c>
       <c r="Q54">
-        <v>216.5656696959995</v>
+        <v>177.0536633439995</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09204149962432145</v>
+        <v>0.09302536131845596</v>
       </c>
       <c r="T54">
-        <v>1.067933016727978</v>
+        <v>1.090654995807297</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07270321771080077</v>
+        <v>0.07133145888606866</v>
       </c>
       <c r="W54">
-        <v>0.1862011938836712</v>
+        <v>0.1864766430556774</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3304691714127308</v>
+        <v>0.3242339040275849</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1425545406391833</v>
+        <v>0.1441045406391833</v>
       </c>
       <c r="C55">
-        <v>-3117.377392660908</v>
+        <v>-3479.156460460768</v>
       </c>
       <c r="D55">
-        <v>8670.191607339095</v>
+        <v>8560.685539539234</v>
       </c>
       <c r="E55">
-        <v>3421.769000000002</v>
+        <v>3674.042000000001</v>
       </c>
       <c r="F55">
-        <v>13370.469</v>
+        <v>13622.742</v>
       </c>
       <c r="G55">
         <v>1582.9</v>
@@ -5803,37 +5803,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M55">
-        <v>2684.790175200001</v>
+        <v>2735.446593600001</v>
       </c>
       <c r="N55">
-        <v>-1814.290175200001</v>
+        <v>-1864.946593600001</v>
       </c>
       <c r="O55">
-        <v>-399.1438385440002</v>
+        <v>-410.2882505920002</v>
       </c>
       <c r="P55">
-        <v>-1415.146336656001</v>
+        <v>-1454.658343008001</v>
       </c>
       <c r="Q55">
-        <v>177.0536633439995</v>
+        <v>137.5416569919994</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09302536131845596</v>
+        <v>0.0940519996079876</v>
       </c>
       <c r="T55">
-        <v>1.090654995807297</v>
+        <v>1.114364887020499</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07133145888606866</v>
+        <v>0.07001050594373408</v>
       </c>
       <c r="W55">
-        <v>0.1864766430556774</v>
+        <v>0.1867418904064982</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3242339040275849</v>
+        <v>0.3182295724715185</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1441045406391833</v>
+        <v>0.1456545406391833</v>
       </c>
       <c r="C56">
-        <v>-3479.156460460768</v>
+        <v>-3838.203867256185</v>
       </c>
       <c r="D56">
-        <v>8560.685539539234</v>
+        <v>8453.911132743819</v>
       </c>
       <c r="E56">
-        <v>3674.042000000001</v>
+        <v>3926.315000000002</v>
       </c>
       <c r="F56">
-        <v>13622.742</v>
+        <v>13875.015</v>
       </c>
       <c r="G56">
         <v>1582.9</v>
@@ -5885,37 +5885,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M56">
-        <v>2735.446593600001</v>
+        <v>2786.103012</v>
       </c>
       <c r="N56">
-        <v>-1864.946593600001</v>
+        <v>-1915.603012000001</v>
       </c>
       <c r="O56">
-        <v>-410.2882505920002</v>
+        <v>-421.4326626400002</v>
       </c>
       <c r="P56">
-        <v>-1454.658343008001</v>
+        <v>-1494.170349360001</v>
       </c>
       <c r="Q56">
-        <v>137.5416569919994</v>
+        <v>98.02965063999955</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.0940519996079876</v>
+        <v>0.09512426626594289</v>
       </c>
       <c r="T56">
-        <v>1.114364887020499</v>
+        <v>1.13912855117651</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07001050594373408</v>
+        <v>0.06873758765384799</v>
       </c>
       <c r="W56">
-        <v>0.1867418904064982</v>
+        <v>0.1869974923991073</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3182295724715185</v>
+        <v>0.3124435802447636</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1456545406391833</v>
+        <v>0.1472045406391833</v>
       </c>
       <c r="C57">
-        <v>-3838.203867256185</v>
+        <v>-4194.620567012371</v>
       </c>
       <c r="D57">
-        <v>8453.911132743819</v>
+        <v>8349.767432987632</v>
       </c>
       <c r="E57">
-        <v>3926.315000000002</v>
+        <v>4178.588000000002</v>
       </c>
       <c r="F57">
-        <v>13875.015</v>
+        <v>14127.288</v>
       </c>
       <c r="G57">
         <v>1582.9</v>
@@ -5967,37 +5967,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M57">
-        <v>2786.103012</v>
+        <v>2836.7594304</v>
       </c>
       <c r="N57">
-        <v>-1915.603012000001</v>
+        <v>-1966.259430400001</v>
       </c>
       <c r="O57">
-        <v>-421.4326626400002</v>
+        <v>-432.5770746880002</v>
       </c>
       <c r="P57">
-        <v>-1494.170349360001</v>
+        <v>-1533.682355712001</v>
       </c>
       <c r="Q57">
-        <v>98.02965063999955</v>
+        <v>58.51764428799947</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09512426626594289</v>
+        <v>0.09624527231744159</v>
       </c>
       <c r="T57">
-        <v>1.13912855117651</v>
+        <v>1.165017836430522</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06873758765384799</v>
+        <v>0.06751013073145785</v>
       </c>
       <c r="W57">
-        <v>0.1869974923991073</v>
+        <v>0.1872439657491233</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3124435802447636</v>
+        <v>0.3068642305975358</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1472045406391833</v>
+        <v>0.1487545406391833</v>
       </c>
       <c r="C58">
-        <v>-4194.620567012371</v>
+        <v>-4548.502599624875</v>
       </c>
       <c r="D58">
-        <v>8349.767432987632</v>
+        <v>8248.158400375129</v>
       </c>
       <c r="E58">
-        <v>4178.588000000002</v>
+        <v>4430.861000000003</v>
       </c>
       <c r="F58">
-        <v>14127.288</v>
+        <v>14379.561</v>
       </c>
       <c r="G58">
         <v>1582.9</v>
@@ -6049,37 +6049,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M58">
-        <v>2836.7594304</v>
+        <v>2887.415848800001</v>
       </c>
       <c r="N58">
-        <v>-1966.259430400001</v>
+        <v>-2016.915848800001</v>
       </c>
       <c r="O58">
-        <v>-432.5770746880002</v>
+        <v>-443.7214867360002</v>
       </c>
       <c r="P58">
-        <v>-1533.682355712001</v>
+        <v>-1573.194362064001</v>
       </c>
       <c r="Q58">
-        <v>58.51764428799947</v>
+        <v>19.00563793599918</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09624527231744159</v>
+        <v>0.09741841818528907</v>
       </c>
       <c r="T58">
-        <v>1.165017836430522</v>
+        <v>1.192111274487045</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06751013073145785</v>
+        <v>0.06632574247301122</v>
       </c>
       <c r="W58">
-        <v>0.1872439657491233</v>
+        <v>0.1874817909114193</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3068642305975358</v>
+        <v>0.3014806476045965</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1487545406391833</v>
+        <v>0.1503045406391833</v>
       </c>
       <c r="C59">
-        <v>-4548.502599624875</v>
+        <v>-4899.94138632342</v>
       </c>
       <c r="D59">
-        <v>8248.158400375129</v>
+        <v>8148.992613676583</v>
       </c>
       <c r="E59">
-        <v>4430.861000000003</v>
+        <v>4683.134000000004</v>
       </c>
       <c r="F59">
-        <v>14379.561</v>
+        <v>14631.834</v>
       </c>
       <c r="G59">
         <v>1582.9</v>
@@ -6131,37 +6131,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M59">
-        <v>2887.415848800001</v>
+        <v>2938.072267200001</v>
       </c>
       <c r="N59">
-        <v>-2016.915848800001</v>
+        <v>-2067.572267200001</v>
       </c>
       <c r="O59">
-        <v>-443.7214867360002</v>
+        <v>-454.8658987840003</v>
       </c>
       <c r="P59">
-        <v>-1573.194362064001</v>
+        <v>-1612.706368416001</v>
       </c>
       <c r="Q59">
-        <v>19.00563793599918</v>
+        <v>-20.50636841600067</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09741841818528907</v>
+        <v>0.09864742814208166</v>
       </c>
       <c r="T59">
-        <v>1.192111274487045</v>
+        <v>1.220494876260547</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06632574247301122</v>
+        <v>0.06518219518899378</v>
       </c>
       <c r="W59">
-        <v>0.1874817909114193</v>
+        <v>0.1877114152060501</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3014806476045965</v>
+        <v>0.2962827054045173</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1503045406391833</v>
+        <v>0.1518545406391833</v>
       </c>
       <c r="C60">
-        <v>-4899.941386323417</v>
+        <v>-5249.0240040195</v>
       </c>
       <c r="D60">
-        <v>8148.992613676583</v>
+        <v>8052.182995980501</v>
       </c>
       <c r="E60">
-        <v>4683.134</v>
+        <v>4935.407000000001</v>
       </c>
       <c r="F60">
-        <v>14631.834</v>
+        <v>14884.107</v>
       </c>
       <c r="G60">
         <v>1582.9</v>
@@ -6213,37 +6213,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M60">
-        <v>2938.0722672</v>
+        <v>2988.728685600001</v>
       </c>
       <c r="N60">
-        <v>-2067.5722672</v>
+        <v>-2118.228685600001</v>
       </c>
       <c r="O60">
-        <v>-454.865898784</v>
+        <v>-466.0103108320002</v>
       </c>
       <c r="P60">
-        <v>-1612.706368416</v>
+        <v>-1652.218374768001</v>
       </c>
       <c r="Q60">
-        <v>-20.50636841600021</v>
+        <v>-60.01837476800074</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09864742814208166</v>
+        <v>0.09993638980408365</v>
       </c>
       <c r="T60">
-        <v>1.220494876260546</v>
+        <v>1.250263043974218</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.06518219518899381</v>
+        <v>0.06407741221968881</v>
       </c>
       <c r="W60">
-        <v>0.1877114152060501</v>
+        <v>0.1879332556262865</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2962827054045173</v>
+        <v>0.2912609646349491</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1518545406391833</v>
+        <v>0.1534045406391833</v>
       </c>
       <c r="C61">
-        <v>-5249.0240040195</v>
+        <v>-5595.833440328139</v>
       </c>
       <c r="D61">
-        <v>8052.182995980501</v>
+        <v>7957.646559671862</v>
       </c>
       <c r="E61">
-        <v>4935.407000000001</v>
+        <v>5187.68</v>
       </c>
       <c r="F61">
-        <v>14884.107</v>
+        <v>15136.38</v>
       </c>
       <c r="G61">
         <v>1582.9</v>
@@ -6295,37 +6295,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M61">
-        <v>2988.728685600001</v>
+        <v>3039.385104</v>
       </c>
       <c r="N61">
-        <v>-2118.228685600001</v>
+        <v>-2168.885104000001</v>
       </c>
       <c r="O61">
-        <v>-466.0103108320002</v>
+        <v>-477.1547228800002</v>
       </c>
       <c r="P61">
-        <v>-1652.218374768001</v>
+        <v>-1691.730381120001</v>
       </c>
       <c r="Q61">
-        <v>-60.01837476800074</v>
+        <v>-99.53038112000058</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09993638980408365</v>
+        <v>0.1012897995491857</v>
       </c>
       <c r="T61">
-        <v>1.250263043974218</v>
+        <v>1.281519620073573</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06407741221968881</v>
+        <v>0.06300945534936067</v>
       </c>
       <c r="W61">
-        <v>0.1879332556262865</v>
+        <v>0.1881477013658484</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2912609646349491</v>
+        <v>0.2864066152243666</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1534045406391833</v>
+        <v>0.1549545406391833</v>
       </c>
       <c r="C62">
-        <v>-5595.833440328139</v>
+        <v>-5940.448830833622</v>
       </c>
       <c r="D62">
-        <v>7957.646559671862</v>
+        <v>7865.304169166379</v>
       </c>
       <c r="E62">
-        <v>5187.68</v>
+        <v>5439.953000000001</v>
       </c>
       <c r="F62">
-        <v>15136.38</v>
+        <v>15388.653</v>
       </c>
       <c r="G62">
         <v>1582.9</v>
@@ -6377,37 +6377,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M62">
-        <v>3039.385104</v>
+        <v>3090.0415224</v>
       </c>
       <c r="N62">
-        <v>-2168.885104000001</v>
+        <v>-2219.541522400001</v>
       </c>
       <c r="O62">
-        <v>-477.1547228800002</v>
+        <v>-488.2991349280002</v>
       </c>
       <c r="P62">
-        <v>-1691.730381120001</v>
+        <v>-1731.242387472001</v>
       </c>
       <c r="Q62">
-        <v>-99.53038112000058</v>
+        <v>-139.0423874720007</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1012897995491857</v>
+        <v>0.1027126149222418</v>
       </c>
       <c r="T62">
-        <v>1.281519620073573</v>
+        <v>1.314379097511358</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06300945534936067</v>
+        <v>0.06197651345838755</v>
       </c>
       <c r="W62">
-        <v>0.1881477013658484</v>
+        <v>0.1883551160975558</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2864066152243666</v>
+        <v>0.2817114248108524</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1549545406391833</v>
+        <v>0.1565045406391833</v>
       </c>
       <c r="C63">
-        <v>-5940.448830833622</v>
+        <v>-6282.945680025065</v>
       </c>
       <c r="D63">
-        <v>7865.304169166379</v>
+        <v>7775.080319974936</v>
       </c>
       <c r="E63">
-        <v>5439.953000000001</v>
+        <v>5692.226000000001</v>
       </c>
       <c r="F63">
-        <v>15388.653</v>
+        <v>15640.926</v>
       </c>
       <c r="G63">
         <v>1582.9</v>
@@ -6459,37 +6459,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M63">
-        <v>3090.0415224</v>
+        <v>3140.6979408</v>
       </c>
       <c r="N63">
-        <v>-2219.541522400001</v>
+        <v>-2270.197940800001</v>
       </c>
       <c r="O63">
-        <v>-488.2991349280002</v>
+        <v>-499.4435469760002</v>
       </c>
       <c r="P63">
-        <v>-1731.242387472001</v>
+        <v>-1770.754393824001</v>
       </c>
       <c r="Q63">
-        <v>-139.0423874720007</v>
+        <v>-178.5543938240005</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1027126149222418</v>
+        <v>0.1042103153149324</v>
       </c>
       <c r="T63">
-        <v>1.314379097511358</v>
+        <v>1.348968021130078</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06197651345838755</v>
+        <v>0.06097689227357485</v>
       </c>
       <c r="W63">
-        <v>0.1883551160975558</v>
+        <v>0.1885558400314662</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2817114248108524</v>
+        <v>0.2771676921526128</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1565045406391833</v>
+        <v>0.1580545406391833</v>
       </c>
       <c r="C64">
-        <v>-6282.945680025065</v>
+        <v>-6623.396067198115</v>
       </c>
       <c r="D64">
-        <v>7775.080319974936</v>
+        <v>7686.902932801887</v>
       </c>
       <c r="E64">
-        <v>5692.226000000001</v>
+        <v>5944.499000000002</v>
       </c>
       <c r="F64">
-        <v>15640.926</v>
+        <v>15893.199</v>
       </c>
       <c r="G64">
         <v>1582.9</v>
@@ -6541,37 +6541,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M64">
-        <v>3140.6979408</v>
+        <v>3191.354359200001</v>
       </c>
       <c r="N64">
-        <v>-2270.197940800001</v>
+        <v>-2320.854359200001</v>
       </c>
       <c r="O64">
-        <v>-499.4435469760002</v>
+        <v>-510.5879590240001</v>
       </c>
       <c r="P64">
-        <v>-1770.754393824001</v>
+        <v>-1810.266400176</v>
       </c>
       <c r="Q64">
-        <v>-178.5543938240005</v>
+        <v>-218.0664001760003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1042103153149324</v>
+        <v>0.1057889724856062</v>
       </c>
       <c r="T64">
-        <v>1.348968021130078</v>
+        <v>1.385426616295755</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06097689227357485</v>
+        <v>0.0600090050946292</v>
       </c>
       <c r="W64">
-        <v>0.1885558400314662</v>
+        <v>0.1887501917769984</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2771676921526128</v>
+        <v>0.2727682049755874</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1580545406391833</v>
+        <v>0.1596045406391833</v>
       </c>
       <c r="C65">
-        <v>-6623.396067198115</v>
+        <v>-6961.868838502969</v>
       </c>
       <c r="D65">
-        <v>7686.902932801887</v>
+        <v>7600.703161497032</v>
       </c>
       <c r="E65">
-        <v>5944.499000000002</v>
+        <v>6196.772000000001</v>
       </c>
       <c r="F65">
-        <v>15893.199</v>
+        <v>16145.472</v>
       </c>
       <c r="G65">
         <v>1582.9</v>
@@ -6623,37 +6623,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M65">
-        <v>3191.354359200001</v>
+        <v>3242.0107776</v>
       </c>
       <c r="N65">
-        <v>-2320.854359200001</v>
+        <v>-2371.5107776</v>
       </c>
       <c r="O65">
-        <v>-510.5879590240001</v>
+        <v>-521.7323710720001</v>
       </c>
       <c r="P65">
-        <v>-1810.266400176</v>
+        <v>-1849.778406528</v>
       </c>
       <c r="Q65">
-        <v>-218.0664001760003</v>
+        <v>-257.5784065280002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1057889724856062</v>
+        <v>0.1074553328324286</v>
       </c>
       <c r="T65">
-        <v>1.385426616295755</v>
+        <v>1.423910688970637</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0600090050946292</v>
+        <v>0.05907136439002562</v>
       </c>
       <c r="W65">
-        <v>0.1887501917769984</v>
+        <v>0.1889384700304829</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2727682049755874</v>
+        <v>0.2685062017728438</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1596045406391833</v>
+        <v>0.1611545406391833</v>
       </c>
       <c r="C66">
-        <v>-6961.868838502969</v>
+        <v>-7298.429786214121</v>
       </c>
       <c r="D66">
-        <v>7600.703161497032</v>
+        <v>7516.415213785881</v>
       </c>
       <c r="E66">
-        <v>6196.772000000001</v>
+        <v>6449.045000000002</v>
       </c>
       <c r="F66">
-        <v>16145.472</v>
+        <v>16397.745</v>
       </c>
       <c r="G66">
         <v>1582.9</v>
@@ -6705,37 +6705,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M66">
-        <v>3242.0107776</v>
+        <v>3292.667196000001</v>
       </c>
       <c r="N66">
-        <v>-2371.5107776</v>
+        <v>-2422.167196000001</v>
       </c>
       <c r="O66">
-        <v>-521.7323710720001</v>
+        <v>-532.8767831200003</v>
       </c>
       <c r="P66">
-        <v>-1849.778406528</v>
+        <v>-1889.290412880001</v>
       </c>
       <c r="Q66">
-        <v>-257.5784065280002</v>
+        <v>-297.0904128800009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1074553328324286</v>
+        <v>0.109216913770498</v>
       </c>
       <c r="T66">
-        <v>1.423910688970637</v>
+        <v>1.464593851512656</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05907136439002562</v>
+        <v>0.0581625741686406</v>
       </c>
       <c r="W66">
-        <v>0.1889384700304829</v>
+        <v>0.189120955106937</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2685062017728438</v>
+        <v>0.2643753371301845</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1611545406391833</v>
+        <v>0.1627045406391833</v>
       </c>
       <c r="C67">
-        <v>-7298.429786214121</v>
+        <v>-7633.141816202817</v>
       </c>
       <c r="D67">
-        <v>7516.415213785881</v>
+        <v>7433.976183797186</v>
       </c>
       <c r="E67">
-        <v>6449.045000000002</v>
+        <v>6701.318000000003</v>
       </c>
       <c r="F67">
-        <v>16397.745</v>
+        <v>16650.018</v>
       </c>
       <c r="G67">
         <v>1582.9</v>
@@ -6787,37 +6787,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M67">
-        <v>3292.667196000001</v>
+        <v>3343.323614400001</v>
       </c>
       <c r="N67">
-        <v>-2422.167196000001</v>
+        <v>-2472.823614400001</v>
       </c>
       <c r="O67">
-        <v>-532.8767831200003</v>
+        <v>-544.0211951680003</v>
       </c>
       <c r="P67">
-        <v>-1889.290412880001</v>
+        <v>-1928.802419232001</v>
       </c>
       <c r="Q67">
-        <v>-297.0904128800009</v>
+        <v>-336.6024192320008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.109216913770498</v>
+        <v>0.1110821171166891</v>
       </c>
       <c r="T67">
-        <v>1.464593851512656</v>
+        <v>1.507670141263028</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0581625741686406</v>
+        <v>0.05728132304487333</v>
       </c>
       <c r="W67">
-        <v>0.189120955106937</v>
+        <v>0.1892979103325894</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2643753371301845</v>
+        <v>0.2603696502039696</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1627045406391833</v>
+        <v>0.1642545406391833</v>
       </c>
       <c r="C68">
-        <v>-7633.141816202817</v>
+        <v>-7966.065104508241</v>
       </c>
       <c r="D68">
-        <v>7433.976183797186</v>
+        <v>7353.325895491763</v>
       </c>
       <c r="E68">
-        <v>6701.318000000003</v>
+        <v>6953.591000000004</v>
       </c>
       <c r="F68">
-        <v>16650.018</v>
+        <v>16902.291</v>
       </c>
       <c r="G68">
         <v>1582.9</v>
@@ -6869,37 +6869,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M68">
-        <v>3343.323614400001</v>
+        <v>3393.980032800001</v>
       </c>
       <c r="N68">
-        <v>-2472.823614400001</v>
+        <v>-2523.480032800001</v>
       </c>
       <c r="O68">
-        <v>-544.0211951680003</v>
+        <v>-555.1656072160002</v>
       </c>
       <c r="P68">
-        <v>-1928.802419232001</v>
+        <v>-1968.314425584001</v>
       </c>
       <c r="Q68">
-        <v>-336.6024192320008</v>
+        <v>-376.1144255840006</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1110821171166891</v>
+        <v>0.1130603630899221</v>
       </c>
       <c r="T68">
-        <v>1.507670141263028</v>
+        <v>1.553357115240696</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05728132304487333</v>
+        <v>0.05642637792480058</v>
       </c>
       <c r="W68">
-        <v>0.1892979103325894</v>
+        <v>0.1894695833127001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2603696502039696</v>
+        <v>0.2564835360218209</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1642545406391833</v>
+        <v>0.1658045406391833</v>
       </c>
       <c r="C69">
-        <v>-7966.065104508241</v>
+        <v>-8297.257243826312</v>
       </c>
       <c r="D69">
-        <v>7353.325895491763</v>
+        <v>7274.406756173689</v>
       </c>
       <c r="E69">
-        <v>6953.591000000004</v>
+        <v>7205.864000000001</v>
       </c>
       <c r="F69">
-        <v>16902.291</v>
+        <v>17154.564</v>
       </c>
       <c r="G69">
         <v>1582.9</v>
@@ -6951,37 +6951,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M69">
-        <v>3393.980032800001</v>
+        <v>3444.6364512</v>
       </c>
       <c r="N69">
-        <v>-2523.480032800001</v>
+        <v>-2574.136451200001</v>
       </c>
       <c r="O69">
-        <v>-555.1656072160002</v>
+        <v>-566.3100192640002</v>
       </c>
       <c r="P69">
-        <v>-1968.314425584001</v>
+        <v>-2007.826431936001</v>
       </c>
       <c r="Q69">
-        <v>-376.1144255840006</v>
+        <v>-415.6264319360007</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1130603630899221</v>
+        <v>0.1151622494364822</v>
       </c>
       <c r="T69">
-        <v>1.553357115240696</v>
+        <v>1.601899525091967</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05642637792480058</v>
+        <v>0.05559657824943588</v>
       </c>
       <c r="W69">
-        <v>0.1894695833127001</v>
+        <v>0.1896362070875133</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2564835360218209</v>
+        <v>0.2527117193156175</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1658045406391833</v>
+        <v>0.1673545406391833</v>
       </c>
       <c r="C70">
-        <v>-8297.257243826312</v>
+        <v>-8626.773380665583</v>
       </c>
       <c r="D70">
-        <v>7274.406756173689</v>
+        <v>7197.16361933442</v>
       </c>
       <c r="E70">
-        <v>7205.864000000001</v>
+        <v>7458.137000000002</v>
       </c>
       <c r="F70">
-        <v>17154.564</v>
+        <v>17406.837</v>
       </c>
       <c r="G70">
         <v>1582.9</v>
@@ -7033,37 +7033,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M70">
-        <v>3444.6364512</v>
+        <v>3495.292869600001</v>
       </c>
       <c r="N70">
-        <v>-2574.136451200001</v>
+        <v>-2624.792869600001</v>
       </c>
       <c r="O70">
-        <v>-566.3100192640002</v>
+        <v>-577.4544313120002</v>
       </c>
       <c r="P70">
-        <v>-2007.826431936001</v>
+        <v>-2047.338438288001</v>
       </c>
       <c r="Q70">
-        <v>-415.6264319360007</v>
+        <v>-455.1384382880005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1151622494364822</v>
+        <v>0.1173997413537881</v>
       </c>
       <c r="T70">
-        <v>1.601899525091967</v>
+        <v>1.65357370332074</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05559657824943588</v>
+        <v>0.05479083073857449</v>
       </c>
       <c r="W70">
-        <v>0.1896362070875133</v>
+        <v>0.1897980011876942</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2527117193156175</v>
+        <v>0.249049230629884</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1673545406391833</v>
+        <v>0.1689045406391833</v>
       </c>
       <c r="C71">
-        <v>-8626.773380665583</v>
+        <v>-8954.666343856599</v>
       </c>
       <c r="D71">
-        <v>7197.16361933442</v>
+        <v>7121.543656143405</v>
       </c>
       <c r="E71">
-        <v>7458.137000000002</v>
+        <v>7710.410000000003</v>
       </c>
       <c r="F71">
-        <v>17406.837</v>
+        <v>17659.11</v>
       </c>
       <c r="G71">
         <v>1582.9</v>
@@ -7115,37 +7115,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M71">
-        <v>3495.292869600001</v>
+        <v>3545.949288000001</v>
       </c>
       <c r="N71">
-        <v>-2624.792869600001</v>
+        <v>-2675.449288000002</v>
       </c>
       <c r="O71">
-        <v>-577.4544313120002</v>
+        <v>-588.5988433600004</v>
       </c>
       <c r="P71">
-        <v>-2047.338438288001</v>
+        <v>-2086.850444640001</v>
       </c>
       <c r="Q71">
-        <v>-455.1384382880005</v>
+        <v>-494.6504446400011</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1173997413537881</v>
+        <v>0.1197863993989143</v>
       </c>
       <c r="T71">
-        <v>1.65357370332074</v>
+        <v>1.708692826764765</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05479083073857449</v>
+        <v>0.05400810458516627</v>
       </c>
       <c r="W71">
-        <v>0.1897980011876942</v>
+        <v>0.1899551725992986</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.249049230629884</v>
+        <v>0.2454913844780284</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1689045406391833</v>
+        <v>0.1704545406391833</v>
       </c>
       <c r="C72">
-        <v>-8954.666343856599</v>
+        <v>-9280.986765044096</v>
       </c>
       <c r="D72">
-        <v>7121.543656143405</v>
+        <v>7047.49623495591</v>
       </c>
       <c r="E72">
-        <v>7710.410000000003</v>
+        <v>7962.683000000005</v>
       </c>
       <c r="F72">
-        <v>17659.11</v>
+        <v>17911.38300000001</v>
       </c>
       <c r="G72">
         <v>1582.9</v>
@@ -7197,37 +7197,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M72">
-        <v>3545.949288000001</v>
+        <v>3596.605706400001</v>
       </c>
       <c r="N72">
-        <v>-2675.449288000002</v>
+        <v>-2726.105706400002</v>
       </c>
       <c r="O72">
-        <v>-588.5988433600004</v>
+        <v>-599.7432554080003</v>
       </c>
       <c r="P72">
-        <v>-2086.850444640001</v>
+        <v>-2126.362450992001</v>
       </c>
       <c r="Q72">
-        <v>-494.6504446400011</v>
+        <v>-534.1624509920009</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1197863993989143</v>
+        <v>0.122337654550601</v>
       </c>
       <c r="T72">
-        <v>1.708692826764765</v>
+        <v>1.767613269066999</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05400810458516627</v>
+        <v>0.05324742705579773</v>
       </c>
       <c r="W72">
-        <v>0.1899551725992986</v>
+        <v>0.1901079166471958</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2454913844780284</v>
+        <v>0.2420337593445351</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1704545406391833</v>
+        <v>0.1720045406391833</v>
       </c>
       <c r="C73">
-        <v>-9280.986765044092</v>
+        <v>-9605.783191739518</v>
       </c>
       <c r="D73">
-        <v>7047.49623495591</v>
+        <v>6974.972808260485</v>
       </c>
       <c r="E73">
-        <v>7962.683000000001</v>
+        <v>8214.956000000002</v>
       </c>
       <c r="F73">
-        <v>17911.383</v>
+        <v>18163.656</v>
       </c>
       <c r="G73">
         <v>1582.9</v>
@@ -7279,37 +7279,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M73">
-        <v>3596.605706400001</v>
+        <v>3647.2621248</v>
       </c>
       <c r="N73">
-        <v>-2726.105706400001</v>
+        <v>-2776.7621248</v>
       </c>
       <c r="O73">
-        <v>-599.7432554080001</v>
+        <v>-610.8876674560001</v>
       </c>
       <c r="P73">
-        <v>-2126.362450992001</v>
+        <v>-2165.874457344</v>
       </c>
       <c r="Q73">
-        <v>-534.1624509920005</v>
+        <v>-573.6744573440003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.122337654550601</v>
+        <v>0.1250711422131225</v>
       </c>
       <c r="T73">
-        <v>1.767613269066998</v>
+        <v>1.830742314390819</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05324742705579774</v>
+        <v>0.05250787945780055</v>
       </c>
       <c r="W73">
-        <v>0.1901079166471958</v>
+        <v>0.1902564178048737</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2420337593445353</v>
+        <v>0.2386721793536389</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1720045406391833</v>
+        <v>0.1735545406391833</v>
       </c>
       <c r="C74">
-        <v>-9605.783191739518</v>
+        <v>-9929.102193464341</v>
       </c>
       <c r="D74">
-        <v>6974.972808260485</v>
+        <v>6903.926806535658</v>
       </c>
       <c r="E74">
-        <v>8214.956000000002</v>
+        <v>8467.228999999999</v>
       </c>
       <c r="F74">
-        <v>18163.656</v>
+        <v>18415.929</v>
       </c>
       <c r="G74">
         <v>1582.9</v>
@@ -7361,37 +7361,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M74">
-        <v>3647.2621248</v>
+        <v>3697.9185432</v>
       </c>
       <c r="N74">
-        <v>-2776.7621248</v>
+        <v>-2827.4185432</v>
       </c>
       <c r="O74">
-        <v>-610.8876674560001</v>
+        <v>-622.0320795040001</v>
       </c>
       <c r="P74">
-        <v>-2165.874457344</v>
+        <v>-2205.386463696</v>
       </c>
       <c r="Q74">
-        <v>-573.6744573440003</v>
+        <v>-613.1864636960001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1250711422131225</v>
+        <v>0.1280071104432381</v>
       </c>
       <c r="T74">
-        <v>1.830742314390819</v>
+        <v>1.898547585294183</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05250787945780055</v>
+        <v>0.0517885934378307</v>
       </c>
       <c r="W74">
-        <v>0.1902564178048737</v>
+        <v>0.1904008504376836</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2386721793536389</v>
+        <v>0.2354026974446849</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1735545406391833</v>
+        <v>0.1751045406391833</v>
       </c>
       <c r="C75">
-        <v>-9929.102193464341</v>
+        <v>-10250.98846147181</v>
       </c>
       <c r="D75">
-        <v>6903.926806535658</v>
+        <v>6834.313538528187</v>
       </c>
       <c r="E75">
-        <v>8467.228999999999</v>
+        <v>8719.502</v>
       </c>
       <c r="F75">
-        <v>18415.929</v>
+        <v>18668.202</v>
       </c>
       <c r="G75">
         <v>1582.9</v>
@@ -7443,37 +7443,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M75">
-        <v>3697.9185432</v>
+        <v>3748.5749616</v>
       </c>
       <c r="N75">
-        <v>-2827.4185432</v>
+        <v>-2878.0749616</v>
       </c>
       <c r="O75">
-        <v>-622.0320795040001</v>
+        <v>-633.176491552</v>
       </c>
       <c r="P75">
-        <v>-2205.386463696</v>
+        <v>-2244.898470048</v>
       </c>
       <c r="Q75">
-        <v>-613.1864636960001</v>
+        <v>-652.6984700480004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1280071104432381</v>
+        <v>0.1311689223833627</v>
       </c>
       <c r="T75">
-        <v>1.898547585294183</v>
+        <v>1.971568646267036</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0517885934378307</v>
+        <v>0.05108874758056271</v>
       </c>
       <c r="W75">
-        <v>0.1904008504376836</v>
+        <v>0.190541379485823</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2354026974446849</v>
+        <v>0.2322215799116487</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1751045406391833</v>
+        <v>0.1766545406391833</v>
       </c>
       <c r="C76">
-        <v>-10250.98846147181</v>
+        <v>-10571.4849024959</v>
       </c>
       <c r="D76">
-        <v>6834.313538528187</v>
+        <v>6766.090097504103</v>
       </c>
       <c r="E76">
-        <v>8719.502</v>
+        <v>8971.775000000001</v>
       </c>
       <c r="F76">
-        <v>18668.202</v>
+        <v>18920.475</v>
       </c>
       <c r="G76">
         <v>1582.9</v>
@@ -7525,37 +7525,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M76">
-        <v>3748.5749616</v>
+        <v>3799.231380000001</v>
       </c>
       <c r="N76">
-        <v>-2878.0749616</v>
+        <v>-2928.731380000001</v>
       </c>
       <c r="O76">
-        <v>-633.176491552</v>
+        <v>-644.3209036000003</v>
       </c>
       <c r="P76">
-        <v>-2244.898470048</v>
+        <v>-2284.410476400001</v>
       </c>
       <c r="Q76">
-        <v>-652.6984700480004</v>
+        <v>-692.2104764000007</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1311689223833627</v>
+        <v>0.1345836792786972</v>
       </c>
       <c r="T76">
-        <v>1.971568646267036</v>
+        <v>2.050431392117718</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05108874758056271</v>
+        <v>0.05040756427948853</v>
       </c>
       <c r="W76">
-        <v>0.190541379485823</v>
+        <v>0.1906781610926787</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2322215799116487</v>
+        <v>0.2291252921794933</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1766545406391833</v>
+        <v>0.1782045406391833</v>
       </c>
       <c r="C77">
-        <v>-10571.4849024959</v>
+        <v>-10890.63272694061</v>
       </c>
       <c r="D77">
-        <v>6766.090097504103</v>
+        <v>6699.215273059392</v>
       </c>
       <c r="E77">
-        <v>8971.775000000001</v>
+        <v>9224.048000000003</v>
       </c>
       <c r="F77">
-        <v>18920.475</v>
+        <v>19172.748</v>
       </c>
       <c r="G77">
         <v>1582.9</v>
@@ -7607,37 +7607,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M77">
-        <v>3799.231380000001</v>
+        <v>3849.887798400001</v>
       </c>
       <c r="N77">
-        <v>-2928.731380000001</v>
+        <v>-2979.387798400001</v>
       </c>
       <c r="O77">
-        <v>-644.3209036000003</v>
+        <v>-655.4653156480002</v>
       </c>
       <c r="P77">
-        <v>-2284.410476400001</v>
+        <v>-2323.922482752001</v>
       </c>
       <c r="Q77">
-        <v>-692.2104764000007</v>
+        <v>-731.7224827520006</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1345836792786972</v>
+        <v>0.1382829992486429</v>
       </c>
       <c r="T77">
-        <v>2.050431392117718</v>
+        <v>2.135866033455956</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05040756427948853</v>
+        <v>0.04974430685475841</v>
       </c>
       <c r="W77">
-        <v>0.1906781610926787</v>
+        <v>0.1908113431835645</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2291252921794933</v>
+        <v>0.2261104857034474</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1782045406391833</v>
+        <v>0.1797545406391833</v>
       </c>
       <c r="C78">
-        <v>-10890.63272694061</v>
+        <v>-11208.47153189068</v>
       </c>
       <c r="D78">
-        <v>6699.215273059392</v>
+        <v>6633.64946810932</v>
       </c>
       <c r="E78">
-        <v>9224.048000000003</v>
+        <v>9476.321000000004</v>
       </c>
       <c r="F78">
-        <v>19172.748</v>
+        <v>19425.021</v>
       </c>
       <c r="G78">
         <v>1582.9</v>
@@ -7689,37 +7689,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M78">
-        <v>3849.887798400001</v>
+        <v>3900.544216800001</v>
       </c>
       <c r="N78">
-        <v>-2979.387798400001</v>
+        <v>-3030.044216800001</v>
       </c>
       <c r="O78">
-        <v>-655.4653156480002</v>
+        <v>-666.6097276960002</v>
       </c>
       <c r="P78">
-        <v>-2323.922482752001</v>
+        <v>-2363.434489104001</v>
       </c>
       <c r="Q78">
-        <v>-731.7224827520006</v>
+        <v>-771.2344891040009</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1382829992486429</v>
+        <v>0.1423039992159752</v>
       </c>
       <c r="T78">
-        <v>2.135866033455956</v>
+        <v>2.228729774040998</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04974430685475841</v>
+        <v>0.04909827689560571</v>
       </c>
       <c r="W78">
-        <v>0.1908113431835645</v>
+        <v>0.1909410659993624</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2261104857034474</v>
+        <v>0.223173985889117</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1797545406391833</v>
+        <v>0.1813045406391833</v>
       </c>
       <c r="C79">
-        <v>-11208.47153189068</v>
+        <v>-11525.03937929485</v>
       </c>
       <c r="D79">
-        <v>6633.64946810932</v>
+        <v>6569.354620705151</v>
       </c>
       <c r="E79">
-        <v>9476.321000000004</v>
+        <v>9728.594000000001</v>
       </c>
       <c r="F79">
-        <v>19425.021</v>
+        <v>19677.294</v>
       </c>
       <c r="G79">
         <v>1582.9</v>
@@ -7771,37 +7771,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M79">
-        <v>3900.544216800001</v>
+        <v>3951.2006352</v>
       </c>
       <c r="N79">
-        <v>-3030.044216800001</v>
+        <v>-3080.700635200001</v>
       </c>
       <c r="O79">
-        <v>-666.6097276960002</v>
+        <v>-677.7541397440002</v>
       </c>
       <c r="P79">
-        <v>-2363.434489104001</v>
+        <v>-2402.946495456001</v>
       </c>
       <c r="Q79">
-        <v>-771.2344891040009</v>
+        <v>-810.7464954560007</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1423039992159752</v>
+        <v>0.1466905446348832</v>
       </c>
       <c r="T79">
-        <v>2.228729774040998</v>
+        <v>2.330035672861043</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04909827689560571</v>
+        <v>0.04846881180720052</v>
       </c>
       <c r="W79">
-        <v>0.1909410659993624</v>
+        <v>0.1910674625891141</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.223173985889117</v>
+        <v>0.2203127809418205</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1813045406391833</v>
+        <v>0.1828545406391834</v>
       </c>
       <c r="C80">
-        <v>-11525.03937929485</v>
+        <v>-11840.37286964617</v>
       </c>
       <c r="D80">
-        <v>6569.354620705151</v>
+        <v>6506.294130353835</v>
       </c>
       <c r="E80">
-        <v>9728.594000000001</v>
+        <v>9980.867000000002</v>
       </c>
       <c r="F80">
-        <v>19677.294</v>
+        <v>19929.567</v>
       </c>
       <c r="G80">
         <v>1582.9</v>
@@ -7853,37 +7853,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M80">
-        <v>3951.2006352</v>
+        <v>4001.857053600001</v>
       </c>
       <c r="N80">
-        <v>-3080.700635200001</v>
+        <v>-3131.357053600001</v>
       </c>
       <c r="O80">
-        <v>-677.7541397440002</v>
+        <v>-688.8985517920001</v>
       </c>
       <c r="P80">
-        <v>-2402.946495456001</v>
+        <v>-2442.458501808001</v>
       </c>
       <c r="Q80">
-        <v>-810.7464954560007</v>
+        <v>-850.2585018080006</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1466905446348832</v>
+        <v>0.1514948562841633</v>
       </c>
       <c r="T80">
-        <v>2.330035672861043</v>
+        <v>2.440989752521094</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04846881180720052</v>
+        <v>0.04785528254381823</v>
       </c>
       <c r="W80">
-        <v>0.1910674625891141</v>
+        <v>0.1911906592652013</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2203127809418205</v>
+        <v>0.2175240115628102</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1828545406391834</v>
+        <v>0.1844045406391833</v>
       </c>
       <c r="C81">
-        <v>-11840.37286964617</v>
+        <v>-12154.50721145905</v>
       </c>
       <c r="D81">
-        <v>6506.294130353835</v>
+        <v>6444.432788540953</v>
       </c>
       <c r="E81">
-        <v>9980.867000000002</v>
+        <v>10233.14</v>
       </c>
       <c r="F81">
-        <v>19929.567</v>
+        <v>20181.84</v>
       </c>
       <c r="G81">
         <v>1582.9</v>
@@ -7935,37 +7935,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M81">
-        <v>4001.857053600001</v>
+        <v>4052.513472000001</v>
       </c>
       <c r="N81">
-        <v>-3131.357053600001</v>
+        <v>-3182.013472000001</v>
       </c>
       <c r="O81">
-        <v>-688.8985517920001</v>
+        <v>-700.0429638400003</v>
       </c>
       <c r="P81">
-        <v>-2442.458501808001</v>
+        <v>-2481.970508160001</v>
       </c>
       <c r="Q81">
-        <v>-850.2585018080006</v>
+        <v>-889.7705081600013</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1514948562841633</v>
+        <v>0.1567795990983715</v>
       </c>
       <c r="T81">
-        <v>2.440989752521094</v>
+        <v>2.563039240147148</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04785528254381823</v>
+        <v>0.0472570915120205</v>
       </c>
       <c r="W81">
-        <v>0.1911906592652013</v>
+        <v>0.1913107760243863</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2175240115628102</v>
+        <v>0.2148049614182749</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1844045406391833</v>
+        <v>0.1859545406391833</v>
       </c>
       <c r="C82">
-        <v>-12154.50721145905</v>
+        <v>-12467.47628682016</v>
       </c>
       <c r="D82">
-        <v>6444.432788540953</v>
+        <v>6383.736713179848</v>
       </c>
       <c r="E82">
-        <v>10233.14</v>
+        <v>10485.413</v>
       </c>
       <c r="F82">
-        <v>20181.84</v>
+        <v>20434.113</v>
       </c>
       <c r="G82">
         <v>1582.9</v>
@@ -8017,37 +8017,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M82">
-        <v>4052.513472000001</v>
+        <v>4103.169890400001</v>
       </c>
       <c r="N82">
-        <v>-3182.013472000001</v>
+        <v>-3232.669890400001</v>
       </c>
       <c r="O82">
-        <v>-700.0429638400003</v>
+        <v>-711.1873758880002</v>
       </c>
       <c r="P82">
-        <v>-2481.970508160001</v>
+        <v>-2521.482514512001</v>
       </c>
       <c r="Q82">
-        <v>-889.7705081600013</v>
+        <v>-929.2825145120012</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1567795990983715</v>
+        <v>0.1626206306298647</v>
       </c>
       <c r="T82">
-        <v>2.563039240147148</v>
+        <v>2.697936042260156</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0472570915120205</v>
+        <v>0.04667367062915604</v>
       </c>
       <c r="W82">
-        <v>0.1913107760243863</v>
+        <v>0.1914279269376655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2148049614182749</v>
+        <v>0.2121530483143457</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1859545406391833</v>
+        <v>0.1875045406391833</v>
       </c>
       <c r="C83">
-        <v>-12467.47628682016</v>
+        <v>-12779.31271326951</v>
       </c>
       <c r="D83">
-        <v>6383.736713179848</v>
+        <v>6324.173286730492</v>
       </c>
       <c r="E83">
-        <v>10485.413</v>
+        <v>10737.686</v>
       </c>
       <c r="F83">
-        <v>20434.113</v>
+        <v>20686.386</v>
       </c>
       <c r="G83">
         <v>1582.9</v>
@@ -8099,37 +8099,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M83">
-        <v>4103.169890400001</v>
+        <v>4153.8263088</v>
       </c>
       <c r="N83">
-        <v>-3232.669890400001</v>
+        <v>-3283.3263088</v>
       </c>
       <c r="O83">
-        <v>-711.1873758880002</v>
+        <v>-722.3317879360001</v>
       </c>
       <c r="P83">
-        <v>-2521.482514512001</v>
+        <v>-2560.994520864</v>
       </c>
       <c r="Q83">
-        <v>-929.2825145120012</v>
+        <v>-968.7945208640001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1626206306298647</v>
+        <v>0.1691106656648572</v>
       </c>
       <c r="T83">
-        <v>2.697936042260156</v>
+        <v>2.847821377941275</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.04667367062915604</v>
+        <v>0.04610447952392244</v>
       </c>
       <c r="W83">
-        <v>0.1914279269376655</v>
+        <v>0.1915422205115964</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2121530483143457</v>
+        <v>0.2095658160178293</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1875045406391833</v>
+        <v>0.1890545406391834</v>
       </c>
       <c r="C84">
-        <v>-12779.31271326951</v>
+        <v>-13090.04790224941</v>
       </c>
       <c r="D84">
-        <v>6324.173286730492</v>
+        <v>6265.711097750597</v>
       </c>
       <c r="E84">
-        <v>10737.686</v>
+        <v>10989.959</v>
       </c>
       <c r="F84">
-        <v>20686.386</v>
+        <v>20938.659</v>
       </c>
       <c r="G84">
         <v>1582.9</v>
@@ -8181,37 +8181,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M84">
-        <v>4153.8263088</v>
+        <v>4204.482727200001</v>
       </c>
       <c r="N84">
-        <v>-3283.3263088</v>
+        <v>-3333.982727200001</v>
       </c>
       <c r="O84">
-        <v>-722.3317879360001</v>
+        <v>-733.4761999840002</v>
       </c>
       <c r="P84">
-        <v>-2560.994520864</v>
+        <v>-2600.506527216001</v>
       </c>
       <c r="Q84">
-        <v>-968.7945208640001</v>
+        <v>-1008.306527216001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1691106656648572</v>
+        <v>0.1763642342333783</v>
       </c>
       <c r="T84">
-        <v>2.847821377941275</v>
+        <v>3.015340282526057</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.04610447952392244</v>
+        <v>0.0455490038670077</v>
       </c>
       <c r="W84">
-        <v>0.1915422205115964</v>
+        <v>0.1916537600235049</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2095658160178293</v>
+        <v>0.2070409266682169</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1890545406391834</v>
+        <v>0.1906045406391833</v>
       </c>
       <c r="C85">
-        <v>-13090.04790224941</v>
+        <v>-13399.71211434104</v>
       </c>
       <c r="D85">
-        <v>6265.711097750597</v>
+        <v>6208.319885658962</v>
       </c>
       <c r="E85">
-        <v>10989.959</v>
+        <v>11242.232</v>
       </c>
       <c r="F85">
-        <v>20938.659</v>
+        <v>21190.932</v>
       </c>
       <c r="G85">
         <v>1582.9</v>
@@ -8263,37 +8263,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M85">
-        <v>4204.482727200001</v>
+        <v>4255.139145600001</v>
       </c>
       <c r="N85">
-        <v>-3333.982727200001</v>
+        <v>-3384.639145600001</v>
       </c>
       <c r="O85">
-        <v>-733.4761999840002</v>
+        <v>-744.6206120320003</v>
       </c>
       <c r="P85">
-        <v>-2600.506527216001</v>
+        <v>-2640.018533568001</v>
       </c>
       <c r="Q85">
-        <v>-1008.306527216001</v>
+        <v>-1047.818533568001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1763642342333783</v>
+        <v>0.1845244988729644</v>
       </c>
       <c r="T85">
-        <v>3.015340282526057</v>
+        <v>3.203799050183936</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0455490038670077</v>
+        <v>0.0450067538209719</v>
       </c>
       <c r="W85">
-        <v>0.1916537600235049</v>
+        <v>0.1917626438327489</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2070409266682169</v>
+        <v>0.2045761537316905</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1906045406391833</v>
+        <v>0.1921545406391833</v>
       </c>
       <c r="C86">
-        <v>-13399.71211434104</v>
+        <v>-13708.33451149312</v>
       </c>
       <c r="D86">
-        <v>6208.319885658964</v>
+        <v>6151.970488506879</v>
       </c>
       <c r="E86">
-        <v>11242.232</v>
+        <v>11494.505</v>
       </c>
       <c r="F86">
-        <v>21190.932</v>
+        <v>21443.205</v>
       </c>
       <c r="G86">
         <v>1582.9</v>
@@ -8345,37 +8345,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M86">
-        <v>4255.1391456</v>
+        <v>4305.795564000001</v>
       </c>
       <c r="N86">
-        <v>-3384.6391456</v>
+        <v>-3435.295564000001</v>
       </c>
       <c r="O86">
-        <v>-744.6206120320001</v>
+        <v>-755.7650240800002</v>
       </c>
       <c r="P86">
-        <v>-2640.018533568</v>
+        <v>-2679.530539920001</v>
       </c>
       <c r="Q86">
-        <v>-1047.818533568</v>
+        <v>-1087.330539920001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1845244988729643</v>
+        <v>0.1937727987978287</v>
       </c>
       <c r="T86">
-        <v>3.203799050183934</v>
+        <v>3.41738565352953</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04500675382097191</v>
+        <v>0.04447726259954871</v>
       </c>
       <c r="W86">
-        <v>0.1917626438327488</v>
+        <v>0.1918689656700106</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2045761537316906</v>
+        <v>0.2021693754524941</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1921545406391833</v>
+        <v>0.2239339875155095</v>
       </c>
       <c r="C87">
-        <v>-13708.33451149312</v>
+        <v>-14925.82539096335</v>
       </c>
       <c r="D87">
-        <v>6151.970488506879</v>
+        <v>5186.752609036651</v>
       </c>
       <c r="E87">
-        <v>11494.505</v>
+        <v>11746.778</v>
       </c>
       <c r="F87">
-        <v>21443.205</v>
+        <v>21695.478</v>
       </c>
       <c r="G87">
         <v>1582.9</v>
@@ -8427,45 +8427,45 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M87">
-        <v>4305.795564000001</v>
+        <v>5115.793712400001</v>
       </c>
       <c r="N87">
-        <v>-3435.295564000001</v>
+        <v>-4245.293712400001</v>
       </c>
       <c r="O87">
-        <v>-755.7650240800002</v>
+        <v>-933.9646167280002</v>
       </c>
       <c r="P87">
-        <v>-2679.530539920001</v>
+        <v>-3311.329095672001</v>
       </c>
       <c r="Q87">
-        <v>-1087.330539920001</v>
+        <v>-1719.129095672001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1937727987978287</v>
+        <v>0.2052669049714318</v>
       </c>
       <c r="T87">
-        <v>3.41738565352953</v>
+        <v>3.682838451996115</v>
       </c>
       <c r="U87">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04447726259954871</v>
+        <v>0.03743505128750702</v>
       </c>
       <c r="W87">
-        <v>0.1918689656700106</v>
+        <v>0.2269728149064059</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.2021693754524941</v>
+        <v>0.1701593240341228</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2239339875155095</v>
+        <v>0.2258339875155095</v>
       </c>
       <c r="C88">
-        <v>-14925.82539096335</v>
+        <v>-15226.29972697628</v>
       </c>
       <c r="D88">
-        <v>5186.752609036651</v>
+        <v>5138.551273023726</v>
       </c>
       <c r="E88">
-        <v>11746.778</v>
+        <v>11999.051</v>
       </c>
       <c r="F88">
-        <v>21695.478</v>
+        <v>21947.751</v>
       </c>
       <c r="G88">
         <v>1582.9</v>
@@ -8509,37 +8509,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M88">
-        <v>5115.793712400001</v>
+        <v>5175.279685800001</v>
       </c>
       <c r="N88">
-        <v>-4245.293712400001</v>
+        <v>-4304.779685800001</v>
       </c>
       <c r="O88">
-        <v>-933.9646167280002</v>
+        <v>-947.0515308760002</v>
       </c>
       <c r="P88">
-        <v>-3311.329095672001</v>
+        <v>-3357.728154924001</v>
       </c>
       <c r="Q88">
-        <v>-1719.129095672001</v>
+        <v>-1765.528154924001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2052669049714318</v>
+        <v>0.2175335899692342</v>
       </c>
       <c r="T88">
-        <v>3.682838451996115</v>
+        <v>3.966133717534277</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03743505128750702</v>
+        <v>0.0370047633416736</v>
       </c>
       <c r="W88">
-        <v>0.2269728149064059</v>
+        <v>0.2270742768040334</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1701593240341228</v>
+        <v>0.1682034697348801</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2258339875155095</v>
+        <v>0.2277339875155095</v>
       </c>
       <c r="C89">
-        <v>-15226.29972697628</v>
+        <v>-15525.88642622379</v>
       </c>
       <c r="D89">
-        <v>5138.551273023726</v>
+        <v>5091.237573776209</v>
       </c>
       <c r="E89">
-        <v>11999.051</v>
+        <v>12251.324</v>
       </c>
       <c r="F89">
-        <v>21947.751</v>
+        <v>22200.024</v>
       </c>
       <c r="G89">
         <v>1582.9</v>
@@ -8591,37 +8591,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M89">
-        <v>5175.279685800001</v>
+        <v>5234.7656592</v>
       </c>
       <c r="N89">
-        <v>-4304.779685800001</v>
+        <v>-4364.2656592</v>
       </c>
       <c r="O89">
-        <v>-947.0515308760002</v>
+        <v>-960.138445024</v>
       </c>
       <c r="P89">
-        <v>-3357.728154924001</v>
+        <v>-3404.127214176</v>
       </c>
       <c r="Q89">
-        <v>-1765.528154924001</v>
+        <v>-1811.927214176</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2175335899692342</v>
+        <v>0.2318447224666704</v>
       </c>
       <c r="T89">
-        <v>3.966133717534277</v>
+        <v>4.296644860662134</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0370047633416736</v>
+        <v>0.0365842546673364</v>
       </c>
       <c r="W89">
-        <v>0.2270742768040334</v>
+        <v>0.2271734327494421</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1682034697348801</v>
+        <v>0.166292066669711</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2277339875155095</v>
+        <v>0.2296339875155095</v>
       </c>
       <c r="C90">
-        <v>-15525.88642622379</v>
+        <v>-15824.60978400428</v>
       </c>
       <c r="D90">
-        <v>5091.237573776209</v>
+        <v>5044.787215995725</v>
       </c>
       <c r="E90">
-        <v>12251.324</v>
+        <v>12503.597</v>
       </c>
       <c r="F90">
-        <v>22200.024</v>
+        <v>22452.297</v>
       </c>
       <c r="G90">
         <v>1582.9</v>
@@ -8673,37 +8673,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M90">
-        <v>5234.7656592</v>
+        <v>5294.2516326</v>
       </c>
       <c r="N90">
-        <v>-4364.2656592</v>
+        <v>-4423.7516326</v>
       </c>
       <c r="O90">
-        <v>-960.138445024</v>
+        <v>-973.2253591720001</v>
       </c>
       <c r="P90">
-        <v>-3404.127214176</v>
+        <v>-3450.526273428</v>
       </c>
       <c r="Q90">
-        <v>-1811.927214176</v>
+        <v>-1858.326273428</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2318447224666704</v>
+        <v>0.2487578790545495</v>
       </c>
       <c r="T90">
-        <v>4.296644860662134</v>
+        <v>4.687248938904146</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0365842546673364</v>
+        <v>0.03617319562613037</v>
       </c>
       <c r="W90">
-        <v>0.2271734327494421</v>
+        <v>0.2272703604713585</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.166292066669711</v>
+        <v>0.1644236164824109</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2296339875155095</v>
+        <v>0.2315339875155095</v>
       </c>
       <c r="C91">
-        <v>-15824.60978400428</v>
+        <v>-16122.4932169911</v>
       </c>
       <c r="D91">
-        <v>5044.787215995725</v>
+        <v>4999.176783008906</v>
       </c>
       <c r="E91">
-        <v>12503.597</v>
+        <v>12755.87</v>
       </c>
       <c r="F91">
-        <v>22452.297</v>
+        <v>22704.57</v>
       </c>
       <c r="G91">
         <v>1582.9</v>
@@ -8755,37 +8755,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M91">
-        <v>5294.2516326</v>
+        <v>5353.737606000001</v>
       </c>
       <c r="N91">
-        <v>-4423.7516326</v>
+        <v>-4483.237606000001</v>
       </c>
       <c r="O91">
-        <v>-973.2253591720001</v>
+        <v>-986.3122733200001</v>
       </c>
       <c r="P91">
-        <v>-3450.526273428</v>
+        <v>-3496.92533268</v>
       </c>
       <c r="Q91">
-        <v>-1858.326273428</v>
+        <v>-1904.72533268</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2487578790545495</v>
+        <v>0.2690536669600045</v>
       </c>
       <c r="T91">
-        <v>4.687248938904146</v>
+        <v>5.155973832794562</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03617319562613037</v>
+        <v>0.03577127123028449</v>
       </c>
       <c r="W91">
-        <v>0.2272703604713585</v>
+        <v>0.2273651342438989</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1644236164824109</v>
+        <v>0.162596687410384</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2315339875155095</v>
+        <v>0.2334339875155095</v>
       </c>
       <c r="C92">
-        <v>-16122.4932169911</v>
+        <v>-16419.55930259537</v>
       </c>
       <c r="D92">
-        <v>4999.176783008906</v>
+        <v>4954.383697404634</v>
       </c>
       <c r="E92">
-        <v>12755.87</v>
+        <v>13008.143</v>
       </c>
       <c r="F92">
-        <v>22704.57</v>
+        <v>22956.843</v>
       </c>
       <c r="G92">
         <v>1582.9</v>
@@ -8837,37 +8837,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M92">
-        <v>5353.737606000001</v>
+        <v>5413.223579400002</v>
       </c>
       <c r="N92">
-        <v>-4483.237606000001</v>
+        <v>-4542.723579400002</v>
       </c>
       <c r="O92">
-        <v>-986.3122733200001</v>
+        <v>-999.3991874680004</v>
       </c>
       <c r="P92">
-        <v>-3496.92533268</v>
+        <v>-3543.324391932001</v>
       </c>
       <c r="Q92">
-        <v>-1904.72533268</v>
+        <v>-1951.124391932001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2690536669600045</v>
+        <v>0.2938596299555606</v>
       </c>
       <c r="T92">
-        <v>5.155973832794562</v>
+        <v>5.728859814216181</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03577127123028449</v>
+        <v>0.03537818033764399</v>
       </c>
       <c r="W92">
-        <v>0.2273651342438989</v>
+        <v>0.2274578250763836</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.162596687410384</v>
+        <v>0.1608099106256545</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2334339875155095</v>
+        <v>0.2353339875155095</v>
       </c>
       <c r="C93">
-        <v>-16419.55930259537</v>
+        <v>-16715.82981623145</v>
       </c>
       <c r="D93">
-        <v>4954.383697404634</v>
+        <v>4910.386183768557</v>
       </c>
       <c r="E93">
-        <v>13008.143</v>
+        <v>13260.416</v>
       </c>
       <c r="F93">
-        <v>22956.843</v>
+        <v>23209.11600000001</v>
       </c>
       <c r="G93">
         <v>1582.9</v>
@@ -8919,37 +8919,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M93">
-        <v>5413.223579400002</v>
+        <v>5472.709552800002</v>
       </c>
       <c r="N93">
-        <v>-4542.723579400002</v>
+        <v>-4602.209552800002</v>
       </c>
       <c r="O93">
-        <v>-999.3991874680004</v>
+        <v>-1012.486101616</v>
       </c>
       <c r="P93">
-        <v>-3543.324391932001</v>
+        <v>-3589.723451184002</v>
       </c>
       <c r="Q93">
-        <v>-1951.124391932001</v>
+        <v>-1997.523451184001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2938596299555606</v>
+        <v>0.3248670837000058</v>
       </c>
       <c r="T93">
-        <v>5.728859814216181</v>
+        <v>6.444967290993205</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03537818033764399</v>
+        <v>0.03499363489919134</v>
       </c>
       <c r="W93">
-        <v>0.2274578250763836</v>
+        <v>0.2275485008907707</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1608099106256545</v>
+        <v>0.1590619768145061</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2353339875155095</v>
+        <v>0.2372339875155095</v>
       </c>
       <c r="C94">
-        <v>-16715.82981623145</v>
+        <v>-17011.32576661417</v>
       </c>
       <c r="D94">
-        <v>4910.386183768557</v>
+        <v>4867.163233385833</v>
       </c>
       <c r="E94">
-        <v>13260.416</v>
+        <v>13512.689</v>
       </c>
       <c r="F94">
-        <v>23209.11600000001</v>
+        <v>23461.389</v>
       </c>
       <c r="G94">
         <v>1582.9</v>
@@ -9001,37 +9001,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M94">
-        <v>5472.709552800002</v>
+        <v>5532.195526200001</v>
       </c>
       <c r="N94">
-        <v>-4602.209552800002</v>
+        <v>-4661.695526200001</v>
       </c>
       <c r="O94">
-        <v>-1012.486101616</v>
+        <v>-1025.573015764</v>
       </c>
       <c r="P94">
-        <v>-3589.723451184002</v>
+        <v>-3636.122510436001</v>
       </c>
       <c r="Q94">
-        <v>-1997.523451184001</v>
+        <v>-2043.922510436001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3248670837000058</v>
+        <v>0.3647338099428638</v>
       </c>
       <c r="T94">
-        <v>6.444967290993205</v>
+        <v>7.365676903992235</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03499363489919134</v>
+        <v>0.03461735925511401</v>
       </c>
       <c r="W94">
-        <v>0.2275485008907707</v>
+        <v>0.2276372266876441</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1590619768145061</v>
+        <v>0.157351632977791</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2372339875155095</v>
+        <v>0.2391339875155095</v>
       </c>
       <c r="C95">
-        <v>-17011.32576661417</v>
+        <v>-17306.06742920825</v>
       </c>
       <c r="D95">
-        <v>4867.163233385833</v>
+        <v>4824.694570791748</v>
       </c>
       <c r="E95">
-        <v>13512.689</v>
+        <v>13764.962</v>
       </c>
       <c r="F95">
-        <v>23461.389</v>
+        <v>23713.662</v>
       </c>
       <c r="G95">
         <v>1582.9</v>
@@ -9083,37 +9083,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M95">
-        <v>5532.195526200001</v>
+        <v>5591.681499600001</v>
       </c>
       <c r="N95">
-        <v>-4661.695526200001</v>
+        <v>-4721.181499600001</v>
       </c>
       <c r="O95">
-        <v>-1025.573015764</v>
+        <v>-1038.659929912</v>
       </c>
       <c r="P95">
-        <v>-3636.122510436001</v>
+        <v>-3682.521569688001</v>
       </c>
       <c r="Q95">
-        <v>-2043.922510436001</v>
+        <v>-2090.321569688001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3647338099428638</v>
+        <v>0.4178894449333412</v>
       </c>
       <c r="T95">
-        <v>7.365676903992235</v>
+        <v>8.593289721324277</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03461735925511401</v>
+        <v>0.03424908947580429</v>
       </c>
       <c r="W95">
-        <v>0.2276372266876441</v>
+        <v>0.2277240647016054</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.157351632977791</v>
+        <v>0.1556776794354741</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2391339875155095</v>
+        <v>0.2410339875155095</v>
       </c>
       <c r="C96">
-        <v>-17306.06742920825</v>
+        <v>-17600.07437794161</v>
       </c>
       <c r="D96">
-        <v>4824.694570791748</v>
+        <v>4782.960622058393</v>
       </c>
       <c r="E96">
-        <v>13764.962</v>
+        <v>14017.235</v>
       </c>
       <c r="F96">
-        <v>23713.662</v>
+        <v>23965.935</v>
       </c>
       <c r="G96">
         <v>1582.9</v>
@@ -9165,37 +9165,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M96">
-        <v>5591.681499600001</v>
+        <v>5651.167473000001</v>
       </c>
       <c r="N96">
-        <v>-4721.181499600001</v>
+        <v>-4780.667473000001</v>
       </c>
       <c r="O96">
-        <v>-1038.659929912</v>
+        <v>-1051.74684406</v>
       </c>
       <c r="P96">
-        <v>-3682.521569688001</v>
+        <v>-3728.920628940001</v>
       </c>
       <c r="Q96">
-        <v>-2090.321569688001</v>
+        <v>-2136.720628940001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4178894449333412</v>
+        <v>0.4923073339200096</v>
       </c>
       <c r="T96">
-        <v>8.593289721324277</v>
+        <v>10.31194766558914</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03424908947580429</v>
+        <v>0.03388857274448003</v>
       </c>
       <c r="W96">
-        <v>0.2277240647016054</v>
+        <v>0.2278090745468516</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1556776794354741</v>
+        <v>0.1540389670203638</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2410339875155095</v>
+        <v>0.2429339875155095</v>
       </c>
       <c r="C97">
-        <v>-17600.07437794161</v>
+        <v>-17893.36551528685</v>
       </c>
       <c r="D97">
-        <v>4782.960622058393</v>
+        <v>4741.942484713159</v>
       </c>
       <c r="E97">
-        <v>14017.235</v>
+        <v>14269.50800000001</v>
       </c>
       <c r="F97">
-        <v>23965.935</v>
+        <v>24218.20800000001</v>
       </c>
       <c r="G97">
         <v>1582.9</v>
@@ -9247,37 +9247,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M97">
-        <v>5651.167473000001</v>
+        <v>5710.653446400001</v>
       </c>
       <c r="N97">
-        <v>-4780.667473000001</v>
+        <v>-4840.153446400001</v>
       </c>
       <c r="O97">
-        <v>-1051.74684406</v>
+        <v>-1064.833758208</v>
       </c>
       <c r="P97">
-        <v>-3728.920628940001</v>
+        <v>-3775.319688192001</v>
       </c>
       <c r="Q97">
-        <v>-2136.720628940001</v>
+        <v>-2183.119688192001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4923073339200096</v>
+        <v>0.6039341674000122</v>
       </c>
       <c r="T97">
-        <v>10.31194766558914</v>
+        <v>12.88993458198643</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03388857274448003</v>
+        <v>0.0335355667783917</v>
       </c>
       <c r="W97">
-        <v>0.2278090745468516</v>
+        <v>0.2278923133536553</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1540389670203638</v>
+        <v>0.1524343944472351</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2429339875155095</v>
+        <v>0.2448339875155095</v>
       </c>
       <c r="C98">
-        <v>-17893.36551528684</v>
+        <v>-18185.95910080808</v>
       </c>
       <c r="D98">
-        <v>4741.942484713161</v>
+        <v>4701.62189919192</v>
       </c>
       <c r="E98">
-        <v>14269.508</v>
+        <v>14521.781</v>
       </c>
       <c r="F98">
-        <v>24218.208</v>
+        <v>24470.481</v>
       </c>
       <c r="G98">
         <v>1582.9</v>
@@ -9329,37 +9329,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M98">
-        <v>5710.653446400001</v>
+        <v>5770.139419800001</v>
       </c>
       <c r="N98">
-        <v>-4840.153446400001</v>
+        <v>-4899.639419800001</v>
       </c>
       <c r="O98">
-        <v>-1064.833758208</v>
+        <v>-1077.920672356</v>
       </c>
       <c r="P98">
-        <v>-3775.319688192</v>
+        <v>-3821.718747444001</v>
       </c>
       <c r="Q98">
-        <v>-2183.119688192</v>
+        <v>-2229.518747444001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6039341674000106</v>
+        <v>0.789978889866681</v>
       </c>
       <c r="T98">
-        <v>12.88993458198639</v>
+        <v>17.18657944264852</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03353556677839171</v>
+        <v>0.03318983928583096</v>
       </c>
       <c r="W98">
-        <v>0.2278923133536552</v>
+        <v>0.2279738358964011</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1524343944472351</v>
+        <v>0.1508629058446862</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2448339875155095</v>
+        <v>0.2467339875155095</v>
       </c>
       <c r="C99">
-        <v>-18185.95910080808</v>
+        <v>-18477.87277826366</v>
       </c>
       <c r="D99">
-        <v>4701.62189919192</v>
+        <v>4661.98122173634</v>
       </c>
       <c r="E99">
-        <v>14521.781</v>
+        <v>14774.054</v>
       </c>
       <c r="F99">
-        <v>24470.481</v>
+        <v>24722.754</v>
       </c>
       <c r="G99">
         <v>1582.9</v>
@@ -9411,37 +9411,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M99">
-        <v>5770.139419800001</v>
+        <v>5829.625393200001</v>
       </c>
       <c r="N99">
-        <v>-4899.639419800001</v>
+        <v>-4959.125393200001</v>
       </c>
       <c r="O99">
-        <v>-1077.920672356</v>
+        <v>-1091.007586504</v>
       </c>
       <c r="P99">
-        <v>-3821.718747444001</v>
+        <v>-3868.117806696001</v>
       </c>
       <c r="Q99">
-        <v>-2229.518747444001</v>
+        <v>-2275.917806696</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.789978889866681</v>
+        <v>1.162068334800021</v>
       </c>
       <c r="T99">
-        <v>17.18657944264852</v>
+        <v>25.77986916397278</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03318983928583096</v>
+        <v>0.03285116745638371</v>
       </c>
       <c r="W99">
-        <v>0.2279738358964011</v>
+        <v>0.2280536947137847</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1508629058446862</v>
+        <v>0.1493234884381078</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2467339875155095</v>
+        <v>0.2486339875155095</v>
       </c>
       <c r="C100">
-        <v>-18477.87277826366</v>
+        <v>-18769.12360134923</v>
       </c>
       <c r="D100">
-        <v>4661.98122173634</v>
+        <v>4623.00339865077</v>
       </c>
       <c r="E100">
-        <v>14774.054</v>
+        <v>15026.327</v>
       </c>
       <c r="F100">
-        <v>24722.754</v>
+        <v>24975.027</v>
       </c>
       <c r="G100">
         <v>1582.9</v>
@@ -9493,37 +9493,37 @@
         <v>870.4999999999998</v>
       </c>
       <c r="M100">
-        <v>5829.625393200001</v>
+        <v>5889.111366600001</v>
       </c>
       <c r="N100">
-        <v>-4959.125393200001</v>
+        <v>-5018.611366600001</v>
       </c>
       <c r="O100">
-        <v>-1091.007586504</v>
+        <v>-1104.094500652</v>
       </c>
       <c r="P100">
-        <v>-3868.117806696001</v>
+        <v>-3914.516865948</v>
       </c>
       <c r="Q100">
-        <v>-2275.917806696</v>
+        <v>-2322.316865948001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.162068334800021</v>
+        <v>2.278336669600042</v>
       </c>
       <c r="T100">
-        <v>25.77986916397278</v>
+        <v>51.55973832794556</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03285116745638371</v>
+        <v>0.0325193374820768</v>
       </c>
       <c r="W100">
-        <v>0.2280536947137847</v>
+        <v>0.2281319402217263</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1493234884381078</v>
+        <v>0.1478151703730765</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2486339875155095</v>
-      </c>
-      <c r="C101">
-        <v>-18769.12360134923</v>
-      </c>
-      <c r="D101">
-        <v>4623.00339865077</v>
-      </c>
-      <c r="E101">
-        <v>15026.327</v>
-      </c>
-      <c r="F101">
-        <v>24975.027</v>
-      </c>
-      <c r="G101">
-        <v>1582.9</v>
-      </c>
-      <c r="H101">
-        <v>15278.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2462.7</v>
-      </c>
-      <c r="K101">
-        <v>1592.2</v>
-      </c>
-      <c r="L101">
-        <v>870.4999999999998</v>
-      </c>
-      <c r="M101">
-        <v>5889.111366600001</v>
-      </c>
-      <c r="N101">
-        <v>-5018.611366600001</v>
-      </c>
-      <c r="O101">
-        <v>-1104.094500652</v>
-      </c>
-      <c r="P101">
-        <v>-3914.516865948</v>
-      </c>
-      <c r="Q101">
-        <v>-2322.316865948001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.278336669600042</v>
-      </c>
-      <c r="T101">
-        <v>51.55973832794556</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0325193374820768</v>
-      </c>
-      <c r="W101">
-        <v>0.2281319402217263</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1478151703730765</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
